--- a/data/nzd0003/nzd0003.xlsx
+++ b/data/nzd0003/nzd0003.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH184"/>
+  <dimension ref="A1:AH185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20115,13 +20115,13 @@
         <v>340.52</v>
       </c>
       <c r="W183" t="n">
-        <v>341.9</v>
+        <v>347.09</v>
       </c>
       <c r="X183" t="n">
-        <v>328.6</v>
+        <v>337.43</v>
       </c>
       <c r="Y183" t="n">
-        <v>338.97</v>
+        <v>343.98</v>
       </c>
       <c r="Z183" t="n">
         <v>337.43</v>
@@ -20160,10 +20160,10 @@
         </is>
       </c>
       <c r="B184" t="n">
-        <v>308.55</v>
+        <v>313.27</v>
       </c>
       <c r="C184" t="n">
-        <v>305.68</v>
+        <v>310.99</v>
       </c>
       <c r="D184" t="n">
         <v>310.12</v>
@@ -20223,13 +20223,13 @@
         <v>343.56</v>
       </c>
       <c r="W184" t="n">
-        <v>341.9</v>
+        <v>347.09</v>
       </c>
       <c r="X184" t="n">
-        <v>328.6</v>
+        <v>337.43</v>
       </c>
       <c r="Y184" t="n">
-        <v>338.97</v>
+        <v>343.98</v>
       </c>
       <c r="Z184" t="n">
         <v>337.43</v>
@@ -20256,6 +20256,114 @@
         <v>312.16</v>
       </c>
       <c r="AH184" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:17:51+00:00</t>
+        </is>
+      </c>
+      <c r="B185" t="n">
+        <v>314.84</v>
+      </c>
+      <c r="C185" t="n">
+        <v>310.9</v>
+      </c>
+      <c r="D185" t="n">
+        <v>301.87</v>
+      </c>
+      <c r="E185" t="n">
+        <v>319.35</v>
+      </c>
+      <c r="F185" t="n">
+        <v>324.12</v>
+      </c>
+      <c r="G185" t="n">
+        <v>333.34</v>
+      </c>
+      <c r="H185" t="n">
+        <v>339.89</v>
+      </c>
+      <c r="I185" t="n">
+        <v>346.71</v>
+      </c>
+      <c r="J185" t="n">
+        <v>356.43</v>
+      </c>
+      <c r="K185" t="n">
+        <v>355.77</v>
+      </c>
+      <c r="L185" t="n">
+        <v>352.72</v>
+      </c>
+      <c r="M185" t="n">
+        <v>350.36</v>
+      </c>
+      <c r="N185" t="n">
+        <v>347.16</v>
+      </c>
+      <c r="O185" t="n">
+        <v>346.56</v>
+      </c>
+      <c r="P185" t="n">
+        <v>344.17</v>
+      </c>
+      <c r="Q185" t="n">
+        <v>343.02</v>
+      </c>
+      <c r="R185" t="n">
+        <v>336.07</v>
+      </c>
+      <c r="S185" t="n">
+        <v>340.7</v>
+      </c>
+      <c r="T185" t="n">
+        <v>339.94</v>
+      </c>
+      <c r="U185" t="n">
+        <v>338.6</v>
+      </c>
+      <c r="V185" t="n">
+        <v>346.61</v>
+      </c>
+      <c r="W185" t="n">
+        <v>347.07</v>
+      </c>
+      <c r="X185" t="n">
+        <v>340.17</v>
+      </c>
+      <c r="Y185" t="n">
+        <v>349.09</v>
+      </c>
+      <c r="Z185" t="n">
+        <v>343.81</v>
+      </c>
+      <c r="AA185" t="n">
+        <v>336.03</v>
+      </c>
+      <c r="AB185" t="n">
+        <v>329.24</v>
+      </c>
+      <c r="AC185" t="n">
+        <v>323.3</v>
+      </c>
+      <c r="AD185" t="n">
+        <v>323.84</v>
+      </c>
+      <c r="AE185" t="n">
+        <v>325.86</v>
+      </c>
+      <c r="AF185" t="n">
+        <v>322.1</v>
+      </c>
+      <c r="AG185" t="n">
+        <v>313.32</v>
+      </c>
+      <c r="AH185" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -20272,7 +20380,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B185"/>
+  <dimension ref="A1:B186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22125,6 +22233,16 @@
       </c>
       <c r="B185" t="n">
         <v>-0.23</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B186" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -22293,28 +22411,28 @@
         <v>0.0366</v>
       </c>
       <c r="I2" t="n">
-        <v>1.121752483770701</v>
+        <v>1.104244000223428</v>
       </c>
       <c r="J2" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="K2" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2583225993249452</v>
+        <v>0.2534870662715749</v>
       </c>
       <c r="M2" t="n">
-        <v>12.35134191377381</v>
+        <v>12.36105844632712</v>
       </c>
       <c r="N2" t="n">
-        <v>228.0839544463019</v>
+        <v>228.0978683487552</v>
       </c>
       <c r="O2" t="n">
-        <v>15.10244862419012</v>
+        <v>15.10290926771247</v>
       </c>
       <c r="P2" t="n">
-        <v>307.1962272240319</v>
+        <v>307.3595062549546</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -22371,28 +22489,28 @@
         <v>0.0328</v>
       </c>
       <c r="I3" t="n">
-        <v>1.118996263883629</v>
+        <v>1.102151338176627</v>
       </c>
       <c r="J3" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="K3" t="n">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2566335216641261</v>
+        <v>0.2521577302084</v>
       </c>
       <c r="M3" t="n">
-        <v>11.96170492514781</v>
+        <v>11.97435582236456</v>
       </c>
       <c r="N3" t="n">
-        <v>231.1278209998165</v>
+        <v>231.0121879669879</v>
       </c>
       <c r="O3" t="n">
-        <v>15.20288857420906</v>
+        <v>15.19908510295892</v>
       </c>
       <c r="P3" t="n">
-        <v>303.1915421733197</v>
+        <v>303.3470134323667</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -22449,28 +22567,28 @@
         <v>0.0287</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4542074187058802</v>
+        <v>0.4276526411212234</v>
       </c>
       <c r="J4" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="K4" t="n">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="L4" t="n">
-        <v>0.04379183801000608</v>
+        <v>0.03896564248905365</v>
       </c>
       <c r="M4" t="n">
-        <v>13.27931195208826</v>
+        <v>13.3486544535513</v>
       </c>
       <c r="N4" t="n">
-        <v>281.2001804269852</v>
+        <v>283.348759839003</v>
       </c>
       <c r="O4" t="n">
-        <v>16.76902443277441</v>
+        <v>16.83296645986687</v>
       </c>
       <c r="P4" t="n">
-        <v>315.9962238036005</v>
+        <v>316.2440837404448</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -22527,28 +22645,28 @@
         <v>0.035</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9387224421076605</v>
+        <v>0.9243162132903535</v>
       </c>
       <c r="J5" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="K5" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1914186794616051</v>
+        <v>0.187850729894243</v>
       </c>
       <c r="M5" t="n">
-        <v>12.58119637694516</v>
+        <v>12.58695545489359</v>
       </c>
       <c r="N5" t="n">
-        <v>234.7322108303322</v>
+        <v>234.4728846342299</v>
       </c>
       <c r="O5" t="n">
-        <v>15.32097290743418</v>
+        <v>15.31250745744243</v>
       </c>
       <c r="P5" t="n">
-        <v>308.5200585620213</v>
+        <v>308.6525044392894</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -22605,28 +22723,28 @@
         <v>0.0321</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7317350202624691</v>
+        <v>0.7194478386200682</v>
       </c>
       <c r="J6" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="K6" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1350492595011845</v>
+        <v>0.1320702325541319</v>
       </c>
       <c r="M6" t="n">
-        <v>11.79028794719247</v>
+        <v>11.78395976040824</v>
       </c>
       <c r="N6" t="n">
-        <v>216.549641914644</v>
+        <v>216.1643944156329</v>
       </c>
       <c r="O6" t="n">
-        <v>14.71562577380398</v>
+        <v>14.70253020454755</v>
       </c>
       <c r="P6" t="n">
-        <v>317.0800445796704</v>
+        <v>317.1931428037089</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -22683,28 +22801,28 @@
         <v>0.034</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4365734935633627</v>
+        <v>0.4331670204361249</v>
       </c>
       <c r="J7" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="K7" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="L7" t="n">
-        <v>0.05645939148753198</v>
+        <v>0.05624021174356153</v>
       </c>
       <c r="M7" t="n">
-        <v>11.30024740879458</v>
+        <v>11.25345444379944</v>
       </c>
       <c r="N7" t="n">
-        <v>201.1359738951856</v>
+        <v>200.0926723498357</v>
       </c>
       <c r="O7" t="n">
-        <v>14.18224149756256</v>
+        <v>14.14541170662189</v>
       </c>
       <c r="P7" t="n">
-        <v>325.2359302375069</v>
+        <v>325.2672853580007</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -22761,28 +22879,28 @@
         <v>0.0439</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4633049236103581</v>
+        <v>0.4613375903307176</v>
       </c>
       <c r="J8" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="K8" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="L8" t="n">
-        <v>0.08913835539244319</v>
+        <v>0.0893979837691713</v>
       </c>
       <c r="M8" t="n">
-        <v>9.146170044185693</v>
+        <v>9.106030925238802</v>
       </c>
       <c r="N8" t="n">
-        <v>138.5071681779578</v>
+        <v>137.7667661905488</v>
       </c>
       <c r="O8" t="n">
-        <v>11.76890683869822</v>
+        <v>11.73740883630407</v>
       </c>
       <c r="P8" t="n">
-        <v>329.6570589947373</v>
+        <v>329.6751674517044</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -22839,28 +22957,28 @@
         <v>0.0436</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4690077291472549</v>
+        <v>0.4668824961708092</v>
       </c>
       <c r="J9" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="K9" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1079982498800542</v>
+        <v>0.1082450842525874</v>
       </c>
       <c r="M9" t="n">
-        <v>8.293649939302528</v>
+        <v>8.257834120689594</v>
       </c>
       <c r="N9" t="n">
-        <v>114.7254076887987</v>
+        <v>114.1191185693457</v>
       </c>
       <c r="O9" t="n">
-        <v>10.71099471052053</v>
+        <v>10.6826550337145</v>
       </c>
       <c r="P9" t="n">
-        <v>336.4879084419436</v>
+        <v>336.5074702977295</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -22917,28 +23035,28 @@
         <v>0.0433</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5586859866999891</v>
+        <v>0.5584254055258275</v>
       </c>
       <c r="J10" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="K10" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1190713922930204</v>
+        <v>0.1202214277821697</v>
       </c>
       <c r="M10" t="n">
-        <v>9.002755102943887</v>
+        <v>8.954619721144416</v>
       </c>
       <c r="N10" t="n">
-        <v>145.8207943396228</v>
+        <v>145.0199430549475</v>
       </c>
       <c r="O10" t="n">
-        <v>12.07562811366857</v>
+        <v>12.04242264060465</v>
       </c>
       <c r="P10" t="n">
-        <v>341.9944848663667</v>
+        <v>341.9968834040358</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -22995,28 +23113,28 @@
         <v>0.0418</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5801087888768822</v>
+        <v>0.5834001833674057</v>
       </c>
       <c r="J11" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="K11" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1311561262709537</v>
+        <v>0.1337712254397809</v>
       </c>
       <c r="M11" t="n">
-        <v>9.432851973952316</v>
+        <v>9.394261038777627</v>
       </c>
       <c r="N11" t="n">
-        <v>140.7740722295789</v>
+        <v>140.0583217817383</v>
       </c>
       <c r="O11" t="n">
-        <v>11.86482499784885</v>
+        <v>11.83462385467904</v>
       </c>
       <c r="P11" t="n">
-        <v>337.2382907435618</v>
+        <v>337.2079948724401</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -23073,28 +23191,28 @@
         <v>0.0421</v>
       </c>
       <c r="I12" t="n">
-        <v>0.6043465120503583</v>
+        <v>0.6086882465263107</v>
       </c>
       <c r="J12" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="K12" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1353884597686826</v>
+        <v>0.1383995449000794</v>
       </c>
       <c r="M12" t="n">
-        <v>9.581338224701751</v>
+        <v>9.548320763915124</v>
       </c>
       <c r="N12" t="n">
-        <v>147.2861945820856</v>
+        <v>146.5773900306743</v>
       </c>
       <c r="O12" t="n">
-        <v>12.13615237965005</v>
+        <v>12.10691496751647</v>
       </c>
       <c r="P12" t="n">
-        <v>332.5125983595109</v>
+        <v>332.4726345604259</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -23151,28 +23269,28 @@
         <v>0.0429</v>
       </c>
       <c r="I13" t="n">
-        <v>0.6385048391041344</v>
+        <v>0.6452019569636704</v>
       </c>
       <c r="J13" t="n">
+        <v>184</v>
+      </c>
+      <c r="K13" t="n">
         <v>183</v>
       </c>
-      <c r="K13" t="n">
-        <v>182</v>
-      </c>
       <c r="L13" t="n">
-        <v>0.1984389591246375</v>
+        <v>0.2033156887358171</v>
       </c>
       <c r="M13" t="n">
-        <v>8.136308999450103</v>
+        <v>8.12317452378101</v>
       </c>
       <c r="N13" t="n">
-        <v>104.9239455177484</v>
+        <v>104.5923250073248</v>
       </c>
       <c r="O13" t="n">
-        <v>10.24323901496731</v>
+        <v>10.2270389168774</v>
       </c>
       <c r="P13" t="n">
-        <v>326.8500358887566</v>
+        <v>326.7889725420501</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -23229,28 +23347,28 @@
         <v>0.0448</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5822704687821689</v>
+        <v>0.5875575703634135</v>
       </c>
       <c r="J14" t="n">
+        <v>184</v>
+      </c>
+      <c r="K14" t="n">
         <v>183</v>
       </c>
-      <c r="K14" t="n">
-        <v>182</v>
-      </c>
       <c r="L14" t="n">
-        <v>0.1763851020174424</v>
+        <v>0.1805494769798326</v>
       </c>
       <c r="M14" t="n">
-        <v>8.008815164774781</v>
+        <v>7.991721718007088</v>
       </c>
       <c r="N14" t="n">
-        <v>100.8668338792937</v>
+        <v>100.466308956171</v>
       </c>
       <c r="O14" t="n">
-        <v>10.0432481737381</v>
+        <v>10.0232883304917</v>
       </c>
       <c r="P14" t="n">
-        <v>326.5467976696161</v>
+        <v>326.4985906462818</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -23307,28 +23425,28 @@
         <v>0.0419</v>
       </c>
       <c r="I15" t="n">
-        <v>0.6328043449204063</v>
+        <v>0.637448779638521</v>
       </c>
       <c r="J15" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="K15" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1874405276068671</v>
+        <v>0.1913344270832786</v>
       </c>
       <c r="M15" t="n">
-        <v>8.271564624818007</v>
+        <v>8.248282685816301</v>
       </c>
       <c r="N15" t="n">
-        <v>110.7654975562325</v>
+        <v>110.2735987756204</v>
       </c>
       <c r="O15" t="n">
-        <v>10.52451887528511</v>
+        <v>10.50112369109232</v>
       </c>
       <c r="P15" t="n">
-        <v>325.2668417533358</v>
+        <v>325.2244371240849</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -23385,28 +23503,28 @@
         <v>0.0442</v>
       </c>
       <c r="I16" t="n">
-        <v>0.687760175287028</v>
+        <v>0.6906070810752005</v>
       </c>
       <c r="J16" t="n">
+        <v>184</v>
+      </c>
+      <c r="K16" t="n">
         <v>183</v>
       </c>
-      <c r="K16" t="n">
-        <v>182</v>
-      </c>
       <c r="L16" t="n">
-        <v>0.2033056727677389</v>
+        <v>0.2065112368710619</v>
       </c>
       <c r="M16" t="n">
-        <v>8.906313226387331</v>
+        <v>8.869173210711953</v>
       </c>
       <c r="N16" t="n">
-        <v>117.6338034801242</v>
+        <v>117.0346499715438</v>
       </c>
       <c r="O16" t="n">
-        <v>10.84591183258117</v>
+        <v>10.81825540332376</v>
       </c>
       <c r="P16" t="n">
-        <v>323.2256778409121</v>
+        <v>323.1995930969046</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -23463,28 +23581,28 @@
         <v>0.0482</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6414691034128981</v>
+        <v>0.6430729587460858</v>
       </c>
       <c r="J17" t="n">
+        <v>184</v>
+      </c>
+      <c r="K17" t="n">
         <v>183</v>
       </c>
-      <c r="K17" t="n">
-        <v>182</v>
-      </c>
       <c r="L17" t="n">
-        <v>0.1967355875975859</v>
+        <v>0.1993802438986003</v>
       </c>
       <c r="M17" t="n">
-        <v>8.491265633440555</v>
+        <v>8.451600790240596</v>
       </c>
       <c r="N17" t="n">
-        <v>106.6210484446175</v>
+        <v>106.0522748701008</v>
       </c>
       <c r="O17" t="n">
-        <v>10.32574687103153</v>
+        <v>10.29816852018361</v>
       </c>
       <c r="P17" t="n">
-        <v>324.5365214430933</v>
+        <v>324.5218261356599</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -23541,28 +23659,28 @@
         <v>0.0524</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5876380328785485</v>
+        <v>0.586176204191835</v>
       </c>
       <c r="J18" t="n">
+        <v>184</v>
+      </c>
+      <c r="K18" t="n">
         <v>183</v>
       </c>
-      <c r="K18" t="n">
-        <v>182</v>
-      </c>
       <c r="L18" t="n">
-        <v>0.1286495548399491</v>
+        <v>0.1294056250764849</v>
       </c>
       <c r="M18" t="n">
-        <v>10.65168460500503</v>
+        <v>10.60321881264777</v>
       </c>
       <c r="N18" t="n">
-        <v>148.4295000560546</v>
+        <v>147.62991981466</v>
       </c>
       <c r="O18" t="n">
-        <v>12.18316461581533</v>
+        <v>12.15030533833039</v>
       </c>
       <c r="P18" t="n">
-        <v>322.0809218860447</v>
+        <v>322.0943158758403</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -23619,28 +23737,28 @@
         <v>0.05</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4075768071006595</v>
+        <v>0.4163727810631477</v>
       </c>
       <c r="J19" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="K19" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="L19" t="n">
-        <v>0.07893542706222922</v>
+        <v>0.08273343011344847</v>
       </c>
       <c r="M19" t="n">
-        <v>9.235599605108558</v>
+        <v>9.225415108833252</v>
       </c>
       <c r="N19" t="n">
-        <v>122.8375829786211</v>
+        <v>122.5851556212783</v>
       </c>
       <c r="O19" t="n">
-        <v>11.08321176277983</v>
+        <v>11.07181808111379</v>
       </c>
       <c r="P19" t="n">
-        <v>321.1626156591047</v>
+        <v>321.0821331612764</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -23697,28 +23815,28 @@
         <v>0.0506</v>
       </c>
       <c r="I20" t="n">
-        <v>0.2773260173492831</v>
+        <v>0.2871495079136117</v>
       </c>
       <c r="J20" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="K20" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="L20" t="n">
-        <v>0.03898382192259742</v>
+        <v>0.04197759729125827</v>
       </c>
       <c r="M20" t="n">
-        <v>9.079447679262216</v>
+        <v>9.072975295508169</v>
       </c>
       <c r="N20" t="n">
-        <v>120.1494357191729</v>
+        <v>120.0142804552349</v>
       </c>
       <c r="O20" t="n">
-        <v>10.96126980414098</v>
+        <v>10.95510294133446</v>
       </c>
       <c r="P20" t="n">
-        <v>322.8023791986068</v>
+        <v>322.7124950014295</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -23775,28 +23893,28 @@
         <v>0.0544</v>
       </c>
       <c r="I21" t="n">
-        <v>0.4407350382726815</v>
+        <v>0.4468484964682901</v>
       </c>
       <c r="J21" t="n">
+        <v>184</v>
+      </c>
+      <c r="K21" t="n">
         <v>183</v>
       </c>
-      <c r="K21" t="n">
-        <v>182</v>
-      </c>
       <c r="L21" t="n">
-        <v>0.09455114045445556</v>
+        <v>0.09782182346873347</v>
       </c>
       <c r="M21" t="n">
-        <v>8.876079618246969</v>
+        <v>8.854436446229755</v>
       </c>
       <c r="N21" t="n">
-        <v>118.0505930655642</v>
+        <v>117.6068122937955</v>
       </c>
       <c r="O21" t="n">
-        <v>10.86510897623969</v>
+        <v>10.84466745888483</v>
       </c>
       <c r="P21" t="n">
-        <v>320.8808950476123</v>
+        <v>320.8248805519115</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -23853,28 +23971,28 @@
         <v>0.0505</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2713545289920898</v>
+        <v>0.2855619162800117</v>
       </c>
       <c r="J22" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="K22" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="L22" t="n">
-        <v>0.02961278977107018</v>
+        <v>0.03284035612633662</v>
       </c>
       <c r="M22" t="n">
-        <v>10.22885332308254</v>
+        <v>10.23139948238514</v>
       </c>
       <c r="N22" t="n">
-        <v>152.909374199959</v>
+        <v>153.1614851357744</v>
       </c>
       <c r="O22" t="n">
-        <v>12.36565300337831</v>
+        <v>12.37584280506885</v>
       </c>
       <c r="P22" t="n">
-        <v>325.2305999792959</v>
+        <v>325.1006034579984</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -23931,28 +24049,28 @@
         <v>0.0567</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2727210270960424</v>
+        <v>0.2953915111028976</v>
       </c>
       <c r="J23" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="K23" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="L23" t="n">
-        <v>0.03042811877601914</v>
+        <v>0.03547598303547694</v>
       </c>
       <c r="M23" t="n">
-        <v>9.692541460318877</v>
+        <v>9.753380188705538</v>
       </c>
       <c r="N23" t="n">
-        <v>150.1883957149948</v>
+        <v>151.2980440312423</v>
       </c>
       <c r="O23" t="n">
-        <v>12.25513752329996</v>
+        <v>12.30032698879352</v>
       </c>
       <c r="P23" t="n">
-        <v>327.3975984975386</v>
+        <v>327.1910097890136</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -24009,28 +24127,28 @@
         <v>0.0536</v>
       </c>
       <c r="I24" t="n">
-        <v>0.3978004663429848</v>
+        <v>0.4153953548055233</v>
       </c>
       <c r="J24" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="K24" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="L24" t="n">
-        <v>0.06604073675637323</v>
+        <v>0.07301725292812067</v>
       </c>
       <c r="M24" t="n">
-        <v>9.628689766439249</v>
+        <v>9.469563687512535</v>
       </c>
       <c r="N24" t="n">
-        <v>141.8210908809113</v>
+        <v>139.7102010604394</v>
       </c>
       <c r="O24" t="n">
-        <v>11.90886606192677</v>
+        <v>11.81990698188608</v>
       </c>
       <c r="P24" t="n">
-        <v>329.4557704489782</v>
+        <v>329.2962138793602</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -24087,28 +24205,28 @@
         <v>0.0562</v>
       </c>
       <c r="I25" t="n">
-        <v>0.2476001676368645</v>
+        <v>0.2686549224966987</v>
       </c>
       <c r="J25" t="n">
+        <v>184</v>
+      </c>
+      <c r="K25" t="n">
         <v>183</v>
       </c>
-      <c r="K25" t="n">
-        <v>182</v>
-      </c>
       <c r="L25" t="n">
-        <v>0.02328416900860986</v>
+        <v>0.02744292449286012</v>
       </c>
       <c r="M25" t="n">
-        <v>10.45668234835184</v>
+        <v>10.51890912909981</v>
       </c>
       <c r="N25" t="n">
-        <v>163.201901797746</v>
+        <v>163.3539443352927</v>
       </c>
       <c r="O25" t="n">
-        <v>12.77504997241678</v>
+        <v>12.78099934806714</v>
       </c>
       <c r="P25" t="n">
-        <v>331.3647780390708</v>
+        <v>331.1726862347517</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -24165,28 +24283,28 @@
         <v>0.064</v>
       </c>
       <c r="I26" t="n">
-        <v>0.1882843991399979</v>
+        <v>0.1989117839336298</v>
       </c>
       <c r="J26" t="n">
+        <v>184</v>
+      </c>
+      <c r="K26" t="n">
         <v>183</v>
       </c>
-      <c r="K26" t="n">
-        <v>182</v>
-      </c>
       <c r="L26" t="n">
-        <v>0.01122044346807527</v>
+        <v>0.01261597230606215</v>
       </c>
       <c r="M26" t="n">
-        <v>11.48707412974436</v>
+        <v>11.47103609612891</v>
       </c>
       <c r="N26" t="n">
-        <v>198.7537559175536</v>
+        <v>198.2727976047556</v>
       </c>
       <c r="O26" t="n">
-        <v>14.0980053879105</v>
+        <v>14.08093738373819</v>
       </c>
       <c r="P26" t="n">
-        <v>328.2461632263655</v>
+        <v>328.1492823037004</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -24243,28 +24361,28 @@
         <v>0.0554</v>
       </c>
       <c r="I27" t="n">
-        <v>0.3388180148804126</v>
+        <v>0.3446611640268548</v>
       </c>
       <c r="J27" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="K27" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="L27" t="n">
-        <v>0.02951905788213338</v>
+        <v>0.03084310657849942</v>
       </c>
       <c r="M27" t="n">
-        <v>12.42107794834952</v>
+        <v>12.3727336815557</v>
       </c>
       <c r="N27" t="n">
-        <v>239.1727667536382</v>
+        <v>238.0561251747902</v>
       </c>
       <c r="O27" t="n">
-        <v>15.46521150044959</v>
+        <v>15.42906754067757</v>
       </c>
       <c r="P27" t="n">
-        <v>321.2628705378914</v>
+        <v>321.2094061642479</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -24321,28 +24439,28 @@
         <v>0.0452</v>
       </c>
       <c r="I28" t="n">
-        <v>0.2487136036737208</v>
+        <v>0.2483079161621949</v>
       </c>
       <c r="J28" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="K28" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="L28" t="n">
-        <v>0.02035291764693337</v>
+        <v>0.02052400101721341</v>
       </c>
       <c r="M28" t="n">
-        <v>11.31546566557057</v>
+        <v>11.25630141613304</v>
       </c>
       <c r="N28" t="n">
-        <v>188.6845219607698</v>
+        <v>187.6599457624911</v>
       </c>
       <c r="O28" t="n">
-        <v>13.7362484674954</v>
+        <v>13.69890308610478</v>
       </c>
       <c r="P28" t="n">
-        <v>323.1001310067457</v>
+        <v>323.1038430168545</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -24399,28 +24517,28 @@
         <v>0.0527</v>
       </c>
       <c r="I29" t="n">
-        <v>0.2247404704977036</v>
+        <v>0.2197891519504727</v>
       </c>
       <c r="J29" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="K29" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="L29" t="n">
-        <v>0.02033121159645956</v>
+        <v>0.01967269780181669</v>
       </c>
       <c r="M29" t="n">
-        <v>10.57802172217215</v>
+        <v>10.5483128018925</v>
       </c>
       <c r="N29" t="n">
-        <v>154.2314013620332</v>
+        <v>153.5247393738642</v>
       </c>
       <c r="O29" t="n">
-        <v>12.41899357283162</v>
+        <v>12.39051005301494</v>
       </c>
       <c r="P29" t="n">
-        <v>322.3467135076777</v>
+        <v>322.3920176986546</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
@@ -24477,28 +24595,28 @@
         <v>0.0524</v>
       </c>
       <c r="I30" t="n">
-        <v>0.2278266625857173</v>
+        <v>0.2240531303180515</v>
       </c>
       <c r="J30" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="K30" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="L30" t="n">
-        <v>0.01978719893584557</v>
+        <v>0.01936383035927891</v>
       </c>
       <c r="M30" t="n">
-        <v>10.43243702729031</v>
+        <v>10.39708517882364</v>
       </c>
       <c r="N30" t="n">
-        <v>162.9443731451962</v>
+        <v>162.1352162780609</v>
       </c>
       <c r="O30" t="n">
-        <v>12.76496663314073</v>
+        <v>12.73323275048646</v>
       </c>
       <c r="P30" t="n">
-        <v>321.6330671331568</v>
+        <v>321.6675946685762</v>
       </c>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr">
@@ -24555,28 +24673,28 @@
         <v>0.0501</v>
       </c>
       <c r="I31" t="n">
-        <v>0.307681538976106</v>
+        <v>0.3058878596310931</v>
       </c>
       <c r="J31" t="n">
+        <v>184</v>
+      </c>
+      <c r="K31" t="n">
         <v>183</v>
       </c>
-      <c r="K31" t="n">
-        <v>182</v>
-      </c>
       <c r="L31" t="n">
-        <v>0.04136684416112424</v>
+        <v>0.04136560300930081</v>
       </c>
       <c r="M31" t="n">
-        <v>9.323860642028636</v>
+        <v>9.284067652261797</v>
       </c>
       <c r="N31" t="n">
-        <v>139.2255032202341</v>
+        <v>138.4820369436907</v>
       </c>
       <c r="O31" t="n">
-        <v>11.79938571368163</v>
+        <v>11.76783909406016</v>
       </c>
       <c r="P31" t="n">
-        <v>319.565073838509</v>
+        <v>319.5815084064319</v>
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
@@ -24633,28 +24751,28 @@
         <v>0.0491</v>
       </c>
       <c r="I32" t="n">
-        <v>0.2758172317187807</v>
+        <v>0.2737009409877997</v>
       </c>
       <c r="J32" t="n">
+        <v>184</v>
+      </c>
+      <c r="K32" t="n">
         <v>183</v>
       </c>
-      <c r="K32" t="n">
-        <v>182</v>
-      </c>
       <c r="L32" t="n">
-        <v>0.04407233457209181</v>
+        <v>0.04391045666558202</v>
       </c>
       <c r="M32" t="n">
-        <v>8.150758207758921</v>
+        <v>8.11856934213543</v>
       </c>
       <c r="N32" t="n">
-        <v>104.7171050525714</v>
+        <v>104.1690033678604</v>
       </c>
       <c r="O32" t="n">
-        <v>10.23313759570208</v>
+        <v>10.20632173546672</v>
       </c>
       <c r="P32" t="n">
-        <v>316.9663413875754</v>
+        <v>316.9857318788913</v>
       </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
@@ -24711,28 +24829,28 @@
         <v>0.0427</v>
       </c>
       <c r="I33" t="n">
-        <v>0.2512282745893271</v>
+        <v>0.2427996839085697</v>
       </c>
       <c r="J33" t="n">
+        <v>184</v>
+      </c>
+      <c r="K33" t="n">
         <v>183</v>
       </c>
-      <c r="K33" t="n">
-        <v>182</v>
-      </c>
       <c r="L33" t="n">
-        <v>0.03156104918198677</v>
+        <v>0.02978969414758958</v>
       </c>
       <c r="M33" t="n">
-        <v>8.714908277280117</v>
+        <v>8.707189779522242</v>
       </c>
       <c r="N33" t="n">
-        <v>122.9061770626048</v>
+        <v>122.6171977377956</v>
       </c>
       <c r="O33" t="n">
-        <v>11.08630583479478</v>
+        <v>11.07326499898723</v>
       </c>
       <c r="P33" t="n">
-        <v>315.1544012247672</v>
+        <v>315.2316280972419</v>
       </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
@@ -24770,7 +24888,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH184"/>
+  <dimension ref="A1:AH185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55978,17 +56096,17 @@
       </c>
       <c r="W183" t="inlineStr">
         <is>
-          <t>-34.43768164996651,173.00618665604676</t>
+          <t>-34.43769247254518,173.0062416170446</t>
         </is>
       </c>
       <c r="X183" t="inlineStr">
         <is>
-          <t>-34.4383839959941,173.0058351543449</t>
+          <t>-34.43840012932538,173.00592927441633</t>
         </is>
       </c>
       <c r="Y183" t="inlineStr">
         <is>
-          <t>-34.439144710534876,173.00578659711385</t>
+          <t>-34.439151257951956,173.00584055511436</t>
         </is>
       </c>
       <c r="Z183" t="inlineStr">
@@ -56045,12 +56163,12 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>-34.42299237808629,173.01242812008567</t>
+          <t>-34.423012128997996,173.0124736228156</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>-34.423636523464104,173.01198304709098</t>
+          <t>-34.4236587433611,173.01203423797742</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -56150,17 +56268,17 @@
       </c>
       <c r="W184" t="inlineStr">
         <is>
-          <t>-34.43768164996651,173.00618665604676</t>
+          <t>-34.43769247254518,173.0062416170446</t>
         </is>
       </c>
       <c r="X184" t="inlineStr">
         <is>
-          <t>-34.4383839959941,173.0058351543449</t>
+          <t>-34.43840012932538,173.00592927441633</t>
         </is>
       </c>
       <c r="Y184" t="inlineStr">
         <is>
-          <t>-34.439144710534876,173.00578659711385</t>
+          <t>-34.439151257951956,173.00584055511436</t>
         </is>
       </c>
       <c r="Z184" t="inlineStr">
@@ -56204,6 +56322,178 @@
         </is>
       </c>
       <c r="AH184" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:17:51+00:00</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>-34.42301869868309,173.01248875826232</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>-34.42365836675286,173.01203337033505</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>-34.42427673007655,173.01152891165648</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>-34.42500602106721,173.01128002397496</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>-34.42568212134511,173.01090860576923</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>-34.426376838143824,173.01058008945753</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>-34.42706037718469,173.0102258334078</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>-34.42774504116784,173.00987418124635</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>-34.42844667776613,173.00954723293066</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>-34.429148773429255,173.00924072814956</t>
+        </is>
+      </c>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>-34.429845607670266,173.00893047831204</t>
+        </is>
+      </c>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>-34.43054351762413,173.0086277573426</t>
+        </is>
+      </c>
+      <c r="N185" t="inlineStr">
+        <is>
+          <t>-34.431239078452414,173.0083163418203</t>
+        </is>
+      </c>
+      <c r="O185" t="inlineStr">
+        <is>
+          <t>-34.431941885773064,173.00803183653676</t>
+        </is>
+      </c>
+      <c r="P185" t="inlineStr">
+        <is>
+          <t>-34.43264109690121,173.00772822512963</t>
+        </is>
+      </c>
+      <c r="Q185" t="inlineStr">
+        <is>
+          <t>-34.4333532641383,173.00744887684377</t>
+        </is>
+      </c>
+      <c r="R185" t="inlineStr">
+        <is>
+          <t>-34.43406574664052,173.00716519749798</t>
+        </is>
+      </c>
+      <c r="S185" t="inlineStr">
+        <is>
+          <t>-34.434796162939946,173.00700617059823</t>
+        </is>
+      </c>
+      <c r="T185" t="inlineStr">
+        <is>
+          <t>-34.435515333651544,173.0067900669868</t>
+        </is>
+      </c>
+      <c r="U185" t="inlineStr">
+        <is>
+          <t>-34.43623328867957,173.00656782126936</t>
+        </is>
+      </c>
+      <c r="V185" t="inlineStr">
+        <is>
+          <t>-34.43697073469777,173.00644458900155</t>
+        </is>
+      </c>
+      <c r="W185" t="inlineStr">
+        <is>
+          <t>-34.437692430839725,173.00624140524883</t>
+        </is>
+      </c>
+      <c r="X185" t="inlineStr">
+        <is>
+          <t>-34.438405135576524,173.00595848042545</t>
+        </is>
+      </c>
+      <c r="Y185" t="inlineStr">
+        <is>
+          <t>-34.43915793603149,173.00589559012954</t>
+        </is>
+      </c>
+      <c r="Z185" t="inlineStr">
+        <is>
+          <t>-34.43989236653427,173.00573340091967</t>
+        </is>
+      </c>
+      <c r="AA185" t="inlineStr">
+        <is>
+          <t>-34.4406200628217,173.00554489029713</t>
+        </is>
+      </c>
+      <c r="AB185" t="inlineStr">
+        <is>
+          <t>-34.441348788226584,173.00536708185885</t>
+        </is>
+      </c>
+      <c r="AC185" t="inlineStr">
+        <is>
+          <t>-34.44207839631469,173.00519846222085</t>
+        </is>
+      </c>
+      <c r="AD185" t="inlineStr">
+        <is>
+          <t>-34.442814777379425,173.00509990279926</t>
+        </is>
+      </c>
+      <c r="AE185" t="inlineStr">
+        <is>
+          <t>-34.44355927811701,173.00501646430226</t>
+        </is>
+      </c>
+      <c r="AF185" t="inlineStr">
+        <is>
+          <t>-34.4443039111596,173.00490401471552</t>
+        </is>
+      </c>
+      <c r="AG185" t="inlineStr">
+        <is>
+          <t>-34.44504018308114,173.00474870176419</t>
+        </is>
+      </c>
+      <c r="AH185" t="inlineStr">
         <is>
           <t>L8</t>
         </is>

--- a/data/nzd0003/nzd0003.xlsx
+++ b/data/nzd0003/nzd0003.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH185"/>
+  <dimension ref="A1:AH187"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20121,7 +20121,7 @@
         <v>337.43</v>
       </c>
       <c r="Y183" t="n">
-        <v>343.98</v>
+        <v>338.97</v>
       </c>
       <c r="Z183" t="n">
         <v>337.43</v>
@@ -20166,7 +20166,7 @@
         <v>310.99</v>
       </c>
       <c r="D184" t="n">
-        <v>310.12</v>
+        <v>315.9</v>
       </c>
       <c r="E184" t="n">
         <v>317.97</v>
@@ -20229,7 +20229,7 @@
         <v>337.43</v>
       </c>
       <c r="Y184" t="n">
-        <v>343.98</v>
+        <v>338.97</v>
       </c>
       <c r="Z184" t="n">
         <v>337.43</v>
@@ -20274,7 +20274,7 @@
         <v>310.9</v>
       </c>
       <c r="D185" t="n">
-        <v>301.87</v>
+        <v>311.17</v>
       </c>
       <c r="E185" t="n">
         <v>319.35</v>
@@ -20337,7 +20337,7 @@
         <v>340.17</v>
       </c>
       <c r="Y185" t="n">
-        <v>349.09</v>
+        <v>333.83</v>
       </c>
       <c r="Z185" t="n">
         <v>343.81</v>
@@ -20364,6 +20364,222 @@
         <v>313.32</v>
       </c>
       <c r="AH185" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:18:00+00:00</t>
+        </is>
+      </c>
+      <c r="B186" t="n">
+        <v>314.63</v>
+      </c>
+      <c r="C186" t="n">
+        <v>310.49</v>
+      </c>
+      <c r="D186" t="n">
+        <v>307.82</v>
+      </c>
+      <c r="E186" t="n">
+        <v>317</v>
+      </c>
+      <c r="F186" t="n">
+        <v>320.77</v>
+      </c>
+      <c r="G186" t="n">
+        <v>330.82</v>
+      </c>
+      <c r="H186" t="n">
+        <v>338.21</v>
+      </c>
+      <c r="I186" t="n">
+        <v>346.16</v>
+      </c>
+      <c r="J186" t="n">
+        <v>355.39</v>
+      </c>
+      <c r="K186" t="n">
+        <v>354.65</v>
+      </c>
+      <c r="L186" t="n">
+        <v>352.09</v>
+      </c>
+      <c r="M186" t="n">
+        <v>350.28</v>
+      </c>
+      <c r="N186" t="n">
+        <v>345.28</v>
+      </c>
+      <c r="O186" t="n">
+        <v>344.96</v>
+      </c>
+      <c r="P186" t="n">
+        <v>342.87</v>
+      </c>
+      <c r="Q186" t="n">
+        <v>344.1</v>
+      </c>
+      <c r="R186" t="n">
+        <v>336.11</v>
+      </c>
+      <c r="S186" t="n">
+        <v>336.82</v>
+      </c>
+      <c r="T186" t="n">
+        <v>337.06</v>
+      </c>
+      <c r="U186" t="n">
+        <v>339.27</v>
+      </c>
+      <c r="V186" t="n">
+        <v>343.88</v>
+      </c>
+      <c r="W186" t="n">
+        <v>342.03</v>
+      </c>
+      <c r="X186" t="n">
+        <v>341.93</v>
+      </c>
+      <c r="Y186" t="n">
+        <v>327.43</v>
+      </c>
+      <c r="Z186" t="n">
+        <v>340.95</v>
+      </c>
+      <c r="AA186" t="n">
+        <v>332.18</v>
+      </c>
+      <c r="AB186" t="n">
+        <v>325.61</v>
+      </c>
+      <c r="AC186" t="n">
+        <v>317.91</v>
+      </c>
+      <c r="AD186" t="n">
+        <v>322.69</v>
+      </c>
+      <c r="AE186" t="n">
+        <v>327.75</v>
+      </c>
+      <c r="AF186" t="n">
+        <v>322.82</v>
+      </c>
+      <c r="AG186" t="n">
+        <v>314.9</v>
+      </c>
+      <c r="AH186" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:17:40+00:00</t>
+        </is>
+      </c>
+      <c r="B187" t="n">
+        <v>316.37</v>
+      </c>
+      <c r="C187" t="n">
+        <v>312.21</v>
+      </c>
+      <c r="D187" t="n">
+        <v>314.1</v>
+      </c>
+      <c r="E187" t="n">
+        <v>321.63</v>
+      </c>
+      <c r="F187" t="n">
+        <v>322.77</v>
+      </c>
+      <c r="G187" t="n">
+        <v>332.83</v>
+      </c>
+      <c r="H187" t="n">
+        <v>340.1</v>
+      </c>
+      <c r="I187" t="n">
+        <v>345.88</v>
+      </c>
+      <c r="J187" t="n">
+        <v>355.21</v>
+      </c>
+      <c r="K187" t="n">
+        <v>356.53</v>
+      </c>
+      <c r="L187" t="n">
+        <v>352.9</v>
+      </c>
+      <c r="M187" t="n">
+        <v>351.01</v>
+      </c>
+      <c r="N187" t="n">
+        <v>346.88</v>
+      </c>
+      <c r="O187" t="n">
+        <v>346.58</v>
+      </c>
+      <c r="P187" t="n">
+        <v>344.94</v>
+      </c>
+      <c r="Q187" t="n">
+        <v>344.98</v>
+      </c>
+      <c r="R187" t="n">
+        <v>339.14</v>
+      </c>
+      <c r="S187" t="n">
+        <v>338.57</v>
+      </c>
+      <c r="T187" t="n">
+        <v>338.73</v>
+      </c>
+      <c r="U187" t="n">
+        <v>340.24</v>
+      </c>
+      <c r="V187" t="n">
+        <v>343.89</v>
+      </c>
+      <c r="W187" t="n">
+        <v>343.61</v>
+      </c>
+      <c r="X187" t="n">
+        <v>344.19</v>
+      </c>
+      <c r="Y187" t="n">
+        <v>334.39</v>
+      </c>
+      <c r="Z187" t="n">
+        <v>341.13</v>
+      </c>
+      <c r="AA187" t="n">
+        <v>334.31</v>
+      </c>
+      <c r="AB187" t="n">
+        <v>327.33</v>
+      </c>
+      <c r="AC187" t="n">
+        <v>320.93</v>
+      </c>
+      <c r="AD187" t="n">
+        <v>322.69</v>
+      </c>
+      <c r="AE187" t="n">
+        <v>327.75</v>
+      </c>
+      <c r="AF187" t="n">
+        <v>322.82</v>
+      </c>
+      <c r="AG187" t="n">
+        <v>314.9</v>
+      </c>
+      <c r="AH187" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -20380,7 +20596,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B186"/>
+  <dimension ref="A1:B188"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22243,6 +22459,26 @@
       </c>
       <c r="B186" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B187" t="n">
+        <v>-0.64</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B188" t="n">
+        <v>0.9</v>
       </c>
     </row>
   </sheetData>
@@ -22411,28 +22647,28 @@
         <v>0.0366</v>
       </c>
       <c r="I2" t="n">
-        <v>1.104244000223428</v>
+        <v>1.062658144515554</v>
       </c>
       <c r="J2" t="n">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="K2" t="n">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2534870662715749</v>
+        <v>0.239634093956088</v>
       </c>
       <c r="M2" t="n">
-        <v>12.36105844632712</v>
+        <v>12.41620132588377</v>
       </c>
       <c r="N2" t="n">
-        <v>228.0978683487552</v>
+        <v>230.315057185448</v>
       </c>
       <c r="O2" t="n">
-        <v>15.10290926771247</v>
+        <v>15.1761344612338</v>
       </c>
       <c r="P2" t="n">
-        <v>307.3595062549546</v>
+        <v>307.7481211609723</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -22489,28 +22725,28 @@
         <v>0.0328</v>
       </c>
       <c r="I3" t="n">
-        <v>1.102151338176627</v>
+        <v>1.060250135607704</v>
       </c>
       <c r="J3" t="n">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="K3" t="n">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2521577302084</v>
+        <v>0.2382666716724522</v>
       </c>
       <c r="M3" t="n">
-        <v>11.97435582236456</v>
+        <v>12.0672663941008</v>
       </c>
       <c r="N3" t="n">
-        <v>231.0121879669879</v>
+        <v>233.2447565446521</v>
       </c>
       <c r="O3" t="n">
-        <v>15.19908510295892</v>
+        <v>15.27235268531513</v>
       </c>
       <c r="P3" t="n">
-        <v>303.3470134323667</v>
+        <v>303.7344159174266</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -22567,28 +22803,28 @@
         <v>0.0287</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4276526411212234</v>
+        <v>0.4096054217789016</v>
       </c>
       <c r="J4" t="n">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="K4" t="n">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03896564248905365</v>
+        <v>0.03666975799624683</v>
       </c>
       <c r="M4" t="n">
-        <v>13.3486544535513</v>
+        <v>13.30136996120907</v>
       </c>
       <c r="N4" t="n">
-        <v>283.348759839003</v>
+        <v>280.2691080294468</v>
       </c>
       <c r="O4" t="n">
-        <v>16.83296645986687</v>
+        <v>16.74123973991911</v>
       </c>
       <c r="P4" t="n">
-        <v>316.2440837404448</v>
+        <v>316.414071289035</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -22645,28 +22881,28 @@
         <v>0.035</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9243162132903535</v>
+        <v>0.8966155105363675</v>
       </c>
       <c r="J5" t="n">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="K5" t="n">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="L5" t="n">
-        <v>0.187850729894243</v>
+        <v>0.1809607466579812</v>
       </c>
       <c r="M5" t="n">
-        <v>12.58695545489359</v>
+        <v>12.5914639823446</v>
       </c>
       <c r="N5" t="n">
-        <v>234.4728846342299</v>
+        <v>233.9431506817787</v>
       </c>
       <c r="O5" t="n">
-        <v>15.31250745744243</v>
+        <v>15.2952002498097</v>
       </c>
       <c r="P5" t="n">
-        <v>308.6525044392894</v>
+        <v>308.9081334731071</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -22723,28 +22959,28 @@
         <v>0.0321</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7194478386200682</v>
+        <v>0.6912455626494605</v>
       </c>
       <c r="J6" t="n">
+        <v>186</v>
+      </c>
+      <c r="K6" t="n">
         <v>184</v>
       </c>
-      <c r="K6" t="n">
-        <v>182</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.1320702325541319</v>
+        <v>0.124583474840789</v>
       </c>
       <c r="M6" t="n">
-        <v>11.78395976040824</v>
+        <v>11.79424750842569</v>
       </c>
       <c r="N6" t="n">
-        <v>216.1643944156329</v>
+        <v>216.0041268042589</v>
       </c>
       <c r="O6" t="n">
-        <v>14.70253020454755</v>
+        <v>14.69707885276047</v>
       </c>
       <c r="P6" t="n">
-        <v>317.1931428037089</v>
+        <v>317.4537294474999</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -22801,28 +23037,28 @@
         <v>0.034</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4331670204361249</v>
+        <v>0.4236223245914422</v>
       </c>
       <c r="J7" t="n">
+        <v>186</v>
+      </c>
+      <c r="K7" t="n">
         <v>184</v>
       </c>
-      <c r="K7" t="n">
-        <v>182</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.05624021174356153</v>
+        <v>0.05504954952672314</v>
       </c>
       <c r="M7" t="n">
-        <v>11.25345444379944</v>
+        <v>11.17322220932808</v>
       </c>
       <c r="N7" t="n">
-        <v>200.0926723498357</v>
+        <v>198.1782458920385</v>
       </c>
       <c r="O7" t="n">
-        <v>14.14541170662189</v>
+        <v>14.07757954664219</v>
       </c>
       <c r="P7" t="n">
-        <v>325.2672853580007</v>
+        <v>325.3554707102288</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -22879,28 +23115,28 @@
         <v>0.0439</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4613375903307176</v>
+        <v>0.456075252834452</v>
       </c>
       <c r="J8" t="n">
+        <v>186</v>
+      </c>
+      <c r="K8" t="n">
         <v>184</v>
       </c>
-      <c r="K8" t="n">
-        <v>182</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.0893979837691713</v>
+        <v>0.08936920690811745</v>
       </c>
       <c r="M8" t="n">
-        <v>9.106030925238802</v>
+        <v>9.033997388029551</v>
       </c>
       <c r="N8" t="n">
-        <v>137.7667661905488</v>
+        <v>136.3548149306396</v>
       </c>
       <c r="O8" t="n">
-        <v>11.73740883630407</v>
+        <v>11.677106445119</v>
       </c>
       <c r="P8" t="n">
-        <v>329.6751674517044</v>
+        <v>329.7237832452196</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -22957,28 +23193,28 @@
         <v>0.0436</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4668824961708092</v>
+        <v>0.4613912893770403</v>
       </c>
       <c r="J9" t="n">
+        <v>186</v>
+      </c>
+      <c r="K9" t="n">
         <v>184</v>
       </c>
-      <c r="K9" t="n">
-        <v>182</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.1082450842525874</v>
+        <v>0.1081314962544289</v>
       </c>
       <c r="M9" t="n">
-        <v>8.257834120689594</v>
+        <v>8.192824608609127</v>
       </c>
       <c r="N9" t="n">
-        <v>114.1191185693457</v>
+        <v>112.9614951598921</v>
       </c>
       <c r="O9" t="n">
-        <v>10.6826550337145</v>
+        <v>10.62833454309245</v>
       </c>
       <c r="P9" t="n">
-        <v>336.5074702977295</v>
+        <v>336.5582120470961</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -23035,28 +23271,28 @@
         <v>0.0433</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5584254055258275</v>
+        <v>0.5556325456985945</v>
       </c>
       <c r="J10" t="n">
+        <v>186</v>
+      </c>
+      <c r="K10" t="n">
         <v>184</v>
       </c>
-      <c r="K10" t="n">
-        <v>182</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.1202214277821697</v>
+        <v>0.1216075949152322</v>
       </c>
       <c r="M10" t="n">
-        <v>8.954619721144416</v>
+        <v>8.871642949713744</v>
       </c>
       <c r="N10" t="n">
-        <v>145.0199430549475</v>
+        <v>143.4650983043738</v>
       </c>
       <c r="O10" t="n">
-        <v>12.04242264060465</v>
+        <v>11.97769169349311</v>
       </c>
       <c r="P10" t="n">
-        <v>341.9968834040358</v>
+        <v>342.0226911805722</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -23113,28 +23349,28 @@
         <v>0.0418</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5834001833674057</v>
+        <v>0.5892596635807974</v>
       </c>
       <c r="J11" t="n">
+        <v>186</v>
+      </c>
+      <c r="K11" t="n">
         <v>184</v>
       </c>
-      <c r="K11" t="n">
-        <v>182</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.1337712254397809</v>
+        <v>0.1387682108315299</v>
       </c>
       <c r="M11" t="n">
-        <v>9.394261038777627</v>
+        <v>9.315262673237326</v>
       </c>
       <c r="N11" t="n">
-        <v>140.0583217817383</v>
+        <v>138.6393536427659</v>
       </c>
       <c r="O11" t="n">
-        <v>11.83462385467904</v>
+        <v>11.7745213763773</v>
       </c>
       <c r="P11" t="n">
-        <v>337.2079948724401</v>
+        <v>337.1538420903414</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -23191,28 +23427,28 @@
         <v>0.0421</v>
       </c>
       <c r="I12" t="n">
-        <v>0.6086882465263107</v>
+        <v>0.6164515828627344</v>
       </c>
       <c r="J12" t="n">
+        <v>186</v>
+      </c>
+      <c r="K12" t="n">
         <v>184</v>
       </c>
-      <c r="K12" t="n">
-        <v>182</v>
-      </c>
       <c r="L12" t="n">
-        <v>0.1383995449000794</v>
+        <v>0.1441511677388536</v>
       </c>
       <c r="M12" t="n">
-        <v>9.548320763915124</v>
+        <v>9.478985175242189</v>
       </c>
       <c r="N12" t="n">
-        <v>146.5773900306743</v>
+        <v>145.1509480480007</v>
       </c>
       <c r="O12" t="n">
-        <v>12.10691496751647</v>
+        <v>12.04786072495863</v>
       </c>
       <c r="P12" t="n">
-        <v>332.4726345604259</v>
+        <v>332.4008950573776</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -23269,28 +23505,28 @@
         <v>0.0429</v>
       </c>
       <c r="I13" t="n">
-        <v>0.6452019569636704</v>
+        <v>0.6584802311972421</v>
       </c>
       <c r="J13" t="n">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="K13" t="n">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2033156887358171</v>
+        <v>0.2130710410444497</v>
       </c>
       <c r="M13" t="n">
-        <v>8.12317452378101</v>
+        <v>8.097427566537691</v>
       </c>
       <c r="N13" t="n">
-        <v>104.5923250073248</v>
+        <v>103.9512904817101</v>
       </c>
       <c r="O13" t="n">
-        <v>10.2270389168774</v>
+        <v>10.19565056686968</v>
       </c>
       <c r="P13" t="n">
-        <v>326.7889725420501</v>
+        <v>326.6674269010856</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -23347,28 +23583,28 @@
         <v>0.0448</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5875575703634135</v>
+        <v>0.5954771941476352</v>
       </c>
       <c r="J14" t="n">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="K14" t="n">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1805494769798326</v>
+        <v>0.1877800783051511</v>
       </c>
       <c r="M14" t="n">
-        <v>7.991721718007088</v>
+        <v>7.944554685581096</v>
       </c>
       <c r="N14" t="n">
-        <v>100.466308956171</v>
+        <v>99.56064265453195</v>
       </c>
       <c r="O14" t="n">
-        <v>10.0232883304917</v>
+        <v>9.978007950213907</v>
       </c>
       <c r="P14" t="n">
-        <v>326.4985906462818</v>
+        <v>326.4260907320088</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -23425,28 +23661,28 @@
         <v>0.0419</v>
       </c>
       <c r="I15" t="n">
-        <v>0.637448779638521</v>
+        <v>0.6447009496328679</v>
       </c>
       <c r="J15" t="n">
+        <v>186</v>
+      </c>
+      <c r="K15" t="n">
         <v>184</v>
       </c>
-      <c r="K15" t="n">
-        <v>182</v>
-      </c>
       <c r="L15" t="n">
-        <v>0.1913344270832786</v>
+        <v>0.1982878115521489</v>
       </c>
       <c r="M15" t="n">
-        <v>8.248282685816301</v>
+        <v>8.192916045564473</v>
       </c>
       <c r="N15" t="n">
-        <v>110.2735987756204</v>
+        <v>109.2281606726697</v>
       </c>
       <c r="O15" t="n">
-        <v>10.50112369109232</v>
+        <v>10.45122771126291</v>
       </c>
       <c r="P15" t="n">
-        <v>325.2244371240849</v>
+        <v>325.1579549414159</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -23503,28 +23739,28 @@
         <v>0.0442</v>
       </c>
       <c r="I16" t="n">
-        <v>0.6906070810752005</v>
+        <v>0.6954349998787357</v>
       </c>
       <c r="J16" t="n">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="K16" t="n">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2065112368710619</v>
+        <v>0.2125345098954571</v>
       </c>
       <c r="M16" t="n">
-        <v>8.869173210711953</v>
+        <v>8.792453300186757</v>
       </c>
       <c r="N16" t="n">
-        <v>117.0346499715438</v>
+        <v>115.8452655088818</v>
       </c>
       <c r="O16" t="n">
-        <v>10.81825540332376</v>
+        <v>10.76314384874986</v>
       </c>
       <c r="P16" t="n">
-        <v>323.1995930969046</v>
+        <v>323.1551744731497</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -23581,28 +23817,28 @@
         <v>0.0482</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6430729587460858</v>
+        <v>0.6489995740333796</v>
       </c>
       <c r="J17" t="n">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="K17" t="n">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1993802438986003</v>
+        <v>0.2059229397295121</v>
       </c>
       <c r="M17" t="n">
-        <v>8.451600790240596</v>
+        <v>8.384639790493061</v>
       </c>
       <c r="N17" t="n">
-        <v>106.0522748701008</v>
+        <v>105.0049742217254</v>
       </c>
       <c r="O17" t="n">
-        <v>10.29816852018361</v>
+        <v>10.24719348025231</v>
       </c>
       <c r="P17" t="n">
-        <v>324.5218261356599</v>
+        <v>324.4673075305541</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -23659,28 +23895,28 @@
         <v>0.0524</v>
       </c>
       <c r="I18" t="n">
-        <v>0.586176204191835</v>
+        <v>0.586306262577783</v>
       </c>
       <c r="J18" t="n">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="K18" t="n">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1294056250764849</v>
+        <v>0.1320609590624854</v>
       </c>
       <c r="M18" t="n">
-        <v>10.60321881264777</v>
+        <v>10.50473779211623</v>
       </c>
       <c r="N18" t="n">
-        <v>147.62991981466</v>
+        <v>146.0585455971497</v>
       </c>
       <c r="O18" t="n">
-        <v>12.15030533833039</v>
+        <v>12.0854683648235</v>
       </c>
       <c r="P18" t="n">
-        <v>322.0943158758403</v>
+        <v>322.0931042098098</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -23737,28 +23973,28 @@
         <v>0.05</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4163727810631477</v>
+        <v>0.4273001014267293</v>
       </c>
       <c r="J19" t="n">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="K19" t="n">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="L19" t="n">
-        <v>0.08273343011344847</v>
+        <v>0.08837862252412199</v>
       </c>
       <c r="M19" t="n">
-        <v>9.225415108833252</v>
+        <v>9.177233370540762</v>
       </c>
       <c r="N19" t="n">
-        <v>122.5851556212783</v>
+        <v>121.6042997003117</v>
       </c>
       <c r="O19" t="n">
-        <v>11.07181808111379</v>
+        <v>11.02743395810248</v>
       </c>
       <c r="P19" t="n">
-        <v>321.0821331612764</v>
+        <v>320.9817530460171</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -23815,28 +24051,28 @@
         <v>0.0506</v>
       </c>
       <c r="I20" t="n">
-        <v>0.2871495079136117</v>
+        <v>0.3019190122478388</v>
       </c>
       <c r="J20" t="n">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="K20" t="n">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="L20" t="n">
-        <v>0.04197759729125827</v>
+        <v>0.04700331515228229</v>
       </c>
       <c r="M20" t="n">
-        <v>9.072975295508169</v>
+        <v>9.040392688161655</v>
       </c>
       <c r="N20" t="n">
-        <v>120.0142804552349</v>
+        <v>119.3327065228234</v>
       </c>
       <c r="O20" t="n">
-        <v>10.95510294133446</v>
+        <v>10.92395104908583</v>
       </c>
       <c r="P20" t="n">
-        <v>322.7124950014295</v>
+        <v>322.5768233721527</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -23893,28 +24129,28 @@
         <v>0.0544</v>
       </c>
       <c r="I21" t="n">
-        <v>0.4468484964682901</v>
+        <v>0.4607204938052216</v>
       </c>
       <c r="J21" t="n">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="K21" t="n">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="L21" t="n">
-        <v>0.09782182346873347</v>
+        <v>0.1050795611772632</v>
       </c>
       <c r="M21" t="n">
-        <v>8.854436446229755</v>
+        <v>8.818599800334166</v>
       </c>
       <c r="N21" t="n">
-        <v>117.6068122937955</v>
+        <v>116.8703560335585</v>
       </c>
       <c r="O21" t="n">
-        <v>10.84466745888483</v>
+        <v>10.81065937089679</v>
       </c>
       <c r="P21" t="n">
-        <v>320.8248805519115</v>
+        <v>320.6972782707353</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -23971,28 +24207,28 @@
         <v>0.0505</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2855619162800117</v>
+        <v>0.307400714362633</v>
       </c>
       <c r="J22" t="n">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="K22" t="n">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="L22" t="n">
-        <v>0.03284035612633662</v>
+        <v>0.03838987168952745</v>
       </c>
       <c r="M22" t="n">
-        <v>10.23139948238514</v>
+        <v>10.20954250364188</v>
       </c>
       <c r="N22" t="n">
-        <v>153.1614851357744</v>
+        <v>152.8297068136362</v>
       </c>
       <c r="O22" t="n">
-        <v>12.37584280506885</v>
+        <v>12.36243126628562</v>
       </c>
       <c r="P22" t="n">
-        <v>325.1006034579984</v>
+        <v>324.9000062892093</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -24049,28 +24285,28 @@
         <v>0.0567</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2953915111028976</v>
+        <v>0.3106134211395512</v>
       </c>
       <c r="J23" t="n">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="K23" t="n">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="L23" t="n">
-        <v>0.03547598303547694</v>
+        <v>0.03979363847429551</v>
       </c>
       <c r="M23" t="n">
-        <v>9.753380188705538</v>
+        <v>9.725110689592539</v>
       </c>
       <c r="N23" t="n">
-        <v>151.2980440312423</v>
+        <v>150.3166296664081</v>
       </c>
       <c r="O23" t="n">
-        <v>12.30032698879352</v>
+        <v>12.2603682516639</v>
       </c>
       <c r="P23" t="n">
-        <v>327.1910097890136</v>
+        <v>327.0511831572599</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -24127,28 +24363,28 @@
         <v>0.0536</v>
       </c>
       <c r="I24" t="n">
-        <v>0.4153953548055233</v>
+        <v>0.4208377753792323</v>
       </c>
       <c r="J24" t="n">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="K24" t="n">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="L24" t="n">
-        <v>0.07301725292812067</v>
+        <v>0.07636809085187202</v>
       </c>
       <c r="M24" t="n">
-        <v>9.469563687512535</v>
+        <v>9.394389971317077</v>
       </c>
       <c r="N24" t="n">
-        <v>139.7102010604394</v>
+        <v>138.3031569998057</v>
       </c>
       <c r="O24" t="n">
-        <v>11.81990698188608</v>
+        <v>11.7602362646252</v>
       </c>
       <c r="P24" t="n">
-        <v>329.2962138793602</v>
+        <v>329.2462119385331</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -24205,28 +24441,28 @@
         <v>0.0562</v>
       </c>
       <c r="I25" t="n">
-        <v>0.2686549224966987</v>
+        <v>0.2301251697681904</v>
       </c>
       <c r="J25" t="n">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="K25" t="n">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="L25" t="n">
-        <v>0.02744292449286012</v>
+        <v>0.02078766301243307</v>
       </c>
       <c r="M25" t="n">
-        <v>10.51890912909981</v>
+        <v>10.37533200561787</v>
       </c>
       <c r="N25" t="n">
-        <v>163.3539443352927</v>
+        <v>161.2733402340786</v>
       </c>
       <c r="O25" t="n">
-        <v>12.78099934806714</v>
+        <v>12.699344086766</v>
       </c>
       <c r="P25" t="n">
-        <v>331.1726862347517</v>
+        <v>331.5253368706214</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -24283,28 +24519,28 @@
         <v>0.064</v>
       </c>
       <c r="I26" t="n">
-        <v>0.1989117839336298</v>
+        <v>0.2138012141245922</v>
       </c>
       <c r="J26" t="n">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="K26" t="n">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="L26" t="n">
-        <v>0.01261597230606215</v>
+        <v>0.01483871319101315</v>
       </c>
       <c r="M26" t="n">
-        <v>11.47103609612891</v>
+        <v>11.41128335713632</v>
       </c>
       <c r="N26" t="n">
-        <v>198.2727976047556</v>
+        <v>196.7399025440221</v>
       </c>
       <c r="O26" t="n">
-        <v>14.08093738373819</v>
+        <v>14.026400199054</v>
       </c>
       <c r="P26" t="n">
-        <v>328.1492823037004</v>
+        <v>328.0130194189719</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -24361,28 +24597,28 @@
         <v>0.0554</v>
       </c>
       <c r="I27" t="n">
-        <v>0.3446611640268548</v>
+        <v>0.3503763985772579</v>
       </c>
       <c r="J27" t="n">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="K27" t="n">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="L27" t="n">
-        <v>0.03084310657849942</v>
+        <v>0.03254930200254158</v>
       </c>
       <c r="M27" t="n">
-        <v>12.3727336815557</v>
+        <v>12.25804840949255</v>
       </c>
       <c r="N27" t="n">
-        <v>238.0561251747902</v>
+        <v>235.5984982407948</v>
       </c>
       <c r="O27" t="n">
-        <v>15.42906754067757</v>
+        <v>15.34921816382824</v>
       </c>
       <c r="P27" t="n">
-        <v>321.2094061642479</v>
+        <v>321.1568989714627</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -24439,28 +24675,28 @@
         <v>0.0452</v>
       </c>
       <c r="I28" t="n">
-        <v>0.2483079161621949</v>
+        <v>0.2421252042856777</v>
       </c>
       <c r="J28" t="n">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="K28" t="n">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="L28" t="n">
-        <v>0.02052400101721341</v>
+        <v>0.0199706984863528</v>
       </c>
       <c r="M28" t="n">
-        <v>11.25630141613304</v>
+        <v>11.17023728085418</v>
       </c>
       <c r="N28" t="n">
-        <v>187.6599457624911</v>
+        <v>185.7554107573885</v>
       </c>
       <c r="O28" t="n">
-        <v>13.69890308610478</v>
+        <v>13.62921167043011</v>
       </c>
       <c r="P28" t="n">
-        <v>323.1038430168545</v>
+        <v>323.1606248045118</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -24517,28 +24753,28 @@
         <v>0.0527</v>
       </c>
       <c r="I29" t="n">
-        <v>0.2197891519504727</v>
+        <v>0.2027626434080579</v>
       </c>
       <c r="J29" t="n">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="K29" t="n">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="L29" t="n">
-        <v>0.01967269780181669</v>
+        <v>0.01708728850130514</v>
       </c>
       <c r="M29" t="n">
-        <v>10.5483128018925</v>
+        <v>10.53139977831955</v>
       </c>
       <c r="N29" t="n">
-        <v>153.5247393738642</v>
+        <v>152.6980022432462</v>
       </c>
       <c r="O29" t="n">
-        <v>12.39051005301494</v>
+        <v>12.35710331118285</v>
       </c>
       <c r="P29" t="n">
-        <v>322.3920176986546</v>
+        <v>322.5483970499984</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
@@ -24595,28 +24831,28 @@
         <v>0.0524</v>
       </c>
       <c r="I30" t="n">
-        <v>0.2240531303180515</v>
+        <v>0.2145582637080309</v>
       </c>
       <c r="J30" t="n">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="K30" t="n">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="L30" t="n">
-        <v>0.01936383035927891</v>
+        <v>0.01816723586647817</v>
       </c>
       <c r="M30" t="n">
-        <v>10.39708517882364</v>
+        <v>10.33892636442199</v>
       </c>
       <c r="N30" t="n">
-        <v>162.1352162780609</v>
+        <v>160.6404176931219</v>
       </c>
       <c r="O30" t="n">
-        <v>12.73323275048646</v>
+        <v>12.67440009204072</v>
       </c>
       <c r="P30" t="n">
-        <v>321.6675946685762</v>
+        <v>321.7548084392226</v>
       </c>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr">
@@ -24673,28 +24909,28 @@
         <v>0.0501</v>
       </c>
       <c r="I31" t="n">
-        <v>0.3058878596310931</v>
+        <v>0.3060745516623196</v>
       </c>
       <c r="J31" t="n">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="K31" t="n">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="L31" t="n">
-        <v>0.04136560300930081</v>
+        <v>0.04234046274998748</v>
       </c>
       <c r="M31" t="n">
-        <v>9.284067652261797</v>
+        <v>9.184564910487845</v>
       </c>
       <c r="N31" t="n">
-        <v>138.4820369436907</v>
+        <v>136.9850304281305</v>
       </c>
       <c r="O31" t="n">
-        <v>11.76783909406016</v>
+        <v>11.70406042483251</v>
       </c>
       <c r="P31" t="n">
-        <v>319.5815084064319</v>
+        <v>319.5797912099612</v>
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
@@ -24751,28 +24987,28 @@
         <v>0.0491</v>
       </c>
       <c r="I32" t="n">
-        <v>0.2737009409877997</v>
+        <v>0.2710018972741595</v>
       </c>
       <c r="J32" t="n">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="K32" t="n">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="L32" t="n">
-        <v>0.04391045666558202</v>
+        <v>0.04403974479452177</v>
       </c>
       <c r="M32" t="n">
-        <v>8.11856934213543</v>
+        <v>8.046290788620825</v>
       </c>
       <c r="N32" t="n">
-        <v>104.1690033678604</v>
+        <v>103.0630128884493</v>
       </c>
       <c r="O32" t="n">
-        <v>10.20632173546672</v>
+        <v>10.15199551262949</v>
       </c>
       <c r="P32" t="n">
-        <v>316.9857318788913</v>
+        <v>317.0105582527363</v>
       </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
@@ -24829,28 +25065,28 @@
         <v>0.0427</v>
       </c>
       <c r="I33" t="n">
-        <v>0.2427996839085697</v>
+        <v>0.2297034246183476</v>
       </c>
       <c r="J33" t="n">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="K33" t="n">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="L33" t="n">
-        <v>0.02978969414758958</v>
+        <v>0.02725035434077094</v>
       </c>
       <c r="M33" t="n">
-        <v>8.707189779522242</v>
+        <v>8.674649719647883</v>
       </c>
       <c r="N33" t="n">
-        <v>122.6171977377956</v>
+        <v>121.7662681688778</v>
       </c>
       <c r="O33" t="n">
-        <v>11.07326499898723</v>
+        <v>11.03477540183205</v>
       </c>
       <c r="P33" t="n">
-        <v>315.2316280972419</v>
+        <v>315.3520901337163</v>
       </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
@@ -24888,7 +25124,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH185"/>
+  <dimension ref="A1:AH187"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56106,7 +56342,7 @@
       </c>
       <c r="Y183" t="inlineStr">
         <is>
-          <t>-34.439151257951956,173.00584055511436</t>
+          <t>-34.439144710534876,173.00578659711385</t>
         </is>
       </c>
       <c r="Z183" t="inlineStr">
@@ -56173,7 +56409,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>-34.42431125270239,173.01160844601128</t>
+          <t>-34.42433543943234,173.0116641683012</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -56278,7 +56514,7 @@
       </c>
       <c r="Y184" t="inlineStr">
         <is>
-          <t>-34.439151257951956,173.00584055511436</t>
+          <t>-34.439144710534876,173.00578659711385</t>
         </is>
       </c>
       <c r="Z184" t="inlineStr">
@@ -56345,7 +56581,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>-34.42427673007655,173.01152891165648</t>
+          <t>-34.42431564648739,173.0116185685702</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -56450,7 +56686,7 @@
       </c>
       <c r="Y185" t="inlineStr">
         <is>
-          <t>-34.43915793603149,173.00589559012954</t>
+          <t>-34.43913799319995,173.00573123901432</t>
         </is>
       </c>
       <c r="Z185" t="inlineStr">
@@ -56494,6 +56730,350 @@
         </is>
       </c>
       <c r="AH185" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:18:00+00:00</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>-34.42301781993551,173.0124867337757</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>-34.423656651093,173.01202941774216</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>-34.42430162821798,173.01158627279065</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>-34.42499618732231,173.0112573685617</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>-34.42566810296886,173.01087630953361</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>-34.42636629294312,173.01055579479663</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>-34.42705334702473,173.01020963685204</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>-34.427742739618985,173.00986887876456</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>-34.42844294322893,173.00953685000826</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>-34.429145544070245,173.00922917827424</t>
+        </is>
+      </c>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>-34.429843850357486,173.0089239577803</t>
+        </is>
+      </c>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>-34.43054329447196,173.00862692933222</t>
+        </is>
+      </c>
+      <c r="N186" t="inlineStr">
+        <is>
+          <t>-34.43123383434152,173.00829688342964</t>
+        </is>
+      </c>
+      <c r="O186" t="inlineStr">
+        <is>
+          <t>-34.43193742267539,173.00801527607538</t>
+        </is>
+      </c>
+      <c r="P186" t="inlineStr">
+        <is>
+          <t>-34.432637559265515,173.0077147353193</t>
+        </is>
+      </c>
+      <c r="Q186" t="inlineStr">
+        <is>
+          <t>-34.43335582397532,173.00746021852848</t>
+        </is>
+      </c>
+      <c r="R186" t="inlineStr">
+        <is>
+          <t>-34.43406583004955,173.00716562107178</t>
+        </is>
+      </c>
+      <c r="S186" t="inlineStr">
+        <is>
+          <t>-34.43478807222903,173.00696508359295</t>
+        </is>
+      </c>
+      <c r="T186" t="inlineStr">
+        <is>
+          <t>-34.43550932814178,173.0067595691641</t>
+        </is>
+      </c>
+      <c r="U186" t="inlineStr">
+        <is>
+          <t>-34.43623468580209,173.00657491630778</t>
+        </is>
+      </c>
+      <c r="V186" t="inlineStr">
+        <is>
+          <t>-34.4369650419294,173.0064156791193</t>
+        </is>
+      </c>
+      <c r="W186" t="inlineStr">
+        <is>
+          <t>-34.43768192105258,173.006188032719</t>
+        </is>
+      </c>
+      <c r="X186" t="inlineStr">
+        <is>
+          <t>-34.43840835126699,173.00597724049155</t>
+        </is>
+      </c>
+      <c r="Y186" t="inlineStr">
+        <is>
+          <t>-34.439129629168136,173.00566231065372</t>
+        </is>
+      </c>
+      <c r="Z186" t="inlineStr">
+        <is>
+          <t>-34.43988937444743,173.0057024798506</t>
+        </is>
+      </c>
+      <c r="AA186" t="inlineStr">
+        <is>
+          <t>-34.4406160349595,173.00550326542805</t>
+        </is>
+      </c>
+      <c r="AB186" t="inlineStr">
+        <is>
+          <t>-34.44134499048346,173.0053278352192</t>
+        </is>
+      </c>
+      <c r="AC186" t="inlineStr">
+        <is>
+          <t>-34.442072757174834,173.005140186411</t>
+        </is>
+      </c>
+      <c r="AD186" t="inlineStr">
+        <is>
+          <t>-34.44281357421961,173.00508746907605</t>
+        </is>
+      </c>
+      <c r="AE186" t="inlineStr">
+        <is>
+          <t>-34.443560936766865,173.00503694030886</t>
+        </is>
+      </c>
+      <c r="AF186" t="inlineStr">
+        <is>
+          <t>-34.444304381780874,173.00491183175293</t>
+        </is>
+      </c>
+      <c r="AG186" t="inlineStr">
+        <is>
+          <t>-34.44504112896994,173.00476586326664</t>
+        </is>
+      </c>
+      <c r="AH186" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:17:40+00:00</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>-34.423025100985846,173.0125035080948</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>-34.423663848494456,173.01204599935255</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>-34.42432790723543,173.01164681533552</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>-34.42501556188803,173.01130200455123</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>-34.425676472149746,173.01089559086702</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>-34.42637470399646,173.0105751726804</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>-34.42706125595453,173.01022785797747</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>-34.427741567921295,173.00986617931943</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>-34.42844229686663,173.00953505296405</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>-34.42915096477939,173.00924856556549</t>
+        </is>
+      </c>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>-34.429846109759566,173.00893234132116</t>
+        </is>
+      </c>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>-34.43054533073531,173.00863448492714</t>
+        </is>
+      </c>
+      <c r="N187" t="inlineStr">
+        <is>
+          <t>-34.43123829741482,173.00831344376198</t>
+        </is>
+      </c>
+      <c r="O187" t="inlineStr">
+        <is>
+          <t>-34.43194194156177,173.0080320435425</t>
+        </is>
+      </c>
+      <c r="P187" t="inlineStr">
+        <is>
+          <t>-34.43264319226935,173.00773621524857</t>
+        </is>
+      </c>
+      <c r="Q187" t="inlineStr">
+        <is>
+          <t>-34.43335790976768,173.0074694599017</t>
+        </is>
+      </c>
+      <c r="R187" t="inlineStr">
+        <is>
+          <t>-34.4340721482794,173.00719770679075</t>
+        </is>
+      </c>
+      <c r="S187" t="inlineStr">
+        <is>
+          <t>-34.434791721391605,173.0069836151021</t>
+        </is>
+      </c>
+      <c r="T187" t="inlineStr">
+        <is>
+          <t>-34.435512810504264,173.00677725366495</t>
+        </is>
+      </c>
+      <c r="U187" t="inlineStr">
+        <is>
+          <t>-34.43623670850113,173.00658518822948</t>
+        </is>
+      </c>
+      <c r="V187" t="inlineStr">
+        <is>
+          <t>-34.436965062782036,173.00641578501626</t>
+        </is>
+      </c>
+      <c r="W187" t="inlineStr">
+        <is>
+          <t>-34.437685215789955,173.00620476458207</t>
+        </is>
+      </c>
+      <c r="X187" t="inlineStr">
+        <is>
+          <t>-34.43841248050168,173.00600133012398</t>
+        </is>
+      </c>
+      <c r="Y187" t="inlineStr">
+        <is>
+          <t>-34.43913872505089,173.00573727024653</t>
+        </is>
+      </c>
+      <c r="Z187" t="inlineStr">
+        <is>
+          <t>-34.43988956276081,173.00570442593184</t>
+        </is>
+      </c>
+      <c r="AA187" t="inlineStr">
+        <is>
+          <t>-34.440618263362936,173.0055262942512</t>
+        </is>
+      </c>
+      <c r="AB187" t="inlineStr">
+        <is>
+          <t>-34.441346789966616,173.00534643142268</t>
+        </is>
+      </c>
+      <c r="AC187" t="inlineStr">
+        <is>
+          <t>-34.44207591677053,173.00517283816248</t>
+        </is>
+      </c>
+      <c r="AD187" t="inlineStr">
+        <is>
+          <t>-34.44281357421961,173.00508746907605</t>
+        </is>
+      </c>
+      <c r="AE187" t="inlineStr">
+        <is>
+          <t>-34.443560936766865,173.00503694030886</t>
+        </is>
+      </c>
+      <c r="AF187" t="inlineStr">
+        <is>
+          <t>-34.444304381780874,173.00491183175293</t>
+        </is>
+      </c>
+      <c r="AG187" t="inlineStr">
+        <is>
+          <t>-34.44504112896994,173.00476586326664</t>
+        </is>
+      </c>
+      <c r="AH187" t="inlineStr">
         <is>
           <t>L8</t>
         </is>

--- a/data/nzd0003/nzd0003.xlsx
+++ b/data/nzd0003/nzd0003.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH187"/>
+  <dimension ref="A1:AH189"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20585,6 +20585,222 @@
         </is>
       </c>
     </row>
+    <row r="188">
+      <c r="A188" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-24 22:17:36+00:00</t>
+        </is>
+      </c>
+      <c r="B188" t="n">
+        <v>326.36</v>
+      </c>
+      <c r="C188" t="n">
+        <v>315.93</v>
+      </c>
+      <c r="D188" t="n">
+        <v>332.56</v>
+      </c>
+      <c r="E188" t="n">
+        <v>328.29</v>
+      </c>
+      <c r="F188" t="n">
+        <v>333.26</v>
+      </c>
+      <c r="G188" t="n">
+        <v>342.27</v>
+      </c>
+      <c r="H188" t="n">
+        <v>347.57</v>
+      </c>
+      <c r="I188" t="n">
+        <v>352.73</v>
+      </c>
+      <c r="J188" t="n">
+        <v>363.06</v>
+      </c>
+      <c r="K188" t="n">
+        <v>362.43</v>
+      </c>
+      <c r="L188" t="n">
+        <v>357.59</v>
+      </c>
+      <c r="M188" t="n">
+        <v>359.49</v>
+      </c>
+      <c r="N188" t="n">
+        <v>353.91</v>
+      </c>
+      <c r="O188" t="n">
+        <v>356.76</v>
+      </c>
+      <c r="P188" t="n">
+        <v>355.38</v>
+      </c>
+      <c r="Q188" t="n">
+        <v>355.15</v>
+      </c>
+      <c r="R188" t="n">
+        <v>347.91</v>
+      </c>
+      <c r="S188" t="n">
+        <v>346.97</v>
+      </c>
+      <c r="T188" t="n">
+        <v>345.81</v>
+      </c>
+      <c r="U188" t="n">
+        <v>347.9</v>
+      </c>
+      <c r="V188" t="n">
+        <v>353.15</v>
+      </c>
+      <c r="W188" t="n">
+        <v>353.55</v>
+      </c>
+      <c r="X188" t="n">
+        <v>355.94</v>
+      </c>
+      <c r="Y188" t="n">
+        <v>347.78</v>
+      </c>
+      <c r="Z188" t="n">
+        <v>346.83</v>
+      </c>
+      <c r="AA188" t="n">
+        <v>339.27</v>
+      </c>
+      <c r="AB188" t="n">
+        <v>333.29</v>
+      </c>
+      <c r="AC188" t="n">
+        <v>329.09</v>
+      </c>
+      <c r="AD188" t="n">
+        <v>337.09</v>
+      </c>
+      <c r="AE188" t="n">
+        <v>342.46</v>
+      </c>
+      <c r="AF188" t="n">
+        <v>334.54</v>
+      </c>
+      <c r="AG188" t="n">
+        <v>327.84</v>
+      </c>
+      <c r="AH188" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-20 22:17:31+00:00</t>
+        </is>
+      </c>
+      <c r="B189" t="n">
+        <v>319.82</v>
+      </c>
+      <c r="C189" t="n">
+        <v>310.58</v>
+      </c>
+      <c r="D189" t="n">
+        <v>332.56</v>
+      </c>
+      <c r="E189" t="n">
+        <v>322.38</v>
+      </c>
+      <c r="F189" t="n">
+        <v>333.26</v>
+      </c>
+      <c r="G189" t="n">
+        <v>335.08</v>
+      </c>
+      <c r="H189" t="n">
+        <v>341.89</v>
+      </c>
+      <c r="I189" t="n">
+        <v>348.12</v>
+      </c>
+      <c r="J189" t="n">
+        <v>358.89</v>
+      </c>
+      <c r="K189" t="n">
+        <v>357.24</v>
+      </c>
+      <c r="L189" t="n">
+        <v>350.55</v>
+      </c>
+      <c r="M189" t="n">
+        <v>350.76</v>
+      </c>
+      <c r="N189" t="n">
+        <v>347.44</v>
+      </c>
+      <c r="O189" t="n">
+        <v>350.49</v>
+      </c>
+      <c r="P189" t="n">
+        <v>355.01</v>
+      </c>
+      <c r="Q189" t="n">
+        <v>353.7</v>
+      </c>
+      <c r="R189" t="n">
+        <v>350.64</v>
+      </c>
+      <c r="S189" t="n">
+        <v>346.94</v>
+      </c>
+      <c r="T189" t="n">
+        <v>346.09</v>
+      </c>
+      <c r="U189" t="n">
+        <v>346.87</v>
+      </c>
+      <c r="V189" t="n">
+        <v>349.99</v>
+      </c>
+      <c r="W189" t="n">
+        <v>349.97</v>
+      </c>
+      <c r="X189" t="n">
+        <v>351.75</v>
+      </c>
+      <c r="Y189" t="n">
+        <v>347.78</v>
+      </c>
+      <c r="Z189" t="n">
+        <v>344.8</v>
+      </c>
+      <c r="AA189" t="n">
+        <v>337.94</v>
+      </c>
+      <c r="AB189" t="n">
+        <v>333.18</v>
+      </c>
+      <c r="AC189" t="n">
+        <v>328.17</v>
+      </c>
+      <c r="AD189" t="n">
+        <v>342.02</v>
+      </c>
+      <c r="AE189" t="n">
+        <v>342.46</v>
+      </c>
+      <c r="AF189" t="n">
+        <v>334.54</v>
+      </c>
+      <c r="AG189" t="n">
+        <v>327.84</v>
+      </c>
+      <c r="AH189" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -20596,7 +20812,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B188"/>
+  <dimension ref="A1:B190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22479,6 +22695,26 @@
       </c>
       <c r="B188" t="n">
         <v>0.9</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>2026-02-24 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B189" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>2026-03-20 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B190" t="n">
+        <v>0.89</v>
       </c>
     </row>
   </sheetData>
@@ -22647,28 +22883,28 @@
         <v>0.0366</v>
       </c>
       <c r="I2" t="n">
-        <v>1.062658144515554</v>
+        <v>1.037596117169578</v>
       </c>
       <c r="J2" t="n">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="K2" t="n">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="L2" t="n">
-        <v>0.239634093956088</v>
+        <v>0.2336283897868845</v>
       </c>
       <c r="M2" t="n">
-        <v>12.41620132588377</v>
+        <v>12.39877350970995</v>
       </c>
       <c r="N2" t="n">
-        <v>230.315057185448</v>
+        <v>229.6627129642806</v>
       </c>
       <c r="O2" t="n">
-        <v>15.1761344612338</v>
+        <v>15.15462678406435</v>
       </c>
       <c r="P2" t="n">
-        <v>307.7481211609723</v>
+        <v>307.9845735501736</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -22725,28 +22961,28 @@
         <v>0.0328</v>
       </c>
       <c r="I3" t="n">
-        <v>1.060250135607704</v>
+        <v>1.023876366671698</v>
       </c>
       <c r="J3" t="n">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="K3" t="n">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2382666716724522</v>
+        <v>0.2269869786875021</v>
       </c>
       <c r="M3" t="n">
-        <v>12.0672663941008</v>
+        <v>12.13031314141661</v>
       </c>
       <c r="N3" t="n">
-        <v>233.2447565446521</v>
+        <v>234.4646317236225</v>
       </c>
       <c r="O3" t="n">
-        <v>15.27235268531513</v>
+        <v>15.31223797240699</v>
       </c>
       <c r="P3" t="n">
-        <v>303.7344159174266</v>
+        <v>304.0738963588247</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -22803,28 +23039,28 @@
         <v>0.0287</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4096054217789016</v>
+        <v>0.4198445762638579</v>
       </c>
       <c r="J4" t="n">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="K4" t="n">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03666975799624683</v>
+        <v>0.03927080105737835</v>
       </c>
       <c r="M4" t="n">
-        <v>13.30136996120907</v>
+        <v>13.21126954386645</v>
       </c>
       <c r="N4" t="n">
-        <v>280.2691080294468</v>
+        <v>277.5139508970735</v>
       </c>
       <c r="O4" t="n">
-        <v>16.74123973991911</v>
+        <v>16.65874998002772</v>
       </c>
       <c r="P4" t="n">
-        <v>316.414071289035</v>
+        <v>316.3172764119875</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -22881,28 +23117,28 @@
         <v>0.035</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8966155105363675</v>
+        <v>0.8819706211106363</v>
       </c>
       <c r="J5" t="n">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="K5" t="n">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1809607466579812</v>
+        <v>0.1791522747282532</v>
       </c>
       <c r="M5" t="n">
-        <v>12.5914639823446</v>
+        <v>12.52693162401841</v>
       </c>
       <c r="N5" t="n">
-        <v>233.9431506817787</v>
+        <v>232.03921667116</v>
       </c>
       <c r="O5" t="n">
-        <v>15.2952002498097</v>
+        <v>15.2328335076295</v>
       </c>
       <c r="P5" t="n">
-        <v>308.9081334731071</v>
+        <v>309.0445897799588</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -22959,28 +23195,28 @@
         <v>0.0321</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6912455626494605</v>
+        <v>0.6863462820439491</v>
       </c>
       <c r="J6" t="n">
+        <v>188</v>
+      </c>
+      <c r="K6" t="n">
         <v>186</v>
       </c>
-      <c r="K6" t="n">
-        <v>184</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.124583474840789</v>
+        <v>0.1254954740051787</v>
       </c>
       <c r="M6" t="n">
-        <v>11.79424750842569</v>
+        <v>11.69094430663893</v>
       </c>
       <c r="N6" t="n">
-        <v>216.0041268042589</v>
+        <v>213.7490437485654</v>
       </c>
       <c r="O6" t="n">
-        <v>14.69707885276047</v>
+        <v>14.62015881406783</v>
       </c>
       <c r="P6" t="n">
-        <v>317.4537294474999</v>
+        <v>317.4994057575345</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -23037,28 +23273,28 @@
         <v>0.034</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4236223245914422</v>
+        <v>0.427576519262751</v>
       </c>
       <c r="J7" t="n">
+        <v>188</v>
+      </c>
+      <c r="K7" t="n">
         <v>186</v>
       </c>
-      <c r="K7" t="n">
-        <v>184</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.05504954952672314</v>
+        <v>0.05719567281221583</v>
       </c>
       <c r="M7" t="n">
-        <v>11.17322220932808</v>
+        <v>11.09635751995371</v>
       </c>
       <c r="N7" t="n">
-        <v>198.1782458920385</v>
+        <v>196.23194137383</v>
       </c>
       <c r="O7" t="n">
-        <v>14.07757954664219</v>
+        <v>14.00828117128686</v>
       </c>
       <c r="P7" t="n">
-        <v>325.3554707102288</v>
+        <v>325.3187156419903</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -23115,28 +23351,28 @@
         <v>0.0439</v>
       </c>
       <c r="I8" t="n">
-        <v>0.456075252834452</v>
+        <v>0.4616209418453718</v>
       </c>
       <c r="J8" t="n">
+        <v>188</v>
+      </c>
+      <c r="K8" t="n">
         <v>186</v>
       </c>
-      <c r="K8" t="n">
-        <v>184</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.08936920690811745</v>
+        <v>0.09316354286615902</v>
       </c>
       <c r="M8" t="n">
-        <v>9.033997388029551</v>
+        <v>8.969879344217171</v>
       </c>
       <c r="N8" t="n">
-        <v>136.3548149306396</v>
+        <v>135.063373417112</v>
       </c>
       <c r="O8" t="n">
-        <v>11.677106445119</v>
+        <v>11.62167687629939</v>
       </c>
       <c r="P8" t="n">
-        <v>329.7237832452196</v>
+        <v>329.6721678846055</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -23193,28 +23429,28 @@
         <v>0.0436</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4613912893770403</v>
+        <v>0.4644773780208437</v>
       </c>
       <c r="J9" t="n">
+        <v>188</v>
+      </c>
+      <c r="K9" t="n">
         <v>186</v>
       </c>
-      <c r="K9" t="n">
-        <v>184</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.1081314962544289</v>
+        <v>0.1115983139211226</v>
       </c>
       <c r="M9" t="n">
-        <v>8.192824608609127</v>
+        <v>8.132806644684532</v>
       </c>
       <c r="N9" t="n">
-        <v>112.9614951598921</v>
+        <v>111.8315865234738</v>
       </c>
       <c r="O9" t="n">
-        <v>10.62833454309245</v>
+        <v>10.57504546200506</v>
       </c>
       <c r="P9" t="n">
-        <v>336.5582120470961</v>
+        <v>336.5295109857489</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -23271,28 +23507,28 @@
         <v>0.0433</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5556325456985945</v>
+        <v>0.5636833281797393</v>
       </c>
       <c r="J10" t="n">
+        <v>188</v>
+      </c>
+      <c r="K10" t="n">
         <v>186</v>
       </c>
-      <c r="K10" t="n">
-        <v>184</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.1216075949152322</v>
+        <v>0.127053212198677</v>
       </c>
       <c r="M10" t="n">
-        <v>8.871642949713744</v>
+        <v>8.823725523733819</v>
       </c>
       <c r="N10" t="n">
-        <v>143.4650983043738</v>
+        <v>142.1530274188327</v>
       </c>
       <c r="O10" t="n">
-        <v>11.97769169349311</v>
+        <v>11.922794446724</v>
       </c>
       <c r="P10" t="n">
-        <v>342.0226911805722</v>
+        <v>341.9476982399187</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -23349,28 +23585,28 @@
         <v>0.0418</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5892596635807974</v>
+        <v>0.6027691978849482</v>
       </c>
       <c r="J11" t="n">
+        <v>188</v>
+      </c>
+      <c r="K11" t="n">
         <v>186</v>
       </c>
-      <c r="K11" t="n">
-        <v>184</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.1387682108315299</v>
+        <v>0.1465868327451151</v>
       </c>
       <c r="M11" t="n">
-        <v>9.315262673237326</v>
+        <v>9.26911078900941</v>
       </c>
       <c r="N11" t="n">
-        <v>138.6393536427659</v>
+        <v>137.736832694663</v>
       </c>
       <c r="O11" t="n">
-        <v>11.7745213763773</v>
+        <v>11.73613363483319</v>
       </c>
       <c r="P11" t="n">
-        <v>337.1538420903414</v>
+        <v>337.0279731176552</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -23427,28 +23663,28 @@
         <v>0.0421</v>
       </c>
       <c r="I12" t="n">
-        <v>0.6164515828627344</v>
+        <v>0.6266197892348692</v>
       </c>
       <c r="J12" t="n">
+        <v>188</v>
+      </c>
+      <c r="K12" t="n">
         <v>186</v>
       </c>
-      <c r="K12" t="n">
-        <v>184</v>
-      </c>
       <c r="L12" t="n">
-        <v>0.1441511677388536</v>
+        <v>0.1507667276925473</v>
       </c>
       <c r="M12" t="n">
-        <v>9.478985175242189</v>
+        <v>9.421024929991422</v>
       </c>
       <c r="N12" t="n">
-        <v>145.1509480480007</v>
+        <v>144.0168528095219</v>
       </c>
       <c r="O12" t="n">
-        <v>12.04786072495863</v>
+        <v>12.00070217985273</v>
       </c>
       <c r="P12" t="n">
-        <v>332.4008950573776</v>
+        <v>332.3062050249342</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -23505,28 +23741,28 @@
         <v>0.0429</v>
       </c>
       <c r="I13" t="n">
-        <v>0.6584802311972421</v>
+        <v>0.6793740140213896</v>
       </c>
       <c r="J13" t="n">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="K13" t="n">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2130710410444497</v>
+        <v>0.2252687749648548</v>
       </c>
       <c r="M13" t="n">
-        <v>8.097427566537691</v>
+        <v>8.106111995678468</v>
       </c>
       <c r="N13" t="n">
-        <v>103.9512904817101</v>
+        <v>104.2904494454469</v>
       </c>
       <c r="O13" t="n">
-        <v>10.19565056686968</v>
+        <v>10.21226955409261</v>
       </c>
       <c r="P13" t="n">
-        <v>326.6674269010856</v>
+        <v>326.4745869949634</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -23583,28 +23819,28 @@
         <v>0.0448</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5954771941476352</v>
+        <v>0.6115412192371834</v>
       </c>
       <c r="J14" t="n">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="K14" t="n">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1877800783051511</v>
+        <v>0.1982896378987195</v>
       </c>
       <c r="M14" t="n">
-        <v>7.944554685581096</v>
+        <v>7.939662748814383</v>
       </c>
       <c r="N14" t="n">
-        <v>99.56064265453195</v>
+        <v>99.34489625624499</v>
       </c>
       <c r="O14" t="n">
-        <v>9.978007950213907</v>
+        <v>9.967190991259523</v>
       </c>
       <c r="P14" t="n">
-        <v>326.4260907320088</v>
+        <v>326.2778236279119</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -23661,28 +23897,28 @@
         <v>0.0419</v>
       </c>
       <c r="I15" t="n">
-        <v>0.6447009496328679</v>
+        <v>0.6663388726119829</v>
       </c>
       <c r="J15" t="n">
+        <v>188</v>
+      </c>
+      <c r="K15" t="n">
         <v>186</v>
       </c>
-      <c r="K15" t="n">
-        <v>184</v>
-      </c>
       <c r="L15" t="n">
-        <v>0.1982878115521489</v>
+        <v>0.2105638606205186</v>
       </c>
       <c r="M15" t="n">
-        <v>8.192916045564473</v>
+        <v>8.206242863651967</v>
       </c>
       <c r="N15" t="n">
-        <v>109.2281606726697</v>
+        <v>109.4999077963551</v>
       </c>
       <c r="O15" t="n">
-        <v>10.45122771126291</v>
+        <v>10.46422036256668</v>
       </c>
       <c r="P15" t="n">
-        <v>325.1579549414159</v>
+        <v>324.9579189293393</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -23739,28 +23975,28 @@
         <v>0.0442</v>
       </c>
       <c r="I16" t="n">
-        <v>0.6954349998787357</v>
+        <v>0.7213182769506231</v>
       </c>
       <c r="J16" t="n">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="K16" t="n">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2125345098954571</v>
+        <v>0.2261186580637654</v>
       </c>
       <c r="M16" t="n">
-        <v>8.792453300186757</v>
+        <v>8.799854116294226</v>
       </c>
       <c r="N16" t="n">
-        <v>115.8452655088818</v>
+        <v>116.5113261748074</v>
       </c>
       <c r="O16" t="n">
-        <v>10.76314384874986</v>
+        <v>10.79404123462605</v>
       </c>
       <c r="P16" t="n">
-        <v>323.1551744731497</v>
+        <v>322.9149620736644</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -23817,28 +24053,28 @@
         <v>0.0482</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6489995740333796</v>
+        <v>0.6732625481532916</v>
       </c>
       <c r="J17" t="n">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="K17" t="n">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2059229397295121</v>
+        <v>0.2193329573664201</v>
       </c>
       <c r="M17" t="n">
-        <v>8.384639790493061</v>
+        <v>8.393835077624097</v>
       </c>
       <c r="N17" t="n">
-        <v>105.0049742217254</v>
+        <v>105.5618905045583</v>
       </c>
       <c r="O17" t="n">
-        <v>10.24719348025231</v>
+        <v>10.2743316329851</v>
       </c>
       <c r="P17" t="n">
-        <v>324.4673075305541</v>
+        <v>324.2421490962284</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -23895,28 +24131,28 @@
         <v>0.0524</v>
       </c>
       <c r="I18" t="n">
-        <v>0.586306262577783</v>
+        <v>0.6084593412549195</v>
       </c>
       <c r="J18" t="n">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="K18" t="n">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1320609590624854</v>
+        <v>0.1423802170805878</v>
       </c>
       <c r="M18" t="n">
-        <v>10.50473779211623</v>
+        <v>10.48669242998693</v>
       </c>
       <c r="N18" t="n">
-        <v>146.0585455971497</v>
+        <v>145.9098332885627</v>
       </c>
       <c r="O18" t="n">
-        <v>12.0854683648235</v>
+        <v>12.07931427228229</v>
       </c>
       <c r="P18" t="n">
-        <v>322.0931042098098</v>
+        <v>321.8874644784053</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -23973,28 +24209,28 @@
         <v>0.05</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4273001014267293</v>
+        <v>0.4551698980953747</v>
       </c>
       <c r="J19" t="n">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="K19" t="n">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="L19" t="n">
-        <v>0.08837862252412199</v>
+        <v>0.09952263247979032</v>
       </c>
       <c r="M19" t="n">
-        <v>9.177233370540762</v>
+        <v>9.215963522735843</v>
       </c>
       <c r="N19" t="n">
-        <v>121.6042997003117</v>
+        <v>122.5109162889957</v>
       </c>
       <c r="O19" t="n">
-        <v>11.02743395810248</v>
+        <v>11.0684649472723</v>
       </c>
       <c r="P19" t="n">
-        <v>320.9817530460171</v>
+        <v>320.7234743157031</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -24051,28 +24287,28 @@
         <v>0.0506</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3019190122478388</v>
+        <v>0.3311812352220657</v>
       </c>
       <c r="J20" t="n">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="K20" t="n">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="L20" t="n">
-        <v>0.04700331515228229</v>
+        <v>0.05615176909319219</v>
       </c>
       <c r="M20" t="n">
-        <v>9.040392688161655</v>
+        <v>9.079654178128386</v>
       </c>
       <c r="N20" t="n">
-        <v>119.3327065228234</v>
+        <v>120.4888727286129</v>
       </c>
       <c r="O20" t="n">
-        <v>10.92395104908583</v>
+        <v>10.9767423550256</v>
       </c>
       <c r="P20" t="n">
-        <v>322.5768233721527</v>
+        <v>322.3056356020773</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -24129,28 +24365,28 @@
         <v>0.0544</v>
       </c>
       <c r="I21" t="n">
-        <v>0.4607204938052216</v>
+        <v>0.48828965240601</v>
       </c>
       <c r="J21" t="n">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="K21" t="n">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1050795611772632</v>
+        <v>0.1169567438681894</v>
       </c>
       <c r="M21" t="n">
-        <v>8.818599800334166</v>
+        <v>8.847595349206676</v>
       </c>
       <c r="N21" t="n">
-        <v>116.8703560335585</v>
+        <v>117.7844740813042</v>
       </c>
       <c r="O21" t="n">
-        <v>10.81065937089679</v>
+        <v>10.85285557267322</v>
       </c>
       <c r="P21" t="n">
-        <v>320.6972782707353</v>
+        <v>320.4414292155427</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -24207,28 +24443,28 @@
         <v>0.0505</v>
       </c>
       <c r="I22" t="n">
-        <v>0.307400714362633</v>
+        <v>0.3426651230729529</v>
       </c>
       <c r="J22" t="n">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="K22" t="n">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="L22" t="n">
-        <v>0.03838987168952745</v>
+        <v>0.04724465232873998</v>
       </c>
       <c r="M22" t="n">
-        <v>10.20954250364188</v>
+        <v>10.24039655701422</v>
       </c>
       <c r="N22" t="n">
-        <v>152.8297068136362</v>
+        <v>154.7552247140712</v>
       </c>
       <c r="O22" t="n">
-        <v>12.36243126628562</v>
+        <v>12.44006530184111</v>
       </c>
       <c r="P22" t="n">
-        <v>324.9000062892093</v>
+        <v>324.5732455707353</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -24285,28 +24521,28 @@
         <v>0.0567</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3106134211395512</v>
+        <v>0.3419653879939457</v>
       </c>
       <c r="J23" t="n">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="K23" t="n">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="L23" t="n">
-        <v>0.03979363847429551</v>
+        <v>0.04801209034945864</v>
       </c>
       <c r="M23" t="n">
-        <v>9.725110689592539</v>
+        <v>9.782279118394735</v>
       </c>
       <c r="N23" t="n">
-        <v>150.3166296664081</v>
+        <v>151.5381202911722</v>
       </c>
       <c r="O23" t="n">
-        <v>12.2603682516639</v>
+        <v>12.31008205866932</v>
       </c>
       <c r="P23" t="n">
-        <v>327.0511831572599</v>
+        <v>326.7606867025217</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -24363,28 +24599,28 @@
         <v>0.0536</v>
       </c>
       <c r="I24" t="n">
-        <v>0.4208377753792323</v>
+        <v>0.4464013108226078</v>
       </c>
       <c r="J24" t="n">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="K24" t="n">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="L24" t="n">
-        <v>0.07636809085187202</v>
+        <v>0.08581890177905271</v>
       </c>
       <c r="M24" t="n">
-        <v>9.394389971317077</v>
+        <v>9.416292202439976</v>
       </c>
       <c r="N24" t="n">
-        <v>138.3031569998057</v>
+        <v>138.7321071488</v>
       </c>
       <c r="O24" t="n">
-        <v>11.7602362646252</v>
+        <v>11.77845945566736</v>
       </c>
       <c r="P24" t="n">
-        <v>329.2462119385331</v>
+        <v>329.0093683111513</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -24441,28 +24677,28 @@
         <v>0.0562</v>
       </c>
       <c r="I25" t="n">
-        <v>0.2301251697681904</v>
+        <v>0.2494665576885781</v>
       </c>
       <c r="J25" t="n">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="K25" t="n">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="L25" t="n">
-        <v>0.02078766301243307</v>
+        <v>0.02472577945245846</v>
       </c>
       <c r="M25" t="n">
-        <v>10.37533200561787</v>
+        <v>10.37921002914623</v>
       </c>
       <c r="N25" t="n">
-        <v>161.2733402340786</v>
+        <v>160.6118993722476</v>
       </c>
       <c r="O25" t="n">
-        <v>12.699344086766</v>
+        <v>12.67327500578472</v>
       </c>
       <c r="P25" t="n">
-        <v>331.5253368706214</v>
+        <v>331.3458326706861</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -24519,28 +24755,28 @@
         <v>0.064</v>
       </c>
       <c r="I26" t="n">
-        <v>0.2138012141245922</v>
+        <v>0.2369650716959092</v>
       </c>
       <c r="J26" t="n">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="K26" t="n">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="L26" t="n">
-        <v>0.01483871319101315</v>
+        <v>0.01843778686580333</v>
       </c>
       <c r="M26" t="n">
-        <v>11.41128335713632</v>
+        <v>11.38635849761069</v>
       </c>
       <c r="N26" t="n">
-        <v>196.7399025440221</v>
+        <v>196.166137505108</v>
       </c>
       <c r="O26" t="n">
-        <v>14.026400199054</v>
+        <v>14.00593222549317</v>
       </c>
       <c r="P26" t="n">
-        <v>328.0130194189719</v>
+        <v>327.7991635796544</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -24597,28 +24833,28 @@
         <v>0.0554</v>
       </c>
       <c r="I27" t="n">
-        <v>0.3503763985772579</v>
+        <v>0.3658826721793622</v>
       </c>
       <c r="J27" t="n">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="K27" t="n">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="L27" t="n">
-        <v>0.03254930200254158</v>
+        <v>0.03607443155212031</v>
       </c>
       <c r="M27" t="n">
-        <v>12.25804840949255</v>
+        <v>12.17586002742707</v>
       </c>
       <c r="N27" t="n">
-        <v>235.5984982407948</v>
+        <v>233.7784439973897</v>
       </c>
       <c r="O27" t="n">
-        <v>15.34921816382824</v>
+        <v>15.28981504130739</v>
       </c>
       <c r="P27" t="n">
-        <v>321.1568989714627</v>
+        <v>321.0132168583633</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -24675,28 +24911,28 @@
         <v>0.0452</v>
       </c>
       <c r="I28" t="n">
-        <v>0.2421252042856777</v>
+        <v>0.2490711402389841</v>
       </c>
       <c r="J28" t="n">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="K28" t="n">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="L28" t="n">
-        <v>0.0199706984863528</v>
+        <v>0.02156920567374054</v>
       </c>
       <c r="M28" t="n">
-        <v>11.17023728085418</v>
+        <v>11.08807233857825</v>
       </c>
       <c r="N28" t="n">
-        <v>185.7554107573885</v>
+        <v>183.9160175936601</v>
       </c>
       <c r="O28" t="n">
-        <v>13.62921167043011</v>
+        <v>13.56156398036967</v>
       </c>
       <c r="P28" t="n">
-        <v>323.1606248045118</v>
+        <v>323.0962562450497</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -24753,28 +24989,28 @@
         <v>0.0527</v>
       </c>
       <c r="I29" t="n">
-        <v>0.2027626434080579</v>
+        <v>0.2040813837955698</v>
       </c>
       <c r="J29" t="n">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="K29" t="n">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="L29" t="n">
-        <v>0.01708728850130514</v>
+        <v>0.01769780082451611</v>
       </c>
       <c r="M29" t="n">
-        <v>10.53139977831955</v>
+        <v>10.42628687442475</v>
       </c>
       <c r="N29" t="n">
-        <v>152.6980022432462</v>
+        <v>151.08083252929</v>
       </c>
       <c r="O29" t="n">
-        <v>12.35710331118285</v>
+        <v>12.29149431636731</v>
       </c>
       <c r="P29" t="n">
-        <v>322.5483970499984</v>
+        <v>322.5361897755731</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
@@ -24831,28 +25067,28 @@
         <v>0.0524</v>
       </c>
       <c r="I30" t="n">
-        <v>0.2145582637080309</v>
+        <v>0.2376378722855778</v>
       </c>
       <c r="J30" t="n">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="K30" t="n">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="L30" t="n">
-        <v>0.01816723586647817</v>
+        <v>0.02247768994312183</v>
       </c>
       <c r="M30" t="n">
-        <v>10.33892636442199</v>
+        <v>10.35247220895499</v>
       </c>
       <c r="N30" t="n">
-        <v>160.6404176931219</v>
+        <v>160.5029753547304</v>
       </c>
       <c r="O30" t="n">
-        <v>12.67440009204072</v>
+        <v>12.6689768866602</v>
       </c>
       <c r="P30" t="n">
-        <v>321.7548084392226</v>
+        <v>321.5408478130942</v>
       </c>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr">
@@ -24909,28 +25145,28 @@
         <v>0.0501</v>
       </c>
       <c r="I31" t="n">
-        <v>0.3060745516623196</v>
+        <v>0.3342192831937316</v>
       </c>
       <c r="J31" t="n">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="K31" t="n">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="L31" t="n">
-        <v>0.04234046274998748</v>
+        <v>0.05037680565217095</v>
       </c>
       <c r="M31" t="n">
-        <v>9.184564910487845</v>
+        <v>9.221341198028536</v>
       </c>
       <c r="N31" t="n">
-        <v>136.9850304281305</v>
+        <v>137.7716914699894</v>
       </c>
       <c r="O31" t="n">
-        <v>11.70406042483251</v>
+        <v>11.73761864561928</v>
       </c>
       <c r="P31" t="n">
-        <v>319.5797912099612</v>
+        <v>319.3185846157044</v>
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
@@ -24987,28 +25223,28 @@
         <v>0.0491</v>
       </c>
       <c r="I32" t="n">
-        <v>0.2710018972741595</v>
+        <v>0.2907041877579874</v>
       </c>
       <c r="J32" t="n">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="K32" t="n">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="L32" t="n">
-        <v>0.04403974479452177</v>
+        <v>0.05091838268484083</v>
       </c>
       <c r="M32" t="n">
-        <v>8.046290788620825</v>
+        <v>8.063566230094603</v>
       </c>
       <c r="N32" t="n">
-        <v>103.0630128884493</v>
+        <v>103.0641991083393</v>
       </c>
       <c r="O32" t="n">
-        <v>10.15199551262949</v>
+        <v>10.15205393545263</v>
       </c>
       <c r="P32" t="n">
-        <v>317.0105582527363</v>
+        <v>316.8277046124099</v>
       </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
@@ -25065,28 +25301,28 @@
         <v>0.0427</v>
       </c>
       <c r="I33" t="n">
-        <v>0.2297034246183476</v>
+        <v>0.2418812270824564</v>
       </c>
       <c r="J33" t="n">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="K33" t="n">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="L33" t="n">
-        <v>0.02725035434077094</v>
+        <v>0.03069494219538293</v>
       </c>
       <c r="M33" t="n">
-        <v>8.674649719647883</v>
+        <v>8.658201774320839</v>
       </c>
       <c r="N33" t="n">
-        <v>121.7662681688778</v>
+        <v>120.8855194623395</v>
       </c>
       <c r="O33" t="n">
-        <v>11.03477540183205</v>
+        <v>10.99479510779257</v>
       </c>
       <c r="P33" t="n">
-        <v>315.3520901337163</v>
+        <v>315.2390700611919</v>
       </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
@@ -25124,7 +25360,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH187"/>
+  <dimension ref="A1:AH189"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57079,6 +57315,350 @@
         </is>
       </c>
     </row>
+    <row r="188">
+      <c r="A188" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-24 22:17:36+00:00</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>-34.42306690421296,173.01259981587987</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>-34.42367941495969,173.01208186191494</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>-34.42440515398195,173.01182477978705</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>-34.42504343110506,173.01136621099997</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>-34.42572036845346,173.01099672152364</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>-34.426414206613686,173.010666181301</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>-34.427092515031354,173.01029987484006</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>-34.42777023265108,173.00993221933848</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>-34.42847048541994,173.00961342408274</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>-34.42916797655943,173.0093094086765</t>
+        </is>
+      </c>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>-34.42985919196517,173.00898088306656</t>
+        </is>
+      </c>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>-34.430568984828724,173.0087222540564</t>
+        </is>
+      </c>
+      <c r="N188" t="inlineStr">
+        <is>
+          <t>-34.431257907016494,173.00838620574308</t>
+        </is>
+      </c>
+      <c r="O188" t="inlineStr">
+        <is>
+          <t>-34.43197033796794,173.00813740951926</t>
+        </is>
+      </c>
+      <c r="P188" t="inlineStr">
+        <is>
+          <t>-34.43267160214416,173.00784454884888</t>
+        </is>
+      </c>
+      <c r="Q188" t="inlineStr">
+        <is>
+          <t>-34.43338201483996,173.0075762608052</t>
+        </is>
+      </c>
+      <c r="R188" t="inlineStr">
+        <is>
+          <t>-34.43409043564966,173.00729057538402</t>
+        </is>
+      </c>
+      <c r="S188" t="inlineStr">
+        <is>
+          <t>-34.43480923733276,173.00707256636832</t>
+        </is>
+      </c>
+      <c r="T188" t="inlineStr">
+        <is>
+          <t>-34.435527574024654,173.00685222749314</t>
+        </is>
+      </c>
+      <c r="U188" t="inlineStr">
+        <is>
+          <t>-34.436252681537425,173.00666630465952</t>
+        </is>
+      </c>
+      <c r="V188" t="inlineStr">
+        <is>
+          <t>-34.43698437229093,173.0065138456585</t>
+        </is>
+      </c>
+      <c r="W188" t="inlineStr">
+        <is>
+          <t>-34.43770594338892,173.00631002709255</t>
+        </is>
+      </c>
+      <c r="X188" t="inlineStr">
+        <is>
+          <t>-34.43843394879138,173.00612657493255</t>
+        </is>
+      </c>
+      <c r="Y188" t="inlineStr">
+        <is>
+          <t>-34.439156224040865,173.0058814813479</t>
+        </is>
+      </c>
+      <c r="Z188" t="inlineStr">
+        <is>
+          <t>-34.43989552600208,173.0057660518411</t>
+        </is>
+      </c>
+      <c r="AA188" t="inlineStr">
+        <is>
+          <t>-34.440623452492176,173.0055799200602</t>
+        </is>
+      </c>
+      <c r="AB188" t="inlineStr">
+        <is>
+          <t>-34.44135302536312,173.00541086943616</t>
+        </is>
+      </c>
+      <c r="AC188" t="inlineStr">
+        <is>
+          <t>-34.44208445391263,173.00526106277482</t>
+        </is>
+      </c>
+      <c r="AD188" t="inlineStr">
+        <is>
+          <t>-34.4428286397817,173.00524316094018</t>
+        </is>
+      </c>
+      <c r="AE188" t="inlineStr">
+        <is>
+          <t>-34.44357384603542,173.00519630650408</t>
+        </is>
+      </c>
+      <c r="AF188" t="inlineStr">
+        <is>
+          <t>-34.44431204237908,173.00503907576322</t>
+        </is>
+      </c>
+      <c r="AG188" t="inlineStr">
+        <is>
+          <t>-34.44504887558894,173.004906413814</t>
+        </is>
+      </c>
+      <c r="AH188" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-20 22:17:31+00:00</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>-34.42303953754436,173.01253676752927</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>-34.42365702770127,173.01203028538447</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>-34.42440515398195,173.01182477978705</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>-34.42501870031506,173.01130923500503</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>-34.42572036845346,173.01099672152364</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>-34.42638411935102,173.01059686434598</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>-34.42706874641992,173.01024511502533</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>-34.42775094150112,173.00988777488274</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>-34.428455511379426,173.00957179253928</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>-34.42915301196131,173.00925588736226</t>
+        </is>
+      </c>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t>-34.42983955470259,173.0089080187039</t>
+        </is>
+      </c>
+      <c r="M189" t="inlineStr">
+        <is>
+          <t>-34.430544633384905,173.0086318973946</t>
+        </is>
+      </c>
+      <c r="N189" t="inlineStr">
+        <is>
+          <t>-34.43123985948995,173.00831923987872</t>
+        </is>
+      </c>
+      <c r="O189" t="inlineStr">
+        <is>
+          <t>-34.43195284824719,173.0080725131774</t>
+        </is>
+      </c>
+      <c r="P189" t="inlineStr">
+        <is>
+          <t>-34.432670595282424,173.00784070943843</t>
+        </is>
+      </c>
+      <c r="Q189" t="inlineStr">
+        <is>
+          <t>-34.43337857803596,173.007561033534</t>
+        </is>
+      </c>
+      <c r="R189" t="inlineStr">
+        <is>
+          <t>-34.434096128283,173.00731948431581</t>
+        </is>
+      </c>
+      <c r="S189" t="inlineStr">
+        <is>
+          <t>-34.43480917477594,173.00707224868515</t>
+        </is>
+      </c>
+      <c r="T189" t="inlineStr">
+        <is>
+          <t>-34.43552815789173,173.00685519256035</t>
+        </is>
+      </c>
+      <c r="U189" t="inlineStr">
+        <is>
+          <t>-34.436250533730195,173.00665539735706</t>
+        </is>
+      </c>
+      <c r="V189" t="inlineStr">
+        <is>
+          <t>-34.43697778287773,173.00648038219452</t>
+        </is>
+      </c>
+      <c r="W189" t="inlineStr">
+        <is>
+          <t>-34.43769847812731,173.00627211563912</t>
+        </is>
+      </c>
+      <c r="X189" t="inlineStr">
+        <is>
+          <t>-34.43842629330535,173.00608191315945</t>
+        </is>
+      </c>
+      <c r="Y189" t="inlineStr">
+        <is>
+          <t>-34.439156224040865,173.0058814813479</t>
+        </is>
+      </c>
+      <c r="Z189" t="inlineStr">
+        <is>
+          <t>-34.4398934022548,173.00574410436715</t>
+        </is>
+      </c>
+      <c r="AA189" t="inlineStr">
+        <is>
+          <t>-34.44062206105458,173.00556554055837</t>
+        </is>
+      </c>
+      <c r="AB189" t="inlineStr">
+        <is>
+          <t>-34.44135291028061,173.0054096801439</t>
+        </is>
+      </c>
+      <c r="AC189" t="inlineStr">
+        <is>
+          <t>-34.44208349139489,173.00525111588138</t>
+        </is>
+      </c>
+      <c r="AD189" t="inlineStr">
+        <is>
+          <t>-34.442833797598716,173.00529646379263</t>
+        </is>
+      </c>
+      <c r="AE189" t="inlineStr">
+        <is>
+          <t>-34.44357384603542,173.00519630650408</t>
+        </is>
+      </c>
+      <c r="AF189" t="inlineStr">
+        <is>
+          <t>-34.44431204237908,173.00503907576322</t>
+        </is>
+      </c>
+      <c r="AG189" t="inlineStr">
+        <is>
+          <t>-34.44504887558894,173.004906413814</t>
+        </is>
+      </c>
+      <c r="AH189" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0003/nzd0003.xlsx
+++ b/data/nzd0003/nzd0003.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH189"/>
+  <dimension ref="A1:AH190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20706,13 +20706,13 @@
         <v>310.58</v>
       </c>
       <c r="D189" t="n">
-        <v>332.56</v>
+        <v>316.85</v>
       </c>
       <c r="E189" t="n">
         <v>322.38</v>
       </c>
       <c r="F189" t="n">
-        <v>333.26</v>
+        <v>324.56</v>
       </c>
       <c r="G189" t="n">
         <v>335.08</v>
@@ -20742,10 +20742,10 @@
         <v>350.49</v>
       </c>
       <c r="P189" t="n">
-        <v>355.01</v>
+        <v>350.19</v>
       </c>
       <c r="Q189" t="n">
-        <v>353.7</v>
+        <v>348.6</v>
       </c>
       <c r="R189" t="n">
         <v>350.64</v>
@@ -20796,6 +20796,114 @@
         <v>327.84</v>
       </c>
       <c r="AH189" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:17:21+00:00</t>
+        </is>
+      </c>
+      <c r="B190" t="n">
+        <v>315.96</v>
+      </c>
+      <c r="C190" t="n">
+        <v>306.45</v>
+      </c>
+      <c r="D190" t="n">
+        <v>304.6</v>
+      </c>
+      <c r="E190" t="n">
+        <v>319.33</v>
+      </c>
+      <c r="F190" t="n">
+        <v>321.12</v>
+      </c>
+      <c r="G190" t="n">
+        <v>329.75</v>
+      </c>
+      <c r="H190" t="n">
+        <v>338.04</v>
+      </c>
+      <c r="I190" t="n">
+        <v>344.75</v>
+      </c>
+      <c r="J190" t="n">
+        <v>353.42</v>
+      </c>
+      <c r="K190" t="n">
+        <v>353.03</v>
+      </c>
+      <c r="L190" t="n">
+        <v>344.56</v>
+      </c>
+      <c r="M190" t="n">
+        <v>344.16</v>
+      </c>
+      <c r="N190" t="n">
+        <v>342.9</v>
+      </c>
+      <c r="O190" t="n">
+        <v>347.91</v>
+      </c>
+      <c r="P190" t="n">
+        <v>347.41</v>
+      </c>
+      <c r="Q190" t="n">
+        <v>346.48</v>
+      </c>
+      <c r="R190" t="n">
+        <v>350.06</v>
+      </c>
+      <c r="S190" t="n">
+        <v>343.54</v>
+      </c>
+      <c r="T190" t="n">
+        <v>344.3</v>
+      </c>
+      <c r="U190" t="n">
+        <v>344.89</v>
+      </c>
+      <c r="V190" t="n">
+        <v>348.74</v>
+      </c>
+      <c r="W190" t="n">
+        <v>350.17</v>
+      </c>
+      <c r="X190" t="n">
+        <v>352.7</v>
+      </c>
+      <c r="Y190" t="n">
+        <v>343.7</v>
+      </c>
+      <c r="Z190" t="n">
+        <v>341.71</v>
+      </c>
+      <c r="AA190" t="n">
+        <v>333.71</v>
+      </c>
+      <c r="AB190" t="n">
+        <v>332.11</v>
+      </c>
+      <c r="AC190" t="n">
+        <v>326.24</v>
+      </c>
+      <c r="AD190" t="n">
+        <v>336.35</v>
+      </c>
+      <c r="AE190" t="n">
+        <v>338.6</v>
+      </c>
+      <c r="AF190" t="n">
+        <v>331.82</v>
+      </c>
+      <c r="AG190" t="n">
+        <v>326.31</v>
+      </c>
+      <c r="AH190" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -20812,7 +20920,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B190"/>
+  <dimension ref="A1:B191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22715,6 +22823,16 @@
       </c>
       <c r="B190" t="n">
         <v>0.89</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B191" t="n">
+        <v>0.78</v>
       </c>
     </row>
   </sheetData>
@@ -22883,28 +23001,28 @@
         <v>0.0366</v>
       </c>
       <c r="I2" t="n">
-        <v>1.037596117169578</v>
+        <v>1.018557168695772</v>
       </c>
       <c r="J2" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="K2" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2336283897868845</v>
+        <v>0.2274297121408498</v>
       </c>
       <c r="M2" t="n">
-        <v>12.39877350970995</v>
+        <v>12.42412546563767</v>
       </c>
       <c r="N2" t="n">
-        <v>229.6627129642806</v>
+        <v>230.4988808405194</v>
       </c>
       <c r="O2" t="n">
-        <v>15.15462678406435</v>
+        <v>15.18218959308964</v>
       </c>
       <c r="P2" t="n">
-        <v>307.9845735501736</v>
+        <v>308.1652473114726</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -22961,28 +23079,28 @@
         <v>0.0328</v>
       </c>
       <c r="I3" t="n">
-        <v>1.023876366671698</v>
+        <v>0.9997065250999205</v>
       </c>
       <c r="J3" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="K3" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2269869786875021</v>
+        <v>0.2181953599558012</v>
       </c>
       <c r="M3" t="n">
-        <v>12.13031314141661</v>
+        <v>12.19218572739411</v>
       </c>
       <c r="N3" t="n">
-        <v>234.4646317236225</v>
+        <v>236.54828663443</v>
       </c>
       <c r="O3" t="n">
-        <v>15.31223797240699</v>
+        <v>15.38012635300601</v>
       </c>
       <c r="P3" t="n">
-        <v>304.0738963588247</v>
+        <v>304.300842406868</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -23039,28 +23157,28 @@
         <v>0.0287</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4198445762638579</v>
+        <v>0.3826333246174325</v>
       </c>
       <c r="J4" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="K4" t="n">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03927080105737835</v>
+        <v>0.03283207926067722</v>
       </c>
       <c r="M4" t="n">
-        <v>13.21126954386645</v>
+        <v>13.29863493402095</v>
       </c>
       <c r="N4" t="n">
-        <v>277.5139508970735</v>
+        <v>279.1916153925064</v>
       </c>
       <c r="O4" t="n">
-        <v>16.65874998002772</v>
+        <v>16.70902796073148</v>
       </c>
       <c r="P4" t="n">
-        <v>316.3172764119875</v>
+        <v>316.6705612353571</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -23117,28 +23235,28 @@
         <v>0.035</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8819706211106363</v>
+        <v>0.8689536328171266</v>
       </c>
       <c r="J5" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="K5" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1791522747282532</v>
+        <v>0.1759136314795609</v>
       </c>
       <c r="M5" t="n">
-        <v>12.52693162401841</v>
+        <v>12.52339981394575</v>
       </c>
       <c r="N5" t="n">
-        <v>232.03921667116</v>
+        <v>231.7112699395491</v>
       </c>
       <c r="O5" t="n">
-        <v>15.2328335076295</v>
+        <v>15.22206523240356</v>
       </c>
       <c r="P5" t="n">
-        <v>309.0445897799588</v>
+        <v>309.1665379804207</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -23195,28 +23313,28 @@
         <v>0.0321</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6863462820439491</v>
+        <v>0.6640615992587874</v>
       </c>
       <c r="J6" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="K6" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1254954740051787</v>
+        <v>0.11875494244818</v>
       </c>
       <c r="M6" t="n">
-        <v>11.69094430663893</v>
+        <v>11.73640403787185</v>
       </c>
       <c r="N6" t="n">
-        <v>213.7490437485654</v>
+        <v>214.3492860756756</v>
       </c>
       <c r="O6" t="n">
-        <v>14.62015881406783</v>
+        <v>14.64067232321233</v>
       </c>
       <c r="P6" t="n">
-        <v>317.4994057575345</v>
+        <v>317.7080923590844</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -23273,28 +23391,28 @@
         <v>0.034</v>
       </c>
       <c r="I7" t="n">
-        <v>0.427576519262751</v>
+        <v>0.4209188054675195</v>
       </c>
       <c r="J7" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="K7" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L7" t="n">
-        <v>0.05719567281221583</v>
+        <v>0.05605255043793489</v>
       </c>
       <c r="M7" t="n">
-        <v>11.09635751995371</v>
+        <v>11.06627254112261</v>
       </c>
       <c r="N7" t="n">
-        <v>196.23194137383</v>
+        <v>195.4381776190958</v>
       </c>
       <c r="O7" t="n">
-        <v>14.00828117128686</v>
+        <v>13.97992051547847</v>
       </c>
       <c r="P7" t="n">
-        <v>325.3187156419903</v>
+        <v>325.381166485556</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -23351,28 +23469,28 @@
         <v>0.0439</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4616209418453718</v>
+        <v>0.4578495427262779</v>
       </c>
       <c r="J8" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="K8" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L8" t="n">
-        <v>0.09316354286615902</v>
+        <v>0.09268122585284877</v>
       </c>
       <c r="M8" t="n">
-        <v>8.969879344217171</v>
+        <v>8.941225301773576</v>
       </c>
       <c r="N8" t="n">
-        <v>135.063373417112</v>
+        <v>134.423130178379</v>
       </c>
       <c r="O8" t="n">
-        <v>11.62167687629939</v>
+        <v>11.59409893775187</v>
       </c>
       <c r="P8" t="n">
-        <v>329.6721678846055</v>
+        <v>329.7075444513451</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -23429,28 +23547,28 @@
         <v>0.0436</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4644773780208437</v>
+        <v>0.4604924927843893</v>
       </c>
       <c r="J9" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="K9" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1115983139211226</v>
+        <v>0.1109298099046184</v>
       </c>
       <c r="M9" t="n">
-        <v>8.132806644684532</v>
+        <v>8.107224512901173</v>
       </c>
       <c r="N9" t="n">
-        <v>111.8315865234738</v>
+        <v>111.3251260968408</v>
       </c>
       <c r="O9" t="n">
-        <v>10.57504546200506</v>
+        <v>10.55107227237312</v>
       </c>
       <c r="P9" t="n">
-        <v>336.5295109857489</v>
+        <v>336.5668900999889</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -23507,28 +23625,28 @@
         <v>0.0433</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5636833281797393</v>
+        <v>0.5602783508103556</v>
       </c>
       <c r="J10" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="K10" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L10" t="n">
-        <v>0.127053212198677</v>
+        <v>0.1269095925214568</v>
       </c>
       <c r="M10" t="n">
-        <v>8.823725523733819</v>
+        <v>8.794158896375306</v>
       </c>
       <c r="N10" t="n">
-        <v>142.1530274188327</v>
+        <v>141.4597078836924</v>
       </c>
       <c r="O10" t="n">
-        <v>11.922794446724</v>
+        <v>11.89368352881867</v>
       </c>
       <c r="P10" t="n">
-        <v>341.9476982399187</v>
+        <v>341.9796376887416</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -23585,28 +23703,28 @@
         <v>0.0418</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6027691978849482</v>
+        <v>0.6026943073167302</v>
       </c>
       <c r="J11" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="K11" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1465868327451151</v>
+        <v>0.1479741124063532</v>
       </c>
       <c r="M11" t="n">
-        <v>9.26911078900941</v>
+        <v>9.220073280565309</v>
       </c>
       <c r="N11" t="n">
-        <v>137.736832694663</v>
+        <v>137.0003044344896</v>
       </c>
       <c r="O11" t="n">
-        <v>11.73613363483319</v>
+        <v>11.70471291550927</v>
       </c>
       <c r="P11" t="n">
-        <v>337.0279731176552</v>
+        <v>337.028675607925</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -23663,28 +23781,28 @@
         <v>0.0421</v>
       </c>
       <c r="I12" t="n">
-        <v>0.6266197892348692</v>
+        <v>0.622357699094974</v>
       </c>
       <c r="J12" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="K12" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1507667276925473</v>
+        <v>0.1503720454496383</v>
       </c>
       <c r="M12" t="n">
-        <v>9.421024929991422</v>
+        <v>9.399525041161157</v>
       </c>
       <c r="N12" t="n">
-        <v>144.0168528095219</v>
+        <v>143.3514616689229</v>
       </c>
       <c r="O12" t="n">
-        <v>12.00070217985273</v>
+        <v>11.97294707534126</v>
       </c>
       <c r="P12" t="n">
-        <v>332.3062050249342</v>
+        <v>332.3461843831307</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -23741,28 +23859,28 @@
         <v>0.0429</v>
       </c>
       <c r="I13" t="n">
-        <v>0.6793740140213896</v>
+        <v>0.6789585344627238</v>
       </c>
       <c r="J13" t="n">
+        <v>189</v>
+      </c>
+      <c r="K13" t="n">
         <v>188</v>
       </c>
-      <c r="K13" t="n">
-        <v>187</v>
-      </c>
       <c r="L13" t="n">
-        <v>0.2252687749648548</v>
+        <v>0.2270251532205581</v>
       </c>
       <c r="M13" t="n">
-        <v>8.106111995678468</v>
+        <v>8.065721606772868</v>
       </c>
       <c r="N13" t="n">
-        <v>104.2904494454469</v>
+        <v>103.736719717888</v>
       </c>
       <c r="O13" t="n">
-        <v>10.21226955409261</v>
+        <v>10.18512246945946</v>
       </c>
       <c r="P13" t="n">
-        <v>326.4745869949634</v>
+        <v>326.4784480281754</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -23819,28 +23937,28 @@
         <v>0.0448</v>
       </c>
       <c r="I14" t="n">
-        <v>0.6115412192371834</v>
+        <v>0.6118310882745359</v>
       </c>
       <c r="J14" t="n">
+        <v>189</v>
+      </c>
+      <c r="K14" t="n">
         <v>188</v>
       </c>
-      <c r="K14" t="n">
-        <v>187</v>
-      </c>
       <c r="L14" t="n">
-        <v>0.1982896378987195</v>
+        <v>0.2002381840010811</v>
       </c>
       <c r="M14" t="n">
-        <v>7.939662748814383</v>
+        <v>7.898855142292204</v>
       </c>
       <c r="N14" t="n">
-        <v>99.34489625624499</v>
+        <v>98.81695596915473</v>
       </c>
       <c r="O14" t="n">
-        <v>9.967190991259523</v>
+        <v>9.940671806731913</v>
       </c>
       <c r="P14" t="n">
-        <v>326.2778236279119</v>
+        <v>326.2751298877338</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -23897,28 +24015,28 @@
         <v>0.0419</v>
       </c>
       <c r="I15" t="n">
-        <v>0.6663388726119829</v>
+        <v>0.6712455796545249</v>
       </c>
       <c r="J15" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="K15" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2105638606205186</v>
+        <v>0.214686159924209</v>
       </c>
       <c r="M15" t="n">
-        <v>8.206242863651967</v>
+        <v>8.185569669940159</v>
       </c>
       <c r="N15" t="n">
-        <v>109.4999077963551</v>
+        <v>109.0552409519068</v>
       </c>
       <c r="O15" t="n">
-        <v>10.46422036256668</v>
+        <v>10.44295173559213</v>
       </c>
       <c r="P15" t="n">
-        <v>324.9579189293393</v>
+        <v>324.9122538190752</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -23975,28 +24093,28 @@
         <v>0.0442</v>
       </c>
       <c r="I16" t="n">
-        <v>0.7213182769506231</v>
+        <v>0.7217558222052944</v>
       </c>
       <c r="J16" t="n">
+        <v>189</v>
+      </c>
+      <c r="K16" t="n">
         <v>188</v>
       </c>
-      <c r="K16" t="n">
-        <v>187</v>
-      </c>
       <c r="L16" t="n">
-        <v>0.2261186580637654</v>
+        <v>0.228902471150169</v>
       </c>
       <c r="M16" t="n">
-        <v>8.799854116294226</v>
+        <v>8.754588744295239</v>
       </c>
       <c r="N16" t="n">
-        <v>116.5113261748074</v>
+        <v>115.4993259169202</v>
       </c>
       <c r="O16" t="n">
-        <v>10.79404123462605</v>
+        <v>10.74706126887347</v>
       </c>
       <c r="P16" t="n">
-        <v>322.9149620736644</v>
+        <v>322.9106846229318</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -24053,28 +24171,28 @@
         <v>0.0482</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6732625481532916</v>
+        <v>0.6725185091356386</v>
       </c>
       <c r="J17" t="n">
+        <v>189</v>
+      </c>
+      <c r="K17" t="n">
         <v>188</v>
       </c>
-      <c r="K17" t="n">
-        <v>187</v>
-      </c>
       <c r="L17" t="n">
-        <v>0.2193329573664201</v>
+        <v>0.2215256503607116</v>
       </c>
       <c r="M17" t="n">
-        <v>8.393835077624097</v>
+        <v>8.345898098438255</v>
       </c>
       <c r="N17" t="n">
-        <v>105.5618905045583</v>
+        <v>104.6089391331936</v>
       </c>
       <c r="O17" t="n">
-        <v>10.2743316329851</v>
+        <v>10.22785114934675</v>
       </c>
       <c r="P17" t="n">
-        <v>324.2421490962284</v>
+        <v>324.2488942345531</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -24131,28 +24249,28 @@
         <v>0.0524</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6084593412549195</v>
+        <v>0.6197737750431406</v>
       </c>
       <c r="J18" t="n">
+        <v>189</v>
+      </c>
+      <c r="K18" t="n">
         <v>188</v>
       </c>
-      <c r="K18" t="n">
-        <v>187</v>
-      </c>
       <c r="L18" t="n">
-        <v>0.1423802170805878</v>
+        <v>0.1477071209538702</v>
       </c>
       <c r="M18" t="n">
-        <v>10.48669242998693</v>
+        <v>10.47821351010291</v>
       </c>
       <c r="N18" t="n">
-        <v>145.9098332885627</v>
+        <v>145.8793587947225</v>
       </c>
       <c r="O18" t="n">
-        <v>12.07931427228229</v>
+        <v>12.07805277330425</v>
       </c>
       <c r="P18" t="n">
-        <v>321.8874644784053</v>
+        <v>321.7818087499231</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -24209,28 +24327,28 @@
         <v>0.05</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4551698980953747</v>
+        <v>0.46528002358129</v>
       </c>
       <c r="J19" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="K19" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L19" t="n">
-        <v>0.09952263247979032</v>
+        <v>0.1041260827185956</v>
       </c>
       <c r="M19" t="n">
-        <v>9.215963522735843</v>
+        <v>9.217921708676785</v>
       </c>
       <c r="N19" t="n">
-        <v>122.5109162889957</v>
+        <v>122.4560407561861</v>
       </c>
       <c r="O19" t="n">
-        <v>11.0684649472723</v>
+        <v>11.06598575618937</v>
       </c>
       <c r="P19" t="n">
-        <v>320.7234743157031</v>
+        <v>320.6292052672611</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -24287,28 +24405,28 @@
         <v>0.0506</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3311812352220657</v>
+        <v>0.3436391252966623</v>
       </c>
       <c r="J20" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="K20" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L20" t="n">
-        <v>0.05615176909319219</v>
+        <v>0.06041046279721252</v>
       </c>
       <c r="M20" t="n">
-        <v>9.079654178128386</v>
+        <v>9.091499039231525</v>
       </c>
       <c r="N20" t="n">
-        <v>120.4888727286129</v>
+        <v>120.7522569417921</v>
       </c>
       <c r="O20" t="n">
-        <v>10.9767423550256</v>
+        <v>10.98873318184549</v>
       </c>
       <c r="P20" t="n">
-        <v>322.3056356020773</v>
+        <v>322.1894754768084</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -24365,28 +24483,28 @@
         <v>0.0544</v>
       </c>
       <c r="I21" t="n">
-        <v>0.48828965240601</v>
+        <v>0.4991111424752181</v>
       </c>
       <c r="J21" t="n">
+        <v>189</v>
+      </c>
+      <c r="K21" t="n">
         <v>188</v>
       </c>
-      <c r="K21" t="n">
-        <v>187</v>
-      </c>
       <c r="L21" t="n">
-        <v>0.1169567438681894</v>
+        <v>0.122142221929654</v>
       </c>
       <c r="M21" t="n">
-        <v>8.847595349206676</v>
+        <v>8.85007313971199</v>
       </c>
       <c r="N21" t="n">
-        <v>117.7844740813042</v>
+        <v>117.8400461323099</v>
       </c>
       <c r="O21" t="n">
-        <v>10.85285557267322</v>
+        <v>10.85541552094207</v>
       </c>
       <c r="P21" t="n">
-        <v>320.4414292155427</v>
+        <v>320.3403766628542</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -24443,28 +24561,28 @@
         <v>0.0505</v>
       </c>
       <c r="I22" t="n">
-        <v>0.3426651230729529</v>
+        <v>0.3568898552945929</v>
       </c>
       <c r="J22" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="K22" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L22" t="n">
-        <v>0.04724465232873998</v>
+        <v>0.0512217784113842</v>
       </c>
       <c r="M22" t="n">
-        <v>10.24039655701422</v>
+        <v>10.24146833850001</v>
       </c>
       <c r="N22" t="n">
-        <v>154.7552247140712</v>
+        <v>155.1109644855123</v>
       </c>
       <c r="O22" t="n">
-        <v>12.44006530184111</v>
+        <v>12.45435524166194</v>
       </c>
       <c r="P22" t="n">
-        <v>324.5732455707353</v>
+        <v>324.4406110181033</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -24521,28 +24639,28 @@
         <v>0.0567</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3419653879939457</v>
+        <v>0.3554944018486785</v>
       </c>
       <c r="J23" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="K23" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L23" t="n">
-        <v>0.04801209034945864</v>
+        <v>0.05189411120115783</v>
       </c>
       <c r="M23" t="n">
-        <v>9.782279118394735</v>
+        <v>9.801140992580509</v>
       </c>
       <c r="N23" t="n">
-        <v>151.5381202911722</v>
+        <v>151.7987990832359</v>
       </c>
       <c r="O23" t="n">
-        <v>12.31008205866932</v>
+        <v>12.32066552923323</v>
       </c>
       <c r="P23" t="n">
-        <v>326.7606867025217</v>
+        <v>326.6345391819769</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -24599,28 +24717,28 @@
         <v>0.0536</v>
       </c>
       <c r="I24" t="n">
-        <v>0.4464013108226078</v>
+        <v>0.4575529972898271</v>
       </c>
       <c r="J24" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="K24" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L24" t="n">
-        <v>0.08581890177905271</v>
+        <v>0.09026564807315807</v>
       </c>
       <c r="M24" t="n">
-        <v>9.416292202439976</v>
+        <v>9.422283400872054</v>
       </c>
       <c r="N24" t="n">
-        <v>138.7321071488</v>
+        <v>138.719954138679</v>
       </c>
       <c r="O24" t="n">
-        <v>11.77845945566736</v>
+        <v>11.77794354455306</v>
       </c>
       <c r="P24" t="n">
-        <v>329.0093683111513</v>
+        <v>328.905387517515</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -24677,28 +24795,28 @@
         <v>0.0562</v>
       </c>
       <c r="I25" t="n">
-        <v>0.2494665576885781</v>
+        <v>0.2548653714095911</v>
       </c>
       <c r="J25" t="n">
+        <v>189</v>
+      </c>
+      <c r="K25" t="n">
         <v>188</v>
       </c>
-      <c r="K25" t="n">
-        <v>187</v>
-      </c>
       <c r="L25" t="n">
-        <v>0.02472577945245846</v>
+        <v>0.02603644316106291</v>
       </c>
       <c r="M25" t="n">
-        <v>10.37921002914623</v>
+        <v>10.35556846244113</v>
       </c>
       <c r="N25" t="n">
-        <v>160.6118993722476</v>
+        <v>159.9273508524098</v>
       </c>
       <c r="O25" t="n">
-        <v>12.67327500578472</v>
+        <v>12.64623860491371</v>
       </c>
       <c r="P25" t="n">
-        <v>331.3458326706861</v>
+        <v>331.2954178105782</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -24755,28 +24873,28 @@
         <v>0.064</v>
       </c>
       <c r="I26" t="n">
-        <v>0.2369650716959092</v>
+        <v>0.2441682737150462</v>
       </c>
       <c r="J26" t="n">
+        <v>189</v>
+      </c>
+      <c r="K26" t="n">
         <v>188</v>
       </c>
-      <c r="K26" t="n">
-        <v>187</v>
-      </c>
       <c r="L26" t="n">
-        <v>0.01843778686580333</v>
+        <v>0.01974178114496672</v>
       </c>
       <c r="M26" t="n">
-        <v>11.38635849761069</v>
+        <v>11.35543659449458</v>
       </c>
       <c r="N26" t="n">
-        <v>196.166137505108</v>
+        <v>195.4236838850844</v>
       </c>
       <c r="O26" t="n">
-        <v>14.00593222549317</v>
+        <v>13.97940212902842</v>
       </c>
       <c r="P26" t="n">
-        <v>327.7991635796544</v>
+        <v>327.7322421480383</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -24833,28 +24951,28 @@
         <v>0.0554</v>
       </c>
       <c r="I27" t="n">
-        <v>0.3658826721793622</v>
+        <v>0.3686644184148316</v>
       </c>
       <c r="J27" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="K27" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L27" t="n">
-        <v>0.03607443155212031</v>
+        <v>0.03699726470059683</v>
       </c>
       <c r="M27" t="n">
-        <v>12.17586002742707</v>
+        <v>12.11990282578515</v>
       </c>
       <c r="N27" t="n">
-        <v>233.7784439973897</v>
+        <v>232.5864388163698</v>
       </c>
       <c r="O27" t="n">
-        <v>15.28981504130739</v>
+        <v>15.2507848590284</v>
       </c>
       <c r="P27" t="n">
-        <v>321.0132168583633</v>
+        <v>320.987279240577</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -24911,28 +25029,28 @@
         <v>0.0452</v>
       </c>
       <c r="I28" t="n">
-        <v>0.2490711402389841</v>
+        <v>0.2513105458648702</v>
       </c>
       <c r="J28" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="K28" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L28" t="n">
-        <v>0.02156920567374054</v>
+        <v>0.02218989691075723</v>
       </c>
       <c r="M28" t="n">
-        <v>11.08807233857825</v>
+        <v>11.04103179242473</v>
       </c>
       <c r="N28" t="n">
-        <v>183.9160175936601</v>
+        <v>182.9720274281656</v>
       </c>
       <c r="O28" t="n">
-        <v>13.56156398036967</v>
+        <v>13.5267153229513</v>
       </c>
       <c r="P28" t="n">
-        <v>323.0962562450497</v>
+        <v>323.0753755311831</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -24989,28 +25107,28 @@
         <v>0.0527</v>
       </c>
       <c r="I29" t="n">
-        <v>0.2040813837955698</v>
+        <v>0.2024352004996034</v>
       </c>
       <c r="J29" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="K29" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L29" t="n">
-        <v>0.01769780082451611</v>
+        <v>0.01761039070620096</v>
       </c>
       <c r="M29" t="n">
-        <v>10.42628687442475</v>
+        <v>10.38073309130314</v>
       </c>
       <c r="N29" t="n">
-        <v>151.08083252929</v>
+        <v>150.2971934487701</v>
       </c>
       <c r="O29" t="n">
-        <v>12.29149431636731</v>
+        <v>12.25957558191841</v>
       </c>
       <c r="P29" t="n">
-        <v>322.5361897755731</v>
+        <v>322.5515391530946</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
@@ -25067,28 +25185,28 @@
         <v>0.0524</v>
       </c>
       <c r="I30" t="n">
-        <v>0.2376378722855778</v>
+        <v>0.2456595970036245</v>
       </c>
       <c r="J30" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="K30" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L30" t="n">
-        <v>0.02247768994312183</v>
+        <v>0.0241936356996324</v>
       </c>
       <c r="M30" t="n">
-        <v>10.35247220895499</v>
+        <v>10.34045453976388</v>
       </c>
       <c r="N30" t="n">
-        <v>160.5029753547304</v>
+        <v>160.027277680616</v>
       </c>
       <c r="O30" t="n">
-        <v>12.6689768866602</v>
+        <v>12.65018883972156</v>
       </c>
       <c r="P30" t="n">
-        <v>321.5408478130942</v>
+        <v>321.4660514757898</v>
       </c>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr">
@@ -25145,28 +25263,28 @@
         <v>0.0501</v>
       </c>
       <c r="I31" t="n">
-        <v>0.3342192831937316</v>
+        <v>0.3440428707283818</v>
       </c>
       <c r="J31" t="n">
+        <v>189</v>
+      </c>
+      <c r="K31" t="n">
         <v>188</v>
       </c>
-      <c r="K31" t="n">
-        <v>187</v>
-      </c>
       <c r="L31" t="n">
-        <v>0.05037680565217095</v>
+        <v>0.05358290921727604</v>
       </c>
       <c r="M31" t="n">
-        <v>9.221341198028536</v>
+        <v>9.220236589215421</v>
       </c>
       <c r="N31" t="n">
-        <v>137.7716914699894</v>
+        <v>137.6009518776039</v>
       </c>
       <c r="O31" t="n">
-        <v>11.73761864561928</v>
+        <v>11.73034321226808</v>
       </c>
       <c r="P31" t="n">
-        <v>319.3185846157044</v>
+        <v>319.2268506132161</v>
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
@@ -25223,28 +25341,28 @@
         <v>0.0491</v>
       </c>
       <c r="I32" t="n">
-        <v>0.2907041877579874</v>
+        <v>0.2975653753485852</v>
       </c>
       <c r="J32" t="n">
+        <v>189</v>
+      </c>
+      <c r="K32" t="n">
         <v>188</v>
       </c>
-      <c r="K32" t="n">
-        <v>187</v>
-      </c>
       <c r="L32" t="n">
-        <v>0.05091838268484083</v>
+        <v>0.05365412007403714</v>
       </c>
       <c r="M32" t="n">
-        <v>8.063566230094603</v>
+        <v>8.056062453975942</v>
       </c>
       <c r="N32" t="n">
-        <v>103.0641991083393</v>
+        <v>102.7901825300712</v>
       </c>
       <c r="O32" t="n">
-        <v>10.15205393545263</v>
+        <v>10.13854933065235</v>
       </c>
       <c r="P32" t="n">
-        <v>316.8277046124099</v>
+        <v>316.7636339053196</v>
       </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
@@ -25301,28 +25419,28 @@
         <v>0.0427</v>
       </c>
       <c r="I33" t="n">
-        <v>0.2418812270824564</v>
+        <v>0.2462627532195138</v>
       </c>
       <c r="J33" t="n">
+        <v>189</v>
+      </c>
+      <c r="K33" t="n">
         <v>188</v>
       </c>
-      <c r="K33" t="n">
-        <v>187</v>
-      </c>
       <c r="L33" t="n">
-        <v>0.03069494219538293</v>
+        <v>0.03210008767954342</v>
       </c>
       <c r="M33" t="n">
-        <v>8.658201774320839</v>
+        <v>8.639464906835665</v>
       </c>
       <c r="N33" t="n">
-        <v>120.8855194623395</v>
+        <v>120.3543303059941</v>
       </c>
       <c r="O33" t="n">
-        <v>10.99479510779257</v>
+        <v>10.97061212084331</v>
       </c>
       <c r="P33" t="n">
-        <v>315.2390700611919</v>
+        <v>315.1981547715239</v>
       </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
@@ -25360,7 +25478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH189"/>
+  <dimension ref="A1:AH190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57505,7 +57623,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>-34.42440515398195,173.01182477978705</t>
+          <t>-34.4243394147575,173.01167332681214</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -57515,7 +57633,7 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>-34.42572036845346,173.01099672152364</t>
+          <t>-34.425683962564044,173.01091284766366</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
@@ -57565,12 +57683,12 @@
       </c>
       <c r="P189" t="inlineStr">
         <is>
-          <t>-34.432670595282424,173.00784070943843</t>
+          <t>-34.43265747885634,173.00779069334303</t>
         </is>
       </c>
       <c r="Q189" t="inlineStr">
         <is>
-          <t>-34.43337857803596,173.007561033534</t>
+          <t>-34.4333664899516,173.0075074755555</t>
         </is>
       </c>
       <c r="R189" t="inlineStr">
@@ -57654,6 +57772,178 @@
         </is>
       </c>
       <c r="AH189" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:17:21+00:00</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>-34.42302338533627,173.01249955552507</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>-34.42363974555973,173.01199047024988</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>-34.42428815393302,173.01155523029027</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>-34.42500593737578,173.01127983116294</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>-34.42566956757573,173.0108796837667</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>-34.42636181541596,173.0105454792083</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>-34.42705263563937,173.01020799791502</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>-34.427736839283604,173.00985528513084</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>-34.42843586915125,173.00951718235967</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>-34.429140873031145,173.00921247220614</t>
+        </is>
+      </c>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>-34.42982284625885,173.00884602192215</t>
+        </is>
+      </c>
+      <c r="M190" t="inlineStr">
+        <is>
+          <t>-34.43052622331426,173.008563586551</t>
+        </is>
+      </c>
+      <c r="N190" t="inlineStr">
+        <is>
+          <t>-34.43122719551585,173.0082722499385</t>
+        </is>
+      </c>
+      <c r="O190" t="inlineStr">
+        <is>
+          <t>-34.43194565150999,173.0080458094274</t>
+        </is>
+      </c>
+      <c r="P190" t="inlineStr">
+        <is>
+          <t>-34.4326499137714,173.00776184589262</t>
+        </is>
+      </c>
+      <c r="Q190" t="inlineStr">
+        <is>
+          <t>-34.43336146509394,173.0074852122435</t>
+        </is>
+      </c>
+      <c r="R190" t="inlineStr">
+        <is>
+          <t>-34.43409491885964,173.0073133424912</t>
+        </is>
+      </c>
+      <c r="S190" t="inlineStr">
+        <is>
+          <t>-34.43480208499793,173.00703624459678</t>
+        </is>
+      </c>
+      <c r="T190" t="inlineStr">
+        <is>
+          <t>-34.43552442531159,173.00683623731007</t>
+        </is>
+      </c>
+      <c r="U190" t="inlineStr">
+        <is>
+          <t>-34.43624640493298,173.00663442992288</t>
+        </is>
+      </c>
+      <c r="V190" t="inlineStr">
+        <is>
+          <t>-34.43697517630353,173.00646714506624</t>
+        </is>
+      </c>
+      <c r="W190" t="inlineStr">
+        <is>
+          <t>-34.437698895181335,173.00627423359725</t>
+        </is>
+      </c>
+      <c r="X190" t="inlineStr">
+        <is>
+          <t>-34.438428029037496,173.0060920393364</t>
+        </is>
+      </c>
+      <c r="Y190" t="inlineStr">
+        <is>
+          <t>-34.43915089202906,173.00583753949735</t>
+        </is>
+      </c>
+      <c r="Z190" t="inlineStr">
+        <is>
+          <t>-34.43989016954818,173.005710696638</t>
+        </is>
+      </c>
+      <c r="AA190" t="inlineStr">
+        <is>
+          <t>-34.4406176356441,173.00551980725865</t>
+        </is>
+      </c>
+      <c r="AB190" t="inlineStr">
+        <is>
+          <t>-34.441351790841,173.00539811157367</t>
+        </is>
+      </c>
+      <c r="AC190" t="inlineStr">
+        <is>
+          <t>-34.442081472197444,173.00523024902952</t>
+        </is>
+      </c>
+      <c r="AD190" t="inlineStr">
+        <is>
+          <t>-34.44282786558406,173.00523516010693</t>
+        </is>
+      </c>
+      <c r="AE190" t="inlineStr">
+        <is>
+          <t>-34.44357045857922,173.00515448776963</t>
+        </is>
+      </c>
+      <c r="AF190" t="inlineStr">
+        <is>
+          <t>-34.444310264504615,173.00500954472804</t>
+        </is>
+      </c>
+      <c r="AG190" t="inlineStr">
+        <is>
+          <t>-34.445047959652456,173.004889795394</t>
+        </is>
+      </c>
+      <c r="AH190" t="inlineStr">
         <is>
           <t>L9</t>
         </is>

--- a/data/nzd0003/nzd0003.xlsx
+++ b/data/nzd0003/nzd0003.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH190"/>
+  <dimension ref="A1:AH191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20909,6 +20909,114 @@
         </is>
       </c>
     </row>
+    <row r="191">
+      <c r="A191" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:17:05+00:00</t>
+        </is>
+      </c>
+      <c r="B191" t="n">
+        <v>312.89</v>
+      </c>
+      <c r="C191" t="n">
+        <v>305.32</v>
+      </c>
+      <c r="D191" t="n">
+        <v>301.3</v>
+      </c>
+      <c r="E191" t="n">
+        <v>314.5</v>
+      </c>
+      <c r="F191" t="n">
+        <v>316.1</v>
+      </c>
+      <c r="G191" t="n">
+        <v>324.8</v>
+      </c>
+      <c r="H191" t="n">
+        <v>333.77</v>
+      </c>
+      <c r="I191" t="n">
+        <v>341.62</v>
+      </c>
+      <c r="J191" t="n">
+        <v>350.64</v>
+      </c>
+      <c r="K191" t="n">
+        <v>349.43</v>
+      </c>
+      <c r="L191" t="n">
+        <v>342.05</v>
+      </c>
+      <c r="M191" t="n">
+        <v>339.93</v>
+      </c>
+      <c r="N191" t="n">
+        <v>340.72</v>
+      </c>
+      <c r="O191" t="n">
+        <v>347.24</v>
+      </c>
+      <c r="P191" t="n">
+        <v>344.59</v>
+      </c>
+      <c r="Q191" t="n">
+        <v>345.59</v>
+      </c>
+      <c r="R191" t="n">
+        <v>347.21</v>
+      </c>
+      <c r="S191" t="n">
+        <v>339.16</v>
+      </c>
+      <c r="T191" t="n">
+        <v>341.66</v>
+      </c>
+      <c r="U191" t="n">
+        <v>344.26</v>
+      </c>
+      <c r="V191" t="n">
+        <v>346.15</v>
+      </c>
+      <c r="W191" t="n">
+        <v>347.36</v>
+      </c>
+      <c r="X191" t="n">
+        <v>351.12</v>
+      </c>
+      <c r="Y191" t="n">
+        <v>342.36</v>
+      </c>
+      <c r="Z191" t="n">
+        <v>338.14</v>
+      </c>
+      <c r="AA191" t="n">
+        <v>331.58</v>
+      </c>
+      <c r="AB191" t="n">
+        <v>329.62</v>
+      </c>
+      <c r="AC191" t="n">
+        <v>324.53</v>
+      </c>
+      <c r="AD191" t="n">
+        <v>333.17</v>
+      </c>
+      <c r="AE191" t="n">
+        <v>333.17</v>
+      </c>
+      <c r="AF191" t="n">
+        <v>328.32</v>
+      </c>
+      <c r="AG191" t="n">
+        <v>322.16</v>
+      </c>
+      <c r="AH191" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -20920,7 +21028,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B191"/>
+  <dimension ref="A1:B192"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22833,6 +22941,16 @@
       </c>
       <c r="B191" t="n">
         <v>0.78</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B192" t="n">
+        <v>-0.28</v>
       </c>
     </row>
   </sheetData>
@@ -23001,28 +23119,28 @@
         <v>0.0366</v>
       </c>
       <c r="I2" t="n">
-        <v>1.018557168695772</v>
+        <v>0.9971653193637229</v>
       </c>
       <c r="J2" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="K2" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2274297121408498</v>
+        <v>0.2199314814476165</v>
       </c>
       <c r="M2" t="n">
-        <v>12.42412546563767</v>
+        <v>12.46792670377295</v>
       </c>
       <c r="N2" t="n">
-        <v>230.4988808405194</v>
+        <v>231.9522530511682</v>
       </c>
       <c r="O2" t="n">
-        <v>15.18218959308964</v>
+        <v>15.22997876069327</v>
       </c>
       <c r="P2" t="n">
-        <v>308.1652473114726</v>
+        <v>308.3684806087908</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -23079,28 +23197,28 @@
         <v>0.0328</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9997065250999205</v>
+        <v>0.9751919787396414</v>
       </c>
       <c r="J3" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="K3" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2181953599558012</v>
+        <v>0.2092011224369252</v>
       </c>
       <c r="M3" t="n">
-        <v>12.19218572739411</v>
+        <v>12.25494282186555</v>
       </c>
       <c r="N3" t="n">
-        <v>236.54828663443</v>
+        <v>238.8100623316552</v>
       </c>
       <c r="O3" t="n">
-        <v>15.38012635300601</v>
+        <v>15.45348058955183</v>
       </c>
       <c r="P3" t="n">
-        <v>304.300842406868</v>
+        <v>304.531288793385</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -23157,28 +23275,28 @@
         <v>0.0287</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3826333246174325</v>
+        <v>0.3582666790996489</v>
       </c>
       <c r="J4" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="K4" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03283207926067722</v>
+        <v>0.0288645185820201</v>
       </c>
       <c r="M4" t="n">
-        <v>13.29863493402095</v>
+        <v>13.37697907998319</v>
       </c>
       <c r="N4" t="n">
-        <v>279.1916153925064</v>
+        <v>281.1527840251486</v>
       </c>
       <c r="O4" t="n">
-        <v>16.70902796073148</v>
+        <v>16.76761116036356</v>
       </c>
       <c r="P4" t="n">
-        <v>316.6705612353571</v>
+        <v>316.9025773911525</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -23235,28 +23353,28 @@
         <v>0.035</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8689536328171266</v>
+        <v>0.8516532852554222</v>
       </c>
       <c r="J5" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="K5" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1759136314795609</v>
+        <v>0.1707273409613249</v>
       </c>
       <c r="M5" t="n">
-        <v>12.52339981394575</v>
+        <v>12.54517305729185</v>
       </c>
       <c r="N5" t="n">
-        <v>231.7112699395491</v>
+        <v>232.1599691132939</v>
       </c>
       <c r="O5" t="n">
-        <v>15.22206523240356</v>
+        <v>15.23679655023633</v>
       </c>
       <c r="P5" t="n">
-        <v>309.1665379804207</v>
+        <v>309.3287947265128</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -23313,28 +23431,28 @@
         <v>0.0321</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6640615992587874</v>
+        <v>0.6458573382370429</v>
       </c>
       <c r="J6" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="K6" t="n">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L6" t="n">
-        <v>0.11875494244818</v>
+        <v>0.1132552178237946</v>
       </c>
       <c r="M6" t="n">
-        <v>11.73640403787185</v>
+        <v>11.76138643659166</v>
       </c>
       <c r="N6" t="n">
-        <v>214.3492860756756</v>
+        <v>215.1665836268247</v>
       </c>
       <c r="O6" t="n">
-        <v>14.64067232321233</v>
+        <v>14.6685576532536</v>
       </c>
       <c r="P6" t="n">
-        <v>317.7080923590844</v>
+        <v>317.8790429038144</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -23391,28 +23509,28 @@
         <v>0.034</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4209188054675195</v>
+        <v>0.4097895938165086</v>
       </c>
       <c r="J7" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="K7" t="n">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L7" t="n">
-        <v>0.05605255043793489</v>
+        <v>0.05365474627440769</v>
       </c>
       <c r="M7" t="n">
-        <v>11.06627254112261</v>
+        <v>11.05733587759864</v>
       </c>
       <c r="N7" t="n">
-        <v>195.4381776190958</v>
+        <v>195.1302135428673</v>
       </c>
       <c r="O7" t="n">
-        <v>13.97992051547847</v>
+        <v>13.96890165842924</v>
       </c>
       <c r="P7" t="n">
-        <v>325.381166485556</v>
+        <v>325.4856774454836</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -23469,28 +23587,28 @@
         <v>0.0439</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4578495427262779</v>
+        <v>0.4501644210492381</v>
       </c>
       <c r="J8" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="K8" t="n">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L8" t="n">
-        <v>0.09268122585284877</v>
+        <v>0.090569819789596</v>
       </c>
       <c r="M8" t="n">
-        <v>8.941225301773576</v>
+        <v>8.934027811591408</v>
       </c>
       <c r="N8" t="n">
-        <v>134.423130178379</v>
+        <v>134.0569700161001</v>
       </c>
       <c r="O8" t="n">
-        <v>11.59409893775187</v>
+        <v>11.57829737120705</v>
       </c>
       <c r="P8" t="n">
-        <v>329.7075444513451</v>
+        <v>329.779713035142</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -23547,28 +23665,28 @@
         <v>0.0436</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4604924927843893</v>
+        <v>0.4536796330205989</v>
       </c>
       <c r="J9" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="K9" t="n">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1109298099046184</v>
+        <v>0.1088569845387386</v>
       </c>
       <c r="M9" t="n">
-        <v>8.107224512901173</v>
+        <v>8.094492658010058</v>
       </c>
       <c r="N9" t="n">
-        <v>111.3251260968408</v>
+        <v>111.007131243677</v>
       </c>
       <c r="O9" t="n">
-        <v>10.55107227237312</v>
+        <v>10.53599218126499</v>
       </c>
       <c r="P9" t="n">
-        <v>336.5668900999889</v>
+        <v>336.6308675438631</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -23625,28 +23743,28 @@
         <v>0.0433</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5602783508103556</v>
+        <v>0.5543514903582465</v>
       </c>
       <c r="J10" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="K10" t="n">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1269095925214568</v>
+        <v>0.1256242014006186</v>
       </c>
       <c r="M10" t="n">
-        <v>8.794158896375306</v>
+        <v>8.778374841885176</v>
       </c>
       <c r="N10" t="n">
-        <v>141.4597078836924</v>
+        <v>140.9147514541727</v>
       </c>
       <c r="O10" t="n">
-        <v>11.89368352881867</v>
+        <v>11.8707519329726</v>
       </c>
       <c r="P10" t="n">
-        <v>341.9796376887416</v>
+        <v>342.0352949890636</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -23703,28 +23821,28 @@
         <v>0.0418</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6026943073167302</v>
+        <v>0.5992178377512493</v>
       </c>
       <c r="J11" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="K11" t="n">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1479741124063532</v>
+        <v>0.1478478680276619</v>
       </c>
       <c r="M11" t="n">
-        <v>9.220073280565309</v>
+        <v>9.195459661343035</v>
       </c>
       <c r="N11" t="n">
-        <v>137.0003044344896</v>
+        <v>136.3429669106039</v>
       </c>
       <c r="O11" t="n">
-        <v>11.70471291550927</v>
+        <v>11.6765991157787</v>
       </c>
       <c r="P11" t="n">
-        <v>337.028675607925</v>
+        <v>337.0613220507137</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -23781,28 +23899,28 @@
         <v>0.0421</v>
       </c>
       <c r="I12" t="n">
-        <v>0.622357699094974</v>
+        <v>0.6158482026371855</v>
       </c>
       <c r="J12" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="K12" t="n">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1503720454496383</v>
+        <v>0.1488845111731957</v>
       </c>
       <c r="M12" t="n">
-        <v>9.399525041161157</v>
+        <v>9.393328827991997</v>
       </c>
       <c r="N12" t="n">
-        <v>143.3514616689229</v>
+        <v>142.8392419343999</v>
       </c>
       <c r="O12" t="n">
-        <v>11.97294707534126</v>
+        <v>11.9515372205587</v>
       </c>
       <c r="P12" t="n">
-        <v>332.3461843831307</v>
+        <v>332.4073130366942</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -23859,28 +23977,28 @@
         <v>0.0429</v>
       </c>
       <c r="I13" t="n">
-        <v>0.6789585344627238</v>
+        <v>0.6745947802735121</v>
       </c>
       <c r="J13" t="n">
+        <v>190</v>
+      </c>
+      <c r="K13" t="n">
         <v>189</v>
       </c>
-      <c r="K13" t="n">
-        <v>188</v>
-      </c>
       <c r="L13" t="n">
-        <v>0.2270251532205581</v>
+        <v>0.2265113931250901</v>
       </c>
       <c r="M13" t="n">
-        <v>8.065721606772868</v>
+        <v>8.051486142438181</v>
       </c>
       <c r="N13" t="n">
-        <v>103.736719717888</v>
+        <v>103.3015914577586</v>
       </c>
       <c r="O13" t="n">
-        <v>10.18512246945946</v>
+        <v>10.16373904907828</v>
       </c>
       <c r="P13" t="n">
-        <v>326.4784480281754</v>
+        <v>326.5190457287676</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -23937,28 +24055,28 @@
         <v>0.0448</v>
       </c>
       <c r="I14" t="n">
-        <v>0.6118310882745359</v>
+        <v>0.6100634400508747</v>
       </c>
       <c r="J14" t="n">
+        <v>190</v>
+      </c>
+      <c r="K14" t="n">
         <v>189</v>
       </c>
-      <c r="K14" t="n">
-        <v>188</v>
-      </c>
       <c r="L14" t="n">
-        <v>0.2002381840010811</v>
+        <v>0.2010547124453093</v>
       </c>
       <c r="M14" t="n">
-        <v>7.898855142292204</v>
+        <v>7.868151298850494</v>
       </c>
       <c r="N14" t="n">
-        <v>98.81695596915473</v>
+        <v>98.31277859360326</v>
       </c>
       <c r="O14" t="n">
-        <v>9.940671806731913</v>
+        <v>9.915280056236599</v>
       </c>
       <c r="P14" t="n">
-        <v>326.2751298877338</v>
+        <v>326.2915750059107</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -24015,28 +24133,28 @@
         <v>0.0419</v>
       </c>
       <c r="I15" t="n">
-        <v>0.6712455796545249</v>
+        <v>0.6753622076929993</v>
       </c>
       <c r="J15" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="K15" t="n">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L15" t="n">
-        <v>0.214686159924209</v>
+        <v>0.2184755125822572</v>
       </c>
       <c r="M15" t="n">
-        <v>8.185569669940159</v>
+        <v>8.161357954328027</v>
       </c>
       <c r="N15" t="n">
-        <v>109.0552409519068</v>
+        <v>108.5767338406031</v>
       </c>
       <c r="O15" t="n">
-        <v>10.44295173559213</v>
+        <v>10.42001601921048</v>
       </c>
       <c r="P15" t="n">
-        <v>324.9122538190752</v>
+        <v>324.8738984362885</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -24093,28 +24211,28 @@
         <v>0.0442</v>
       </c>
       <c r="I16" t="n">
-        <v>0.7217558222052944</v>
+        <v>0.7240099249437086</v>
       </c>
       <c r="J16" t="n">
+        <v>190</v>
+      </c>
+      <c r="K16" t="n">
         <v>189</v>
       </c>
-      <c r="K16" t="n">
-        <v>188</v>
-      </c>
       <c r="L16" t="n">
-        <v>0.228902471150169</v>
+        <v>0.2319183716436549</v>
       </c>
       <c r="M16" t="n">
-        <v>8.754588744295239</v>
+        <v>8.717089489432906</v>
       </c>
       <c r="N16" t="n">
-        <v>115.4993259169202</v>
+        <v>114.9185279640571</v>
       </c>
       <c r="O16" t="n">
-        <v>10.74706126887347</v>
+        <v>10.72000596847115</v>
       </c>
       <c r="P16" t="n">
-        <v>322.9106846229318</v>
+        <v>322.8896119191474</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -24171,28 +24289,28 @@
         <v>0.0482</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6725185091356386</v>
+        <v>0.6756780208696173</v>
       </c>
       <c r="J17" t="n">
+        <v>190</v>
+      </c>
+      <c r="K17" t="n">
         <v>189</v>
       </c>
-      <c r="K17" t="n">
-        <v>188</v>
-      </c>
       <c r="L17" t="n">
-        <v>0.2215256503607116</v>
+        <v>0.2249655719378464</v>
       </c>
       <c r="M17" t="n">
-        <v>8.345898098438255</v>
+        <v>8.314752152705454</v>
       </c>
       <c r="N17" t="n">
-        <v>104.6089391331936</v>
+        <v>104.1150014283743</v>
       </c>
       <c r="O17" t="n">
-        <v>10.22785114934675</v>
+        <v>10.20367587824968</v>
       </c>
       <c r="P17" t="n">
-        <v>324.2488942345531</v>
+        <v>324.219357224665</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -24249,28 +24367,28 @@
         <v>0.0524</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6197737750431406</v>
+        <v>0.628073958371501</v>
       </c>
       <c r="J18" t="n">
+        <v>190</v>
+      </c>
+      <c r="K18" t="n">
         <v>189</v>
       </c>
-      <c r="K18" t="n">
-        <v>188</v>
-      </c>
       <c r="L18" t="n">
-        <v>0.1477071209538702</v>
+        <v>0.152143847669772</v>
       </c>
       <c r="M18" t="n">
-        <v>10.47821351010291</v>
+        <v>10.45771320785136</v>
       </c>
       <c r="N18" t="n">
-        <v>145.8793587947225</v>
+        <v>145.5184783688327</v>
       </c>
       <c r="O18" t="n">
-        <v>12.07805277330425</v>
+        <v>12.06310401052866</v>
       </c>
       <c r="P18" t="n">
-        <v>321.7818087499231</v>
+        <v>321.7042136600215</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -24327,28 +24445,28 @@
         <v>0.05</v>
       </c>
       <c r="I19" t="n">
-        <v>0.46528002358129</v>
+        <v>0.4709802724078025</v>
       </c>
       <c r="J19" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="K19" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1041260827185956</v>
+        <v>0.1073244249127453</v>
       </c>
       <c r="M19" t="n">
-        <v>9.217921708676785</v>
+        <v>9.197794561203313</v>
       </c>
       <c r="N19" t="n">
-        <v>122.4560407561861</v>
+        <v>122.0047119353752</v>
       </c>
       <c r="O19" t="n">
-        <v>11.06598575618937</v>
+        <v>11.04557431442002</v>
       </c>
       <c r="P19" t="n">
-        <v>320.6292052672611</v>
+        <v>320.5759956964715</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -24405,28 +24523,28 @@
         <v>0.0506</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3436391252966623</v>
+        <v>0.3532488433242227</v>
       </c>
       <c r="J20" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="K20" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L20" t="n">
-        <v>0.06041046279721252</v>
+        <v>0.06400682583232098</v>
       </c>
       <c r="M20" t="n">
-        <v>9.091499039231525</v>
+        <v>9.090842714289636</v>
       </c>
       <c r="N20" t="n">
-        <v>120.7522569417921</v>
+        <v>120.6657389267094</v>
       </c>
       <c r="O20" t="n">
-        <v>10.98873318184549</v>
+        <v>10.98479580723781</v>
       </c>
       <c r="P20" t="n">
-        <v>322.1894754768084</v>
+        <v>322.0997725555469</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -24483,28 +24601,28 @@
         <v>0.0544</v>
       </c>
       <c r="I21" t="n">
-        <v>0.4991111424752181</v>
+        <v>0.5090099851349249</v>
       </c>
       <c r="J21" t="n">
+        <v>190</v>
+      </c>
+      <c r="K21" t="n">
         <v>189</v>
       </c>
-      <c r="K21" t="n">
-        <v>188</v>
-      </c>
       <c r="L21" t="n">
-        <v>0.122142221929654</v>
+        <v>0.127087502673446</v>
       </c>
       <c r="M21" t="n">
-        <v>8.85007313971199</v>
+        <v>8.848449429931572</v>
       </c>
       <c r="N21" t="n">
-        <v>117.8400461323099</v>
+        <v>117.8010767040697</v>
       </c>
       <c r="O21" t="n">
-        <v>10.85541552094207</v>
+        <v>10.85362044223354</v>
       </c>
       <c r="P21" t="n">
-        <v>320.3403766628542</v>
+        <v>320.2478363470906</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -24561,28 +24679,28 @@
         <v>0.0505</v>
       </c>
       <c r="I22" t="n">
-        <v>0.3568898552945929</v>
+        <v>0.3682541297772334</v>
       </c>
       <c r="J22" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="K22" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0512217784113842</v>
+        <v>0.0546699070959592</v>
       </c>
       <c r="M22" t="n">
-        <v>10.24146833850001</v>
+        <v>10.23314073621387</v>
       </c>
       <c r="N22" t="n">
-        <v>155.1109644855123</v>
+        <v>155.0623951248661</v>
       </c>
       <c r="O22" t="n">
-        <v>12.45435524166194</v>
+        <v>12.45240519437374</v>
       </c>
       <c r="P22" t="n">
-        <v>324.4406110181033</v>
+        <v>324.334530005509</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -24639,28 +24757,28 @@
         <v>0.0567</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3554944018486785</v>
+        <v>0.3659814303932641</v>
       </c>
       <c r="J23" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="K23" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L23" t="n">
-        <v>0.05189411120115783</v>
+        <v>0.05518102809408765</v>
       </c>
       <c r="M23" t="n">
-        <v>9.801140992580509</v>
+        <v>9.8043770305491</v>
       </c>
       <c r="N23" t="n">
-        <v>151.7987990832359</v>
+        <v>151.6536986864627</v>
       </c>
       <c r="O23" t="n">
-        <v>12.32066552923323</v>
+        <v>12.31477562469015</v>
       </c>
       <c r="P23" t="n">
-        <v>326.6345391819769</v>
+        <v>326.5366469136393</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -24717,28 +24835,28 @@
         <v>0.0536</v>
       </c>
       <c r="I24" t="n">
-        <v>0.4575529972898271</v>
+        <v>0.466882099237251</v>
       </c>
       <c r="J24" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="K24" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L24" t="n">
-        <v>0.09026564807315807</v>
+        <v>0.09425883376802457</v>
       </c>
       <c r="M24" t="n">
-        <v>9.422283400872054</v>
+        <v>9.420608505612627</v>
       </c>
       <c r="N24" t="n">
-        <v>138.719954138679</v>
+        <v>138.5072732684111</v>
       </c>
       <c r="O24" t="n">
-        <v>11.77794354455306</v>
+        <v>11.76891130344736</v>
       </c>
       <c r="P24" t="n">
-        <v>328.905387517515</v>
+        <v>328.8183040364981</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -24795,28 +24913,28 @@
         <v>0.0562</v>
       </c>
       <c r="I25" t="n">
-        <v>0.2548653714095911</v>
+        <v>0.2588445508208134</v>
       </c>
       <c r="J25" t="n">
+        <v>190</v>
+      </c>
+      <c r="K25" t="n">
         <v>189</v>
       </c>
-      <c r="K25" t="n">
-        <v>188</v>
-      </c>
       <c r="L25" t="n">
-        <v>0.02603644316106291</v>
+        <v>0.0271078437259582</v>
       </c>
       <c r="M25" t="n">
-        <v>10.35556846244113</v>
+        <v>10.32387761766466</v>
       </c>
       <c r="N25" t="n">
-        <v>159.9273508524098</v>
+        <v>159.1756282536004</v>
       </c>
       <c r="O25" t="n">
-        <v>12.64623860491371</v>
+        <v>12.61648240412518</v>
       </c>
       <c r="P25" t="n">
-        <v>331.2954178105782</v>
+        <v>331.2582180558338</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -24873,28 +24991,28 @@
         <v>0.064</v>
       </c>
       <c r="I26" t="n">
-        <v>0.2441682737150462</v>
+        <v>0.2478045357505466</v>
       </c>
       <c r="J26" t="n">
+        <v>190</v>
+      </c>
+      <c r="K26" t="n">
         <v>189</v>
       </c>
-      <c r="K26" t="n">
-        <v>188</v>
-      </c>
       <c r="L26" t="n">
-        <v>0.01974178114496672</v>
+        <v>0.0205364237417387</v>
       </c>
       <c r="M26" t="n">
-        <v>11.35543659449458</v>
+        <v>11.31020471985534</v>
       </c>
       <c r="N26" t="n">
-        <v>195.4236838850844</v>
+        <v>194.4682641436898</v>
       </c>
       <c r="O26" t="n">
-        <v>13.97940212902842</v>
+        <v>13.94518784899256</v>
       </c>
       <c r="P26" t="n">
-        <v>327.7322421480383</v>
+        <v>327.6984216330348</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -24951,28 +25069,28 @@
         <v>0.0554</v>
       </c>
       <c r="I27" t="n">
-        <v>0.3686644184148316</v>
+        <v>0.3693685991902713</v>
       </c>
       <c r="J27" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="K27" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L27" t="n">
-        <v>0.03699726470059683</v>
+        <v>0.03753054432499314</v>
       </c>
       <c r="M27" t="n">
-        <v>12.11990282578515</v>
+        <v>12.05823929526886</v>
       </c>
       <c r="N27" t="n">
-        <v>232.5864388163698</v>
+        <v>231.3652477181114</v>
       </c>
       <c r="O27" t="n">
-        <v>15.2507848590284</v>
+        <v>15.21069517537287</v>
       </c>
       <c r="P27" t="n">
-        <v>320.987279240577</v>
+        <v>320.9807059912401</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -25029,28 +25147,28 @@
         <v>0.0452</v>
       </c>
       <c r="I28" t="n">
-        <v>0.2513105458648702</v>
+        <v>0.2511532207724638</v>
       </c>
       <c r="J28" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="K28" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L28" t="n">
-        <v>0.02218989691075723</v>
+        <v>0.02240370698755845</v>
       </c>
       <c r="M28" t="n">
-        <v>11.04103179242473</v>
+        <v>10.98385605488961</v>
       </c>
       <c r="N28" t="n">
-        <v>182.9720274281656</v>
+        <v>182.0091639084203</v>
       </c>
       <c r="O28" t="n">
-        <v>13.5267153229513</v>
+        <v>13.4910771959996</v>
       </c>
       <c r="P28" t="n">
-        <v>323.0753755311831</v>
+        <v>323.076844098766</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -25107,28 +25225,28 @@
         <v>0.0527</v>
       </c>
       <c r="I29" t="n">
-        <v>0.2024352004996034</v>
+        <v>0.1992390553576117</v>
       </c>
       <c r="J29" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="K29" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L29" t="n">
-        <v>0.01761039070620096</v>
+        <v>0.0172477959625813</v>
       </c>
       <c r="M29" t="n">
-        <v>10.38073309130314</v>
+        <v>10.34462898808</v>
       </c>
       <c r="N29" t="n">
-        <v>150.2971934487701</v>
+        <v>149.56688792706</v>
       </c>
       <c r="O29" t="n">
-        <v>12.25957558191841</v>
+        <v>12.2297542055047</v>
       </c>
       <c r="P29" t="n">
-        <v>322.5515391530946</v>
+        <v>322.5813739052892</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
@@ -25185,28 +25303,28 @@
         <v>0.0524</v>
       </c>
       <c r="I30" t="n">
-        <v>0.2456595970036245</v>
+        <v>0.2504573255192607</v>
       </c>
       <c r="J30" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="K30" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L30" t="n">
-        <v>0.0241936356996324</v>
+        <v>0.02537497999679217</v>
       </c>
       <c r="M30" t="n">
-        <v>10.34045453976388</v>
+        <v>10.3114189634408</v>
       </c>
       <c r="N30" t="n">
-        <v>160.027277680616</v>
+        <v>159.3218768198685</v>
       </c>
       <c r="O30" t="n">
-        <v>12.65018883972156</v>
+        <v>12.62227700614546</v>
       </c>
       <c r="P30" t="n">
-        <v>321.4660514757898</v>
+        <v>321.4212665755421</v>
       </c>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr">
@@ -25263,28 +25381,28 @@
         <v>0.0501</v>
       </c>
       <c r="I31" t="n">
-        <v>0.3440428707283818</v>
+        <v>0.3484868427528738</v>
       </c>
       <c r="J31" t="n">
+        <v>190</v>
+      </c>
+      <c r="K31" t="n">
         <v>189</v>
       </c>
-      <c r="K31" t="n">
-        <v>188</v>
-      </c>
       <c r="L31" t="n">
-        <v>0.05358290921727604</v>
+        <v>0.05542996464205929</v>
       </c>
       <c r="M31" t="n">
-        <v>9.220236589215421</v>
+        <v>9.193316693837501</v>
       </c>
       <c r="N31" t="n">
-        <v>137.6009518776039</v>
+        <v>136.9907126547466</v>
       </c>
       <c r="O31" t="n">
-        <v>11.73034321226808</v>
+        <v>11.70430316826878</v>
       </c>
       <c r="P31" t="n">
-        <v>319.2268506132161</v>
+        <v>319.1853056984692</v>
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
@@ -25341,28 +25459,28 @@
         <v>0.0491</v>
       </c>
       <c r="I32" t="n">
-        <v>0.2975653753485852</v>
+        <v>0.3009427121315297</v>
       </c>
       <c r="J32" t="n">
+        <v>190</v>
+      </c>
+      <c r="K32" t="n">
         <v>189</v>
       </c>
-      <c r="K32" t="n">
-        <v>188</v>
-      </c>
       <c r="L32" t="n">
-        <v>0.05365412007403714</v>
+        <v>0.05535158389618755</v>
       </c>
       <c r="M32" t="n">
-        <v>8.056062453975942</v>
+        <v>8.030728435171522</v>
       </c>
       <c r="N32" t="n">
-        <v>102.7901825300712</v>
+        <v>102.3143618106783</v>
       </c>
       <c r="O32" t="n">
-        <v>10.13854933065235</v>
+        <v>10.11505619414338</v>
       </c>
       <c r="P32" t="n">
-        <v>316.7636339053196</v>
+        <v>316.7320605362827</v>
       </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
@@ -25419,28 +25537,28 @@
         <v>0.0427</v>
       </c>
       <c r="I33" t="n">
-        <v>0.2462627532195138</v>
+        <v>0.246625891695572</v>
       </c>
       <c r="J33" t="n">
+        <v>190</v>
+      </c>
+      <c r="K33" t="n">
         <v>189</v>
       </c>
-      <c r="K33" t="n">
-        <v>188</v>
-      </c>
       <c r="L33" t="n">
-        <v>0.03210008767954342</v>
+        <v>0.03253717146140123</v>
       </c>
       <c r="M33" t="n">
-        <v>8.639464906835665</v>
+        <v>8.596002626604479</v>
       </c>
       <c r="N33" t="n">
-        <v>120.3543303059941</v>
+        <v>119.7183215496864</v>
       </c>
       <c r="O33" t="n">
-        <v>10.97061212084331</v>
+        <v>10.9415867930427</v>
       </c>
       <c r="P33" t="n">
-        <v>315.1981547715239</v>
+        <v>315.1947599353398</v>
       </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
@@ -25478,7 +25596,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH190"/>
+  <dimension ref="A1:AH191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57949,6 +58067,178 @@
         </is>
       </c>
     </row>
+    <row r="191">
+      <c r="A191" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:17:05+00:00</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>-34.423010538882856,173.01246995945945</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>-34.42363501702963,173.01197957652337</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>-34.42427434487502,173.011523416558</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>-34.42498572588695,173.01123326706403</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>-34.42564856091963,173.01083128763509</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>-34.4263411016107,173.01049775757585</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>-34.4270347673059,173.01016683168206</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>-34.42772374137057,173.00982510919889</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>-34.42842588643724,173.00948942801858</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>-34.4291304929361,173.00917534761706</t>
+        </is>
+      </c>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>-34.4298158448816,173.00882004331143</t>
+        </is>
+      </c>
+      <c r="M191" t="inlineStr">
+        <is>
+          <t>-34.43051442411252,173.00851980552608</t>
+        </is>
+      </c>
+      <c r="N191" t="inlineStr">
+        <is>
+          <t>-34.43122111457031,173.0082496864921</t>
+        </is>
+      </c>
+      <c r="O191" t="inlineStr">
+        <is>
+          <t>-34.43194378258889,173.00803887473336</t>
+        </is>
+      </c>
+      <c r="P191" t="inlineStr">
+        <is>
+          <t>-34.432642239829356,173.00773258337628</t>
+        </is>
+      </c>
+      <c r="Q191" t="inlineStr">
+        <is>
+          <t>-34.4333593556006,173.00747586585388</t>
+        </is>
+      </c>
+      <c r="R191" t="inlineStr">
+        <is>
+          <t>-34.434088975998975,173.00728316283804</t>
+        </is>
+      </c>
+      <c r="S191" t="inlineStr">
+        <is>
+          <t>-34.43479295168005,173.00698986286838</t>
+        </is>
+      </c>
+      <c r="T191" t="inlineStr">
+        <is>
+          <t>-34.43551892027181,173.00680828096637</t>
+        </is>
+      </c>
+      <c r="U191" t="inlineStr">
+        <is>
+          <t>-34.43624509122402,173.00662775846698</t>
+        </is>
+      </c>
+      <c r="V191" t="inlineStr">
+        <is>
+          <t>-34.43696977547722,173.00643971773906</t>
+        </is>
+      </c>
+      <c r="W191" t="inlineStr">
+        <is>
+          <t>-34.437693035568834,173.00624447628766</t>
+        </is>
+      </c>
+      <c r="X191" t="inlineStr">
+        <is>
+          <t>-34.438425142240405,173.0060751979055</t>
+        </is>
+      </c>
+      <c r="Y191" t="inlineStr">
+        <is>
+          <t>-34.43914914082569,173.0058231076163</t>
+        </is>
+      </c>
+      <c r="Z191" t="inlineStr">
+        <is>
+          <t>-34.439886434662185,173.00567209936187</t>
+        </is>
+      </c>
+      <c r="AA191" t="inlineStr">
+        <is>
+          <t>-34.440615407239434,173.00549677843583</t>
+        </is>
+      </c>
+      <c r="AB191" t="inlineStr">
+        <is>
+          <t>-34.44134918578574,173.0053711903227</t>
+        </is>
+      </c>
+      <c r="AC191" t="inlineStr">
+        <is>
+          <t>-34.4420796831646,173.0052117607834</t>
+        </is>
+      </c>
+      <c r="AD191" t="inlineStr">
+        <is>
+          <t>-34.442824538620556,173.00520077814943</t>
+        </is>
+      </c>
+      <c r="AE191" t="inlineStr">
+        <is>
+          <t>-34.44356569329924,173.00509565986658</t>
+        </is>
+      </c>
+      <c r="AF191" t="inlineStr">
+        <is>
+          <t>-34.444307976788004,173.0049715452361</t>
+        </is>
+      </c>
+      <c r="AG191" t="inlineStr">
+        <is>
+          <t>-34.44504547523821,173.00484471928925</t>
+        </is>
+      </c>
+      <c r="AH191" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0003/nzd0003.xlsx
+++ b/data/nzd0003/nzd0003.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH191"/>
+  <dimension ref="A1:AH193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21017,6 +21017,222 @@
         </is>
       </c>
     </row>
+    <row r="192">
+      <c r="A192" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:16:51+00:00</t>
+        </is>
+      </c>
+      <c r="B192" t="n">
+        <v>307.38</v>
+      </c>
+      <c r="C192" t="n">
+        <v>302.31</v>
+      </c>
+      <c r="D192" t="n">
+        <v>301.3</v>
+      </c>
+      <c r="E192" t="n">
+        <v>310.77</v>
+      </c>
+      <c r="F192" t="n">
+        <v>311.58</v>
+      </c>
+      <c r="G192" t="n">
+        <v>317.98</v>
+      </c>
+      <c r="H192" t="n">
+        <v>329.59</v>
+      </c>
+      <c r="I192" t="n">
+        <v>337.76</v>
+      </c>
+      <c r="J192" t="n">
+        <v>348.64</v>
+      </c>
+      <c r="K192" t="n">
+        <v>344.53</v>
+      </c>
+      <c r="L192" t="n">
+        <v>337.39</v>
+      </c>
+      <c r="M192" t="n">
+        <v>337.17</v>
+      </c>
+      <c r="N192" t="n">
+        <v>336.06</v>
+      </c>
+      <c r="O192" t="n">
+        <v>344.81</v>
+      </c>
+      <c r="P192" t="n">
+        <v>344.75</v>
+      </c>
+      <c r="Q192" t="n">
+        <v>344.87</v>
+      </c>
+      <c r="R192" t="n">
+        <v>342.55</v>
+      </c>
+      <c r="S192" t="n">
+        <v>335.73</v>
+      </c>
+      <c r="T192" t="n">
+        <v>337.53</v>
+      </c>
+      <c r="U192" t="n">
+        <v>338.62</v>
+      </c>
+      <c r="V192" t="n">
+        <v>341.96</v>
+      </c>
+      <c r="W192" t="n">
+        <v>346.09</v>
+      </c>
+      <c r="X192" t="n">
+        <v>348.52</v>
+      </c>
+      <c r="Y192" t="n">
+        <v>340.7</v>
+      </c>
+      <c r="Z192" t="n">
+        <v>334.41</v>
+      </c>
+      <c r="AA192" t="n">
+        <v>328.54</v>
+      </c>
+      <c r="AB192" t="n">
+        <v>328.22</v>
+      </c>
+      <c r="AC192" t="n">
+        <v>325.69</v>
+      </c>
+      <c r="AD192" t="n">
+        <v>326.14</v>
+      </c>
+      <c r="AE192" t="n">
+        <v>326.61</v>
+      </c>
+      <c r="AF192" t="n">
+        <v>325.86</v>
+      </c>
+      <c r="AG192" t="n">
+        <v>319.77</v>
+      </c>
+      <c r="AH192" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:16:47+00:00</t>
+        </is>
+      </c>
+      <c r="B193" t="n">
+        <v>307.25</v>
+      </c>
+      <c r="C193" t="n">
+        <v>302.74</v>
+      </c>
+      <c r="D193" t="n">
+        <v>301.85</v>
+      </c>
+      <c r="E193" t="n">
+        <v>311.13</v>
+      </c>
+      <c r="F193" t="n">
+        <v>311.33</v>
+      </c>
+      <c r="G193" t="n">
+        <v>316.77</v>
+      </c>
+      <c r="H193" t="n">
+        <v>329.64</v>
+      </c>
+      <c r="I193" t="n">
+        <v>339.06</v>
+      </c>
+      <c r="J193" t="n">
+        <v>348.76</v>
+      </c>
+      <c r="K193" t="n">
+        <v>344.8</v>
+      </c>
+      <c r="L193" t="n">
+        <v>337.61</v>
+      </c>
+      <c r="M193" t="n">
+        <v>336.9</v>
+      </c>
+      <c r="N193" t="n">
+        <v>336.88</v>
+      </c>
+      <c r="O193" t="n">
+        <v>345.45</v>
+      </c>
+      <c r="P193" t="n">
+        <v>344.9</v>
+      </c>
+      <c r="Q193" t="n">
+        <v>346.85</v>
+      </c>
+      <c r="R193" t="n">
+        <v>344.21</v>
+      </c>
+      <c r="S193" t="n">
+        <v>336.73</v>
+      </c>
+      <c r="T193" t="n">
+        <v>338.45</v>
+      </c>
+      <c r="U193" t="n">
+        <v>338.35</v>
+      </c>
+      <c r="V193" t="n">
+        <v>342.36</v>
+      </c>
+      <c r="W193" t="n">
+        <v>346.24</v>
+      </c>
+      <c r="X193" t="n">
+        <v>350.88</v>
+      </c>
+      <c r="Y193" t="n">
+        <v>343.33</v>
+      </c>
+      <c r="Z193" t="n">
+        <v>338.12</v>
+      </c>
+      <c r="AA193" t="n">
+        <v>330.23</v>
+      </c>
+      <c r="AB193" t="n">
+        <v>328.61</v>
+      </c>
+      <c r="AC193" t="n">
+        <v>326.26</v>
+      </c>
+      <c r="AD193" t="n">
+        <v>326.47</v>
+      </c>
+      <c r="AE193" t="n">
+        <v>327.17</v>
+      </c>
+      <c r="AF193" t="n">
+        <v>324.14</v>
+      </c>
+      <c r="AG193" t="n">
+        <v>319.09</v>
+      </c>
+      <c r="AH193" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -21028,7 +21244,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B192"/>
+  <dimension ref="A1:B194"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22951,6 +23167,26 @@
       </c>
       <c r="B192" t="n">
         <v>-0.28</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B193" t="n">
+        <v>-0.25</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B194" t="n">
+        <v>0.7</v>
       </c>
     </row>
   </sheetData>
@@ -23119,28 +23355,28 @@
         <v>0.0366</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9971653193637229</v>
+        <v>0.9453921300461924</v>
       </c>
       <c r="J2" t="n">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="K2" t="n">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2199314814476165</v>
+        <v>0.2001231238539575</v>
       </c>
       <c r="M2" t="n">
-        <v>12.46792670377295</v>
+        <v>12.60508866449761</v>
       </c>
       <c r="N2" t="n">
-        <v>231.9522530511682</v>
+        <v>237.5296754781037</v>
       </c>
       <c r="O2" t="n">
-        <v>15.22997876069327</v>
+        <v>15.41199777699516</v>
       </c>
       <c r="P2" t="n">
-        <v>308.3684806087908</v>
+        <v>308.86344343751</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -23197,28 +23433,28 @@
         <v>0.0328</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9751919787396414</v>
+        <v>0.9226065779920558</v>
       </c>
       <c r="J3" t="n">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="K3" t="n">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2092011224369252</v>
+        <v>0.1894947594602907</v>
       </c>
       <c r="M3" t="n">
-        <v>12.25494282186555</v>
+        <v>12.40180225629366</v>
       </c>
       <c r="N3" t="n">
-        <v>238.8100623316552</v>
+        <v>244.5568132593989</v>
       </c>
       <c r="O3" t="n">
-        <v>15.45348058955183</v>
+        <v>15.63831235330075</v>
       </c>
       <c r="P3" t="n">
-        <v>304.531288793385</v>
+        <v>305.028734733303</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -23275,28 +23511,28 @@
         <v>0.0287</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3582666790996489</v>
+        <v>0.3118129769765795</v>
       </c>
       <c r="J4" t="n">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="K4" t="n">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0288645185820201</v>
+        <v>0.02200100734637622</v>
       </c>
       <c r="M4" t="n">
-        <v>13.37697907998319</v>
+        <v>13.51485337804822</v>
       </c>
       <c r="N4" t="n">
-        <v>281.1527840251486</v>
+        <v>284.5665093309357</v>
       </c>
       <c r="O4" t="n">
-        <v>16.76761116036356</v>
+        <v>16.8690992448007</v>
       </c>
       <c r="P4" t="n">
-        <v>316.9025773911525</v>
+        <v>317.3476122523841</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -23353,28 +23589,28 @@
         <v>0.035</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8516532852554222</v>
+        <v>0.8114996444713508</v>
       </c>
       <c r="J5" t="n">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="K5" t="n">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1707273409613249</v>
+        <v>0.1577871712590679</v>
       </c>
       <c r="M5" t="n">
-        <v>12.54517305729185</v>
+        <v>12.61887903022486</v>
       </c>
       <c r="N5" t="n">
-        <v>232.1599691132939</v>
+        <v>234.3579192220429</v>
       </c>
       <c r="O5" t="n">
-        <v>15.23679655023633</v>
+        <v>15.30875302635858</v>
       </c>
       <c r="P5" t="n">
-        <v>309.3287947265128</v>
+        <v>309.7077001201603</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -23431,28 +23667,28 @@
         <v>0.0321</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6458573382370429</v>
+        <v>0.6021458973793785</v>
       </c>
       <c r="J6" t="n">
+        <v>192</v>
+      </c>
+      <c r="K6" t="n">
         <v>190</v>
       </c>
-      <c r="K6" t="n">
-        <v>188</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.1132552178237946</v>
+        <v>0.09950176975879077</v>
       </c>
       <c r="M6" t="n">
-        <v>11.76138643659166</v>
+        <v>11.8584352645372</v>
       </c>
       <c r="N6" t="n">
-        <v>215.1665836268247</v>
+        <v>218.6459970458854</v>
       </c>
       <c r="O6" t="n">
-        <v>14.6685576532536</v>
+        <v>14.78668309817606</v>
       </c>
       <c r="P6" t="n">
-        <v>317.8790429038144</v>
+        <v>318.292051425147</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -23509,28 +23745,28 @@
         <v>0.034</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4097895938165086</v>
+        <v>0.3746265974057084</v>
       </c>
       <c r="J7" t="n">
+        <v>192</v>
+      </c>
+      <c r="K7" t="n">
         <v>190</v>
       </c>
-      <c r="K7" t="n">
-        <v>188</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.05365474627440769</v>
+        <v>0.04536311832073647</v>
       </c>
       <c r="M7" t="n">
-        <v>11.05733587759864</v>
+        <v>11.10114100415648</v>
       </c>
       <c r="N7" t="n">
-        <v>195.1302135428673</v>
+        <v>196.7970267002044</v>
       </c>
       <c r="O7" t="n">
-        <v>13.96890165842924</v>
+        <v>14.02843635977312</v>
       </c>
       <c r="P7" t="n">
-        <v>325.4856774454836</v>
+        <v>325.8179207541988</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -23587,28 +23823,28 @@
         <v>0.0439</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4501644210492381</v>
+        <v>0.4276357100778043</v>
       </c>
       <c r="J8" t="n">
+        <v>192</v>
+      </c>
+      <c r="K8" t="n">
         <v>190</v>
       </c>
-      <c r="K8" t="n">
-        <v>188</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.090569819789596</v>
+        <v>0.08325697432446455</v>
       </c>
       <c r="M8" t="n">
-        <v>8.934027811591408</v>
+        <v>8.958651316627293</v>
       </c>
       <c r="N8" t="n">
-        <v>134.0569700161001</v>
+        <v>134.1717017044406</v>
       </c>
       <c r="O8" t="n">
-        <v>11.57829737120705</v>
+        <v>11.58325091260828</v>
       </c>
       <c r="P8" t="n">
-        <v>329.779713035142</v>
+        <v>329.9925752277028</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -23665,28 +23901,28 @@
         <v>0.0436</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4536796330205989</v>
+        <v>0.4345571083207784</v>
       </c>
       <c r="J9" t="n">
+        <v>192</v>
+      </c>
+      <c r="K9" t="n">
         <v>190</v>
       </c>
-      <c r="K9" t="n">
-        <v>188</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.1088569845387386</v>
+        <v>0.1018647253654497</v>
       </c>
       <c r="M9" t="n">
-        <v>8.094492658010058</v>
+        <v>8.10017433953313</v>
       </c>
       <c r="N9" t="n">
-        <v>111.007131243677</v>
+        <v>110.9424266034457</v>
       </c>
       <c r="O9" t="n">
-        <v>10.53599218126499</v>
+        <v>10.53292108597827</v>
       </c>
       <c r="P9" t="n">
-        <v>336.6308675438631</v>
+        <v>336.8115402296439</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -23743,28 +23979,28 @@
         <v>0.0433</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5543514903582465</v>
+        <v>0.5392505272774357</v>
       </c>
       <c r="J10" t="n">
+        <v>192</v>
+      </c>
+      <c r="K10" t="n">
         <v>190</v>
       </c>
-      <c r="K10" t="n">
-        <v>188</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.1256242014006186</v>
+        <v>0.1214856660928465</v>
       </c>
       <c r="M10" t="n">
-        <v>8.778374841885176</v>
+        <v>8.766792703171223</v>
       </c>
       <c r="N10" t="n">
-        <v>140.9147514541727</v>
+        <v>140.117047827963</v>
       </c>
       <c r="O10" t="n">
-        <v>11.8707519329726</v>
+        <v>11.83710470630226</v>
       </c>
       <c r="P10" t="n">
-        <v>342.0352949890636</v>
+        <v>342.1779757513737</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -23821,28 +24057,28 @@
         <v>0.0418</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5992178377512493</v>
+        <v>0.5836274938460824</v>
       </c>
       <c r="J11" t="n">
+        <v>192</v>
+      </c>
+      <c r="K11" t="n">
         <v>190</v>
       </c>
-      <c r="K11" t="n">
-        <v>188</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.1478478680276619</v>
+        <v>0.1433442275612899</v>
       </c>
       <c r="M11" t="n">
-        <v>9.195459661343035</v>
+        <v>9.209965100035465</v>
       </c>
       <c r="N11" t="n">
-        <v>136.3429669106039</v>
+        <v>135.6387039202519</v>
       </c>
       <c r="O11" t="n">
-        <v>11.6765991157787</v>
+        <v>11.64640304644536</v>
       </c>
       <c r="P11" t="n">
-        <v>337.0613220507137</v>
+        <v>337.2086259857726</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -23899,28 +24135,28 @@
         <v>0.0421</v>
       </c>
       <c r="I12" t="n">
-        <v>0.6158482026371855</v>
+        <v>0.594822844764239</v>
       </c>
       <c r="J12" t="n">
+        <v>192</v>
+      </c>
+      <c r="K12" t="n">
         <v>190</v>
       </c>
-      <c r="K12" t="n">
-        <v>188</v>
-      </c>
       <c r="L12" t="n">
-        <v>0.1488845111731957</v>
+        <v>0.1418158888931912</v>
       </c>
       <c r="M12" t="n">
-        <v>9.393328827991997</v>
+        <v>9.433160178012921</v>
       </c>
       <c r="N12" t="n">
-        <v>142.8392419343999</v>
+        <v>142.6648113245926</v>
       </c>
       <c r="O12" t="n">
-        <v>11.9515372205587</v>
+        <v>11.94423757820451</v>
       </c>
       <c r="P12" t="n">
-        <v>332.4073130366942</v>
+        <v>332.6059699426465</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -23977,28 +24213,28 @@
         <v>0.0429</v>
       </c>
       <c r="I13" t="n">
-        <v>0.6745947802735121</v>
+        <v>0.6607575672400551</v>
       </c>
       <c r="J13" t="n">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="K13" t="n">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2265113931250901</v>
+        <v>0.2221168186942341</v>
       </c>
       <c r="M13" t="n">
-        <v>8.051486142438181</v>
+        <v>8.055512349961834</v>
       </c>
       <c r="N13" t="n">
-        <v>103.3015914577586</v>
+        <v>102.8021957467333</v>
       </c>
       <c r="O13" t="n">
-        <v>10.16373904907828</v>
+        <v>10.13914176578735</v>
       </c>
       <c r="P13" t="n">
-        <v>326.5190457287676</v>
+        <v>326.6485774533174</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -24055,28 +24291,28 @@
         <v>0.0448</v>
       </c>
       <c r="I14" t="n">
-        <v>0.6100634400508747</v>
+        <v>0.5987813991650052</v>
       </c>
       <c r="J14" t="n">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="K14" t="n">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2010547124453093</v>
+        <v>0.197949038596771</v>
       </c>
       <c r="M14" t="n">
-        <v>7.868151298850494</v>
+        <v>7.85515432769804</v>
       </c>
       <c r="N14" t="n">
-        <v>98.31277859360326</v>
+        <v>97.67205631254625</v>
       </c>
       <c r="O14" t="n">
-        <v>9.915280056236599</v>
+        <v>9.882917398852742</v>
       </c>
       <c r="P14" t="n">
-        <v>326.2915750059107</v>
+        <v>326.397182408725</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -24133,28 +24369,28 @@
         <v>0.0419</v>
       </c>
       <c r="I15" t="n">
-        <v>0.6753622076929993</v>
+        <v>0.6792832508329335</v>
       </c>
       <c r="J15" t="n">
+        <v>192</v>
+      </c>
+      <c r="K15" t="n">
         <v>190</v>
       </c>
-      <c r="K15" t="n">
-        <v>188</v>
-      </c>
       <c r="L15" t="n">
-        <v>0.2184755125822572</v>
+        <v>0.2241545213830665</v>
       </c>
       <c r="M15" t="n">
-        <v>8.161357954328027</v>
+        <v>8.093449173073155</v>
       </c>
       <c r="N15" t="n">
-        <v>108.5767338406031</v>
+        <v>107.4817293273121</v>
       </c>
       <c r="O15" t="n">
-        <v>10.42001601921048</v>
+        <v>10.36733954914722</v>
       </c>
       <c r="P15" t="n">
-        <v>324.8738984362885</v>
+        <v>324.8371345903425</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -24211,28 +24447,28 @@
         <v>0.0442</v>
       </c>
       <c r="I16" t="n">
-        <v>0.7240099249437086</v>
+        <v>0.7286079245937408</v>
       </c>
       <c r="J16" t="n">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="K16" t="n">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2319183716436549</v>
+        <v>0.2380136495534394</v>
       </c>
       <c r="M16" t="n">
-        <v>8.717089489432906</v>
+        <v>8.643365646853431</v>
       </c>
       <c r="N16" t="n">
-        <v>114.9185279640571</v>
+        <v>113.7794188871887</v>
       </c>
       <c r="O16" t="n">
-        <v>10.72000596847115</v>
+        <v>10.66674359339291</v>
       </c>
       <c r="P16" t="n">
-        <v>322.8896119191474</v>
+        <v>322.8463606747754</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -24289,28 +24525,28 @@
         <v>0.0482</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6756780208696173</v>
+        <v>0.6821095856217865</v>
       </c>
       <c r="J17" t="n">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="K17" t="n">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2249655719378464</v>
+        <v>0.231917700399687</v>
       </c>
       <c r="M17" t="n">
-        <v>8.314752152705454</v>
+        <v>8.253526003170824</v>
       </c>
       <c r="N17" t="n">
-        <v>104.1150014283743</v>
+        <v>103.1603408371129</v>
       </c>
       <c r="O17" t="n">
-        <v>10.20367587824968</v>
+        <v>10.15678791927413</v>
       </c>
       <c r="P17" t="n">
-        <v>324.219357224665</v>
+        <v>324.1588498147443</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -24367,28 +24603,28 @@
         <v>0.0524</v>
       </c>
       <c r="I18" t="n">
-        <v>0.628073958371501</v>
+        <v>0.6369006329374454</v>
       </c>
       <c r="J18" t="n">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="K18" t="n">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="L18" t="n">
-        <v>0.152143847669772</v>
+        <v>0.158444218848343</v>
       </c>
       <c r="M18" t="n">
-        <v>10.45771320785136</v>
+        <v>10.3851211180094</v>
       </c>
       <c r="N18" t="n">
-        <v>145.5184783688327</v>
+        <v>144.2382594903624</v>
       </c>
       <c r="O18" t="n">
-        <v>12.06310401052866</v>
+        <v>12.00992337570737</v>
       </c>
       <c r="P18" t="n">
-        <v>321.7042136600215</v>
+        <v>321.621178447848</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -24445,28 +24681,28 @@
         <v>0.05</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4709802724078025</v>
+        <v>0.4764975187385918</v>
       </c>
       <c r="J19" t="n">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="K19" t="n">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1073244249127453</v>
+        <v>0.1116502478232393</v>
       </c>
       <c r="M19" t="n">
-        <v>9.197794561203313</v>
+        <v>9.12886362968589</v>
       </c>
       <c r="N19" t="n">
-        <v>122.0047119353752</v>
+        <v>120.8284514514251</v>
       </c>
       <c r="O19" t="n">
-        <v>11.04557431442002</v>
+        <v>10.99219957294376</v>
       </c>
       <c r="P19" t="n">
-        <v>320.5759956964715</v>
+        <v>320.524173142903</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -24523,28 +24759,28 @@
         <v>0.0506</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3532488433242227</v>
+        <v>0.3649607952295507</v>
       </c>
       <c r="J20" t="n">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="K20" t="n">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="L20" t="n">
-        <v>0.06400682583232098</v>
+        <v>0.06920229535832523</v>
       </c>
       <c r="M20" t="n">
-        <v>9.090842714289636</v>
+        <v>9.053424015257912</v>
       </c>
       <c r="N20" t="n">
-        <v>120.6657389267094</v>
+        <v>119.8259444837028</v>
       </c>
       <c r="O20" t="n">
-        <v>10.98479580723781</v>
+        <v>10.94650375616355</v>
       </c>
       <c r="P20" t="n">
-        <v>322.0997725555469</v>
+        <v>321.9897699871551</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -24601,28 +24837,28 @@
         <v>0.0544</v>
       </c>
       <c r="I21" t="n">
-        <v>0.5090099851349249</v>
+        <v>0.5173890838521754</v>
       </c>
       <c r="J21" t="n">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="K21" t="n">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="L21" t="n">
-        <v>0.127087502673446</v>
+        <v>0.1330426855400758</v>
       </c>
       <c r="M21" t="n">
-        <v>8.848449429931572</v>
+        <v>8.794710517191293</v>
       </c>
       <c r="N21" t="n">
-        <v>117.8010767040697</v>
+        <v>116.7809052505071</v>
       </c>
       <c r="O21" t="n">
-        <v>10.85362044223354</v>
+        <v>10.80652142229437</v>
       </c>
       <c r="P21" t="n">
-        <v>320.2478363470906</v>
+        <v>320.1690206367745</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -24679,28 +24915,28 @@
         <v>0.0505</v>
       </c>
       <c r="I22" t="n">
-        <v>0.3682541297772334</v>
+        <v>0.3827653060497535</v>
       </c>
       <c r="J22" t="n">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="K22" t="n">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0546699070959592</v>
+        <v>0.05979331100083873</v>
       </c>
       <c r="M22" t="n">
-        <v>10.23314073621387</v>
+        <v>10.18362222420589</v>
       </c>
       <c r="N22" t="n">
-        <v>155.0623951248661</v>
+        <v>154.0846921276282</v>
       </c>
       <c r="O22" t="n">
-        <v>12.45240519437374</v>
+        <v>12.41308552003201</v>
       </c>
       <c r="P22" t="n">
-        <v>324.334530005509</v>
+        <v>324.1982397647619</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -24757,28 +24993,28 @@
         <v>0.0567</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3659814303932641</v>
+        <v>0.383903373981538</v>
       </c>
       <c r="J23" t="n">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="K23" t="n">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="L23" t="n">
-        <v>0.05518102809408765</v>
+        <v>0.06126355661881899</v>
       </c>
       <c r="M23" t="n">
-        <v>9.8043770305491</v>
+        <v>9.796718253147935</v>
       </c>
       <c r="N23" t="n">
-        <v>151.6536986864627</v>
+        <v>151.0459060963797</v>
       </c>
       <c r="O23" t="n">
-        <v>12.31477562469015</v>
+        <v>12.29007347807082</v>
       </c>
       <c r="P23" t="n">
-        <v>326.5366469136393</v>
+        <v>326.3683240947053</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -24835,28 +25071,28 @@
         <v>0.0536</v>
       </c>
       <c r="I24" t="n">
-        <v>0.466882099237251</v>
+        <v>0.4821490356054249</v>
       </c>
       <c r="J24" t="n">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="K24" t="n">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="L24" t="n">
-        <v>0.09425883376802457</v>
+        <v>0.1014033500754219</v>
       </c>
       <c r="M24" t="n">
-        <v>9.420608505612627</v>
+        <v>9.399360657131529</v>
       </c>
       <c r="N24" t="n">
-        <v>138.5072732684111</v>
+        <v>137.7839799508516</v>
       </c>
       <c r="O24" t="n">
-        <v>11.76891130344736</v>
+        <v>11.73814209961916</v>
       </c>
       <c r="P24" t="n">
-        <v>328.8183040364981</v>
+        <v>328.6749061664032</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -24913,28 +25149,28 @@
         <v>0.0562</v>
       </c>
       <c r="I25" t="n">
-        <v>0.2588445508208134</v>
+        <v>0.2658172761556443</v>
       </c>
       <c r="J25" t="n">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="K25" t="n">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="L25" t="n">
-        <v>0.0271078437259582</v>
+        <v>0.02912714792825877</v>
       </c>
       <c r="M25" t="n">
-        <v>10.32387761766466</v>
+        <v>10.25540703266981</v>
       </c>
       <c r="N25" t="n">
-        <v>159.1756282536004</v>
+        <v>157.6744791060541</v>
       </c>
       <c r="O25" t="n">
-        <v>12.61648240412518</v>
+        <v>12.55684988785221</v>
       </c>
       <c r="P25" t="n">
-        <v>331.2582180558338</v>
+        <v>331.1926169816361</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -24991,28 +25227,28 @@
         <v>0.064</v>
       </c>
       <c r="I26" t="n">
-        <v>0.2478045357505466</v>
+        <v>0.2513160742930027</v>
       </c>
       <c r="J26" t="n">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="K26" t="n">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="L26" t="n">
-        <v>0.0205364237417387</v>
+        <v>0.02156078869992784</v>
       </c>
       <c r="M26" t="n">
-        <v>11.31020471985534</v>
+        <v>11.20575885563618</v>
       </c>
       <c r="N26" t="n">
-        <v>194.4682641436898</v>
+        <v>192.5051460833948</v>
       </c>
       <c r="O26" t="n">
-        <v>13.94518784899256</v>
+        <v>13.87462237624487</v>
       </c>
       <c r="P26" t="n">
-        <v>327.6984216330348</v>
+        <v>327.6655415165953</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -25069,28 +25305,28 @@
         <v>0.0554</v>
       </c>
       <c r="I27" t="n">
-        <v>0.3693685991902713</v>
+        <v>0.3666217329815805</v>
       </c>
       <c r="J27" t="n">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="K27" t="n">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="L27" t="n">
-        <v>0.03753054432499314</v>
+        <v>0.03777703572422342</v>
       </c>
       <c r="M27" t="n">
-        <v>12.05823929526886</v>
+        <v>11.95491871832004</v>
       </c>
       <c r="N27" t="n">
-        <v>231.3652477181114</v>
+        <v>228.985446497623</v>
       </c>
       <c r="O27" t="n">
-        <v>15.21069517537287</v>
+        <v>15.13226508152772</v>
       </c>
       <c r="P27" t="n">
-        <v>320.9807059912401</v>
+        <v>321.0064962416126</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -25147,28 +25383,28 @@
         <v>0.0452</v>
       </c>
       <c r="I28" t="n">
-        <v>0.2511532207724638</v>
+        <v>0.2486019201641688</v>
       </c>
       <c r="J28" t="n">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="K28" t="n">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="L28" t="n">
-        <v>0.02240370698755845</v>
+        <v>0.02243288492777207</v>
       </c>
       <c r="M28" t="n">
-        <v>10.98385605488961</v>
+        <v>10.88430794953198</v>
       </c>
       <c r="N28" t="n">
-        <v>182.0091639084203</v>
+        <v>180.1333148354359</v>
       </c>
       <c r="O28" t="n">
-        <v>13.4910771959996</v>
+        <v>13.42137529597604</v>
       </c>
       <c r="P28" t="n">
-        <v>323.076844098766</v>
+        <v>323.1008039506626</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -25225,28 +25461,28 @@
         <v>0.0527</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1992390553576117</v>
+        <v>0.1956800117898385</v>
       </c>
       <c r="J29" t="n">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="K29" t="n">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="L29" t="n">
-        <v>0.0172477959625813</v>
+        <v>0.01700455861590533</v>
       </c>
       <c r="M29" t="n">
-        <v>10.34462898808</v>
+        <v>10.25709990481732</v>
       </c>
       <c r="N29" t="n">
-        <v>149.56688792706</v>
+        <v>148.0480530577621</v>
       </c>
       <c r="O29" t="n">
-        <v>12.2297542055047</v>
+        <v>12.16749986882112</v>
       </c>
       <c r="P29" t="n">
-        <v>322.5813739052892</v>
+        <v>322.614797570251</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
@@ -25303,28 +25539,28 @@
         <v>0.0524</v>
       </c>
       <c r="I30" t="n">
-        <v>0.2504573255192607</v>
+        <v>0.2471080899664289</v>
       </c>
       <c r="J30" t="n">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="K30" t="n">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="L30" t="n">
-        <v>0.02537497999679217</v>
+        <v>0.02524474966020129</v>
       </c>
       <c r="M30" t="n">
-        <v>10.3114189634408</v>
+        <v>10.22366721621351</v>
       </c>
       <c r="N30" t="n">
-        <v>159.3218768198685</v>
+        <v>157.6965059419894</v>
       </c>
       <c r="O30" t="n">
-        <v>12.62227700614546</v>
+        <v>12.55772694168771</v>
       </c>
       <c r="P30" t="n">
-        <v>321.4212665755421</v>
+        <v>321.4527208480334</v>
       </c>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr">
@@ -25381,28 +25617,28 @@
         <v>0.0501</v>
       </c>
       <c r="I31" t="n">
-        <v>0.3484868427528738</v>
+        <v>0.3454871740637722</v>
       </c>
       <c r="J31" t="n">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="K31" t="n">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="L31" t="n">
-        <v>0.05542996464205929</v>
+        <v>0.05565636814069475</v>
       </c>
       <c r="M31" t="n">
-        <v>9.193316693837501</v>
+        <v>9.115912147537452</v>
       </c>
       <c r="N31" t="n">
-        <v>136.9907126547466</v>
+        <v>135.5843781240074</v>
       </c>
       <c r="O31" t="n">
-        <v>11.70430316826878</v>
+        <v>11.64407051352779</v>
       </c>
       <c r="P31" t="n">
-        <v>319.1853056984692</v>
+        <v>319.2135190374596</v>
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
@@ -25459,28 +25695,28 @@
         <v>0.0491</v>
       </c>
       <c r="I32" t="n">
-        <v>0.3009427121315297</v>
+        <v>0.301307317917718</v>
       </c>
       <c r="J32" t="n">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="K32" t="n">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="L32" t="n">
-        <v>0.05535158389618755</v>
+        <v>0.05662817678878251</v>
       </c>
       <c r="M32" t="n">
-        <v>8.030728435171522</v>
+        <v>7.955483527961834</v>
       </c>
       <c r="N32" t="n">
-        <v>102.3143618106783</v>
+        <v>101.2512241564539</v>
       </c>
       <c r="O32" t="n">
-        <v>10.11505619414338</v>
+        <v>10.06236672738844</v>
       </c>
       <c r="P32" t="n">
-        <v>316.7320605362827</v>
+        <v>316.7286393890259</v>
       </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
@@ -25537,28 +25773,28 @@
         <v>0.0427</v>
       </c>
       <c r="I33" t="n">
-        <v>0.246625891695572</v>
+        <v>0.2422825193236586</v>
       </c>
       <c r="J33" t="n">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="K33" t="n">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="L33" t="n">
-        <v>0.03253717146140123</v>
+        <v>0.03209261697391919</v>
       </c>
       <c r="M33" t="n">
-        <v>8.596002626604479</v>
+        <v>8.527816058457889</v>
       </c>
       <c r="N33" t="n">
-        <v>119.7183215496864</v>
+        <v>118.5232178282049</v>
       </c>
       <c r="O33" t="n">
-        <v>10.9415867930427</v>
+        <v>10.88683690647586</v>
       </c>
       <c r="P33" t="n">
-        <v>315.1947599353398</v>
+        <v>315.2356187592841</v>
       </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
@@ -25596,7 +25832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH191"/>
+  <dimension ref="A1:AH193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58239,6 +58475,350 @@
         </is>
       </c>
     </row>
+    <row r="192">
+      <c r="A192" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:16:51+00:00</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>-34.42298748220088,173.01241684081057</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>-34.42362242155975,173.011950558727</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>-34.42427434487502,173.011523416558</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>-34.42497011741651,173.01119730764063</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>-34.4256296465435,173.01078771185604</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>-34.426312562559495,173.01043200780964</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>-34.427017275574876,173.0101265331384</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>-34.42770758866241,173.00978789544277</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>-34.42841870462471,173.0094694608708</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>-34.429116364455275,173.0091248169411</t>
+        </is>
+      </c>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>-34.42980284629401,173.00877181211737</t>
+        </is>
+      </c>
+      <c r="M192" t="inlineStr">
+        <is>
+          <t>-34.43050672533413,173.00849123919022</t>
+        </is>
+      </c>
+      <c r="N192" t="inlineStr">
+        <is>
+          <t>-34.43120811583791,173.00820145454878</t>
+        </is>
+      </c>
+      <c r="O192" t="inlineStr">
+        <is>
+          <t>-34.431937004259865,173.00801372353223</t>
+        </is>
+      </c>
+      <c r="P192" t="inlineStr">
+        <is>
+          <t>-34.43264267523051,173.00773424366074</t>
+        </is>
+      </c>
+      <c r="Q192" t="inlineStr">
+        <is>
+          <t>-34.43335764904367,173.00746830473003</t>
+        </is>
+      </c>
+      <c r="R192" t="inlineStr">
+        <is>
+          <t>-34.43407925888443,173.00723381646702</t>
+        </is>
+      </c>
+      <c r="S192" t="inlineStr">
+        <is>
+          <t>-34.434785799320636,173.00695354111093</t>
+        </is>
+      </c>
+      <c r="T192" t="inlineStr">
+        <is>
+          <t>-34.4355103082081,173.00676454623903</t>
+        </is>
+      </c>
+      <c r="U192" t="inlineStr">
+        <is>
+          <t>-34.43623333038472,173.00656803306154</t>
+        </is>
+      </c>
+      <c r="V192" t="inlineStr">
+        <is>
+          <t>-34.43696103822006,173.00639534689674</t>
+        </is>
+      </c>
+      <c r="W192" t="inlineStr">
+        <is>
+          <t>-34.43769038727184,173.00623102725586</t>
+        </is>
+      </c>
+      <c r="X192" t="inlineStr">
+        <is>
+          <t>-34.43842039180975,173.0060474841609</t>
+        </is>
+      </c>
+      <c r="Y192" t="inlineStr">
+        <is>
+          <t>-34.4391469714221,173.00580522931668</t>
+        </is>
+      </c>
+      <c r="Z192" t="inlineStr">
+        <is>
+          <t>-34.43988253237334,173.0056317722395</t>
+        </is>
+      </c>
+      <c r="AA192" t="inlineStr">
+        <is>
+          <t>-34.440612226785824,173.00546391101003</t>
+        </is>
+      </c>
+      <c r="AB192" t="inlineStr">
+        <is>
+          <t>-34.44134772109342,173.0053560538771</t>
+        </is>
+      </c>
+      <c r="AC192" t="inlineStr">
+        <is>
+          <t>-34.442080896777824,173.00522430251752</t>
+        </is>
+      </c>
+      <c r="AD192" t="inlineStr">
+        <is>
+          <t>-34.44281718369526,173.00512477024674</t>
+        </is>
+      </c>
+      <c r="AE192" t="inlineStr">
+        <is>
+          <t>-34.44355993631181,173.0050245897016</t>
+        </is>
+      </c>
+      <c r="AF192" t="inlineStr">
+        <is>
+          <t>-34.44430636884295,173.004944837023</t>
+        </is>
+      </c>
+      <c r="AG192" t="inlineStr">
+        <is>
+          <t>-34.44504404444752,173.0048187597988</t>
+        </is>
+      </c>
+      <c r="AH192" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:16:47+00:00</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>-34.42298693821355,173.01241558755788</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>-34.42362422091301,173.01195470412597</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>-34.424276646385266,173.011528718846</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>-34.424971623864515,173.01120077825465</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>-34.42562860039393,173.01078530169184</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>-34.42630749917574,173.0104203425332</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>-34.42701748480618,173.01012701517828</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>-34.427713028694924,173.00980042857148</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>-34.42841913553355,173.00947065889957</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>-34.42911714296394,173.009127601284</t>
+        </is>
+      </c>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>-34.42980345996166,173.0087740891262</t>
+        </is>
+      </c>
+      <c r="M193" t="inlineStr">
+        <is>
+          <t>-34.430505972192414,173.00848844465764</t>
+        </is>
+      </c>
+      <c r="N193" t="inlineStr">
+        <is>
+          <t>-34.43121040316989,173.0082099417137</t>
+        </is>
+      </c>
+      <c r="O193" t="inlineStr">
+        <is>
+          <t>-34.4319387894993,173.0080203477165</t>
+        </is>
+      </c>
+      <c r="P193" t="inlineStr">
+        <is>
+          <t>-34.432643083419066,173.00773580017747</t>
+        </is>
+      </c>
+      <c r="Q193" t="inlineStr">
+        <is>
+          <t>-34.433362342074105,173.00748909782135</t>
+        </is>
+      </c>
+      <c r="R193" t="inlineStr">
+        <is>
+          <t>-34.43408272034812,173.0072513947867</t>
+        </is>
+      </c>
+      <c r="S193" t="inlineStr">
+        <is>
+          <t>-34.43478788455774,173.00696413054396</t>
+        </is>
+      </c>
+      <c r="T193" t="inlineStr">
+        <is>
+          <t>-34.43551222663528,173.00677428859882</t>
+        </is>
+      </c>
+      <c r="U193" t="inlineStr">
+        <is>
+          <t>-34.43623276736509,173.00656517386705</t>
+        </is>
+      </c>
+      <c r="V193" t="inlineStr">
+        <is>
+          <t>-34.43696187232646,173.00639958277628</t>
+        </is>
+      </c>
+      <c r="W193" t="inlineStr">
+        <is>
+          <t>-34.437690700062895,173.00623261572414</t>
+        </is>
+      </c>
+      <c r="X193" t="inlineStr">
+        <is>
+          <t>-34.43842470373938,173.00607263971352</t>
+        </is>
+      </c>
+      <c r="Y193" t="inlineStr">
+        <is>
+          <t>-34.43915040848801,173.0058335545749</t>
+        </is>
+      </c>
+      <c r="Z193" t="inlineStr">
+        <is>
+          <t>-34.43988641373843,173.00567188313065</t>
+        </is>
+      </c>
+      <c r="AA193" t="inlineStr">
+        <is>
+          <t>-34.44061399486802,173.00548218270364</t>
+        </is>
+      </c>
+      <c r="AB193" t="inlineStr">
+        <is>
+          <t>-34.44134812911504,173.0053602704583</t>
+        </is>
+      </c>
+      <c r="AC193" t="inlineStr">
+        <is>
+          <t>-34.44208149312179,173.00523046526632</t>
+        </is>
+      </c>
+      <c r="AD193" t="inlineStr">
+        <is>
+          <t>-34.44281752894885,173.005128338185</t>
+        </is>
+      </c>
+      <c r="AE193" t="inlineStr">
+        <is>
+          <t>-34.44356042776358,173.00503065666652</t>
+        </is>
+      </c>
+      <c r="AF193" t="inlineStr">
+        <is>
+          <t>-34.444305244585244,173.00492616298843</t>
+        </is>
+      </c>
+      <c r="AG193" t="inlineStr">
+        <is>
+          <t>-34.445043637359625,173.00481137383517</t>
+        </is>
+      </c>
+      <c r="AH193" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
